--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122959139</v>
+        <v>122970443</v>
       </c>
       <c r="B2" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459493</v>
+        <v>459134</v>
       </c>
       <c r="R2" t="n">
-        <v>7031246</v>
+        <v>7031419</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran (14 cm dbh, ca 160 år gammal) i gammal granskog vid bäck</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,41 +781,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122960970</v>
+        <v>122960048</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459435</v>
+        <v>459483</v>
       </c>
       <c r="R3" t="n">
-        <v>7031306</v>
+        <v>7031282</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +870,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 17 cm i diameter</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,51 +898,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122964051</v>
+        <v>122960970</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,42 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459393</v>
+        <v>459435</v>
       </c>
       <c r="R4" t="n">
-        <v>7031334</v>
+        <v>7031306</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,11 +992,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,22 +1008,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122960048</v>
+        <v>122964051</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,37 +1057,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459483</v>
+        <v>459393</v>
       </c>
       <c r="R5" t="n">
-        <v>7031282</v>
+        <v>7031334</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,24 +1119,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran ca 17 cm i diameter</t>
+          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,26 +1137,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122988637</v>
+        <v>122959139</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>77709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,37 +1194,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459515</v>
+        <v>459493</v>
       </c>
       <c r="R6" t="n">
-        <v>7031220</v>
+        <v>7031246</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,11 +1251,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på undersidan av död gren på gammal levande gran (14 cm dbh, ca 160 år gammal) i gammal granskog vid bäck</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1274,26 +1279,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122988659</v>
+        <v>122988637</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,21 +1326,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1330,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458995</v>
+        <v>459515</v>
       </c>
       <c r="R7" t="n">
-        <v>7031695</v>
+        <v>7031220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970443</v>
+        <v>122988659</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,42 +1428,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459134</v>
+        <v>458995</v>
       </c>
       <c r="R8" t="n">
-        <v>7031419</v>
+        <v>7031695</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,24 +1485,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,12 +1502,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122965369</v>
+        <v>122971514</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,34 +2990,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459220</v>
+        <v>459123</v>
       </c>
       <c r="R22" t="n">
-        <v>7031200</v>
+        <v>7031364</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,24 +3052,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,22 +3074,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122969476</v>
+        <v>122968278</v>
       </c>
       <c r="B23" t="n">
-        <v>74863</v>
+        <v>78503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,21 +3102,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3131,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458820</v>
+        <v>459059</v>
       </c>
       <c r="R23" t="n">
-        <v>7031282</v>
+        <v>7031142</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3193,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122959207</v>
+        <v>122965369</v>
       </c>
       <c r="B24" t="n">
-        <v>74675</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,38 +3200,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459497</v>
+        <v>459220</v>
       </c>
       <c r="R24" t="n">
-        <v>7031235</v>
+        <v>7031200</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3268,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,12 +3273,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På ved på gren på gammal gran i gammal granskog vid bäck</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,22 +3293,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122959894</v>
+        <v>122969476</v>
       </c>
       <c r="B25" t="n">
-        <v>74847</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3322,25 +3317,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459316</v>
+        <v>458820</v>
       </c>
       <c r="R25" t="n">
-        <v>7031273</v>
+        <v>7031282</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122988658</v>
+        <v>122959207</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>74675</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3424,38 +3419,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458928</v>
+        <v>459497</v>
       </c>
       <c r="R26" t="n">
-        <v>7031321</v>
+        <v>7031235</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3485,9 +3480,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På ved på gren på gammal gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,22 +3512,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122971798</v>
+        <v>122959894</v>
       </c>
       <c r="B27" t="n">
-        <v>79848</v>
+        <v>74847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,25 +3536,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3554,13 +3564,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459082</v>
+        <v>459316</v>
       </c>
       <c r="R27" t="n">
-        <v>7031485</v>
+        <v>7031273</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3587,24 +3597,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,22 +3614,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122971013</v>
+        <v>122988658</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3647,34 +3642,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459018</v>
+        <v>458928</v>
       </c>
       <c r="R28" t="n">
-        <v>7031385</v>
+        <v>7031321</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,24 +3699,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3736,22 +3716,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122962975</v>
+        <v>122971798</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,39 +3744,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459414</v>
+        <v>459082</v>
       </c>
       <c r="R29" t="n">
-        <v>7031352</v>
+        <v>7031485</v>
       </c>
       <c r="S29" t="n">
         <v>11</v>
@@ -3826,14 +3801,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
+          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,48 +3829,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122973453</v>
+        <v>122971013</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -3919,21 +3879,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459256</v>
+        <v>459018</v>
       </c>
       <c r="R30" t="n">
-        <v>7031469</v>
+        <v>7031385</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,14 +3918,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om bålar på en grov gammal sälg.</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,51 +3946,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122988663</v>
+        <v>122962975</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4038,37 +3978,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459127</v>
+        <v>459414</v>
       </c>
       <c r="R31" t="n">
-        <v>7031202</v>
+        <v>7031352</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,6 +4045,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4108,26 +4058,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122962307</v>
+        <v>122973453</v>
       </c>
       <c r="B32" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4136,31 +4111,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4169,10 +4144,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459411</v>
+        <v>459256</v>
       </c>
       <c r="R32" t="n">
-        <v>7031338</v>
+        <v>7031469</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4209,7 +4184,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>Gott om bålar på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4223,7 +4198,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4261,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122962699</v>
+        <v>122988663</v>
       </c>
       <c r="B33" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4273,46 +4248,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459414</v>
+        <v>459127</v>
       </c>
       <c r="R33" t="n">
-        <v>7031347</v>
+        <v>7031202</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4352,51 +4322,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122971514</v>
+        <v>122962307</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4405,31 +4350,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4438,10 +4383,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459123</v>
+        <v>459411</v>
       </c>
       <c r="R34" t="n">
-        <v>7031364</v>
+        <v>7031338</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4423,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4489,6 +4434,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4505,10 +4475,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122968278</v>
+        <v>122962699</v>
       </c>
       <c r="B35" t="n">
-        <v>78503</v>
+        <v>79883</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4517,41 +4487,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459059</v>
+        <v>459414</v>
       </c>
       <c r="R35" t="n">
-        <v>7031142</v>
+        <v>7031347</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4591,6 +4566,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4607,10 +4607,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122959877</v>
+        <v>122988628</v>
       </c>
       <c r="B36" t="n">
-        <v>74854</v>
+        <v>97319</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4619,38 +4619,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459316</v>
+        <v>458859</v>
       </c>
       <c r="R36" t="n">
-        <v>7031273</v>
+        <v>7031389</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,22 +4697,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122959935</v>
+        <v>122959785</v>
       </c>
       <c r="B37" t="n">
-        <v>74854</v>
+        <v>77699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4721,50 +4721,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459442</v>
+        <v>459495</v>
       </c>
       <c r="R37" t="n">
-        <v>7031246</v>
+        <v>7031265</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4793,7 +4784,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4803,12 +4794,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Under gammal björk</t>
+          <t>På gammal gran 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4823,22 +4814,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122958245</v>
+        <v>122962387</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4851,21 +4842,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4875,13 +4866,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459590</v>
+        <v>459409</v>
       </c>
       <c r="R38" t="n">
-        <v>7031260</v>
+        <v>7031325</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4908,24 +4899,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4936,26 +4917,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122967565</v>
+        <v>122974681</v>
       </c>
       <c r="B39" t="n">
-        <v>82553</v>
+        <v>79883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4964,41 +4970,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459190</v>
+        <v>459157</v>
       </c>
       <c r="R39" t="n">
-        <v>7031278</v>
+        <v>7031692</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5027,7 +5033,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5037,12 +5043,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På lite lutande gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,10 +5075,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122962434</v>
+        <v>122988619</v>
       </c>
       <c r="B40" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5085,42 +5091,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459411</v>
+        <v>459028</v>
       </c>
       <c r="R40" t="n">
-        <v>7031335</v>
+        <v>7031497</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5152,11 +5158,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På en liggande levande smal sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5166,50 +5167,30 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gammal tall med grov bark</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122988597</v>
+        <v>122958453</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5222,34 +5203,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458852</v>
+        <v>459574</v>
       </c>
       <c r="R41" t="n">
-        <v>7031387</v>
+        <v>7031253</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,6 +5275,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5292,26 +5288,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122988631</v>
+        <v>122958335</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5324,34 +5345,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Offerdal, Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458987</v>
+        <v>459567</v>
       </c>
       <c r="R42" t="n">
-        <v>7031383</v>
+        <v>7031253</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,6 +5412,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Möjligt gammalt bohål för TTH</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5398,22 +5429,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122964120</v>
+        <v>122959877</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>74854</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5422,43 +5453,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459380</v>
+        <v>459316</v>
       </c>
       <c r="R43" t="n">
-        <v>7031341</v>
+        <v>7031273</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5493,11 +5519,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en gran intill en gammal grovbarkad sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5506,31 +5527,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5547,10 +5543,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122962387</v>
+        <v>122959935</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>74854</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5559,41 +5555,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459409</v>
+        <v>459442</v>
       </c>
       <c r="R44" t="n">
-        <v>7031325</v>
+        <v>7031246</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5620,14 +5625,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>Under gammal björk</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5638,51 +5653,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122974681</v>
+        <v>122958245</v>
       </c>
       <c r="B45" t="n">
-        <v>79883</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5691,41 +5681,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459157</v>
+        <v>459590</v>
       </c>
       <c r="R45" t="n">
-        <v>7031692</v>
+        <v>7031260</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5754,7 +5744,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5764,12 +5754,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5796,10 +5786,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122988619</v>
+        <v>122967565</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5812,42 +5802,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459028</v>
+        <v>459190</v>
       </c>
       <c r="R46" t="n">
-        <v>7031497</v>
+        <v>7031278</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5874,11 +5859,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På lite lutande gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5887,31 +5887,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Gammal tall med grov bark</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122958453</v>
+        <v>122962434</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5924,32 +5919,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5958,13 +5948,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459574</v>
+        <v>459411</v>
       </c>
       <c r="R47" t="n">
-        <v>7031253</v>
+        <v>7031335</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5998,7 +5988,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6017,22 +6007,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6050,10 +6040,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122958335</v>
+        <v>122988597</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6066,39 +6056,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Offerdal, Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459567</v>
+        <v>458852</v>
       </c>
       <c r="R48" t="n">
-        <v>7031253</v>
+        <v>7031387</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6133,11 +6118,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Möjligt gammalt bohål för TTH</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6150,22 +6130,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122988628</v>
+        <v>122988631</v>
       </c>
       <c r="B49" t="n">
-        <v>97319</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6174,25 +6154,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6202,10 +6182,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458859</v>
+        <v>458987</v>
       </c>
       <c r="R49" t="n">
-        <v>7031389</v>
+        <v>7031383</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6264,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122959785</v>
+        <v>122964120</v>
       </c>
       <c r="B50" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6280,34 +6260,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459495</v>
+        <v>459380</v>
       </c>
       <c r="R50" t="n">
-        <v>7031265</v>
+        <v>7031341</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6337,24 +6322,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran 25 cm i diameter</t>
+          <t>Rikligt med lunglav på en gran intill en gammal grovbarkad sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6365,16 +6340,41 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -15164,10 +15164,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122973517</v>
+        <v>122961680</v>
       </c>
       <c r="B127" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15180,37 +15180,51 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>459211</v>
+        <v>459214</v>
       </c>
       <c r="R127" t="n">
-        <v>7031461</v>
+        <v>7031327</v>
       </c>
       <c r="S127" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15250,31 +15264,6 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -15291,10 +15280,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122968503</v>
+        <v>122958966</v>
       </c>
       <c r="B128" t="n">
-        <v>79384</v>
+        <v>77699</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15307,37 +15296,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>228579</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>459372</v>
+        <v>459519</v>
       </c>
       <c r="R128" t="n">
-        <v>7031370</v>
+        <v>7031234</v>
       </c>
       <c r="S128" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15366,7 +15355,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15376,12 +15365,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal barrblandskog</t>
+          <t>På gammal gran 13 cm i diameter</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15396,22 +15385,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122988646</v>
+        <v>122969826</v>
       </c>
       <c r="B129" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15424,34 +15413,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>458844</v>
+        <v>459083</v>
       </c>
       <c r="R129" t="n">
-        <v>7031429</v>
+        <v>7031317</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15481,9 +15470,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15498,22 +15502,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122970354</v>
+        <v>122965408</v>
       </c>
       <c r="B130" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15526,34 +15530,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>459170</v>
+        <v>459226</v>
       </c>
       <c r="R130" t="n">
-        <v>7031379</v>
+        <v>7031188</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15585,7 +15589,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15595,12 +15599,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15615,22 +15619,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122970661</v>
+        <v>122971051</v>
       </c>
       <c r="B131" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15639,41 +15643,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>459099</v>
+        <v>459053</v>
       </c>
       <c r="R131" t="n">
-        <v>7031510</v>
+        <v>7031520</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15702,7 +15706,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15712,12 +15716,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>På gammal sälg och på gran</t>
+          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15744,10 +15748,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122972033</v>
+        <v>122972616</v>
       </c>
       <c r="B132" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15760,16 +15764,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15777,19 +15781,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15798,13 +15793,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>459073</v>
+        <v>459060</v>
       </c>
       <c r="R132" t="n">
-        <v>7031471</v>
+        <v>7031573</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15831,9 +15826,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15848,22 +15858,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122961954</v>
+        <v>122973517</v>
       </c>
       <c r="B133" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15876,47 +15886,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>459411</v>
+        <v>459211</v>
       </c>
       <c r="R133" t="n">
-        <v>7031295</v>
+        <v>7031461</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15948,11 +15948,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15964,7 +15959,27 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15982,10 +15997,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122961680</v>
+        <v>122968503</v>
       </c>
       <c r="B134" t="n">
-        <v>57631</v>
+        <v>79384</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15998,51 +16013,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>459214</v>
+        <v>459372</v>
       </c>
       <c r="R134" t="n">
-        <v>7031327</v>
+        <v>7031370</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16069,9 +16070,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16086,22 +16102,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122971051</v>
+        <v>122988646</v>
       </c>
       <c r="B135" t="n">
-        <v>79882</v>
+        <v>78766</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16110,20 +16126,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -16134,17 +16150,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>459053</v>
+        <v>458844</v>
       </c>
       <c r="R135" t="n">
-        <v>7031520</v>
+        <v>7031429</v>
       </c>
       <c r="S135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16171,24 +16187,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16203,22 +16204,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122973056</v>
+        <v>122970354</v>
       </c>
       <c r="B136" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16231,39 +16232,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>459078</v>
+        <v>459170</v>
       </c>
       <c r="R136" t="n">
-        <v>7031631</v>
+        <v>7031379</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16293,14 +16289,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16315,22 +16321,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122972616</v>
+        <v>122970661</v>
       </c>
       <c r="B137" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16343,39 +16349,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>459060</v>
+        <v>459099</v>
       </c>
       <c r="R137" t="n">
-        <v>7031573</v>
+        <v>7031510</v>
       </c>
       <c r="S137" t="n">
         <v>9</v>
@@ -16407,7 +16408,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16417,12 +16418,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På gammal sälg och på gran</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16442,17 +16443,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122969909</v>
+        <v>122973056</v>
       </c>
       <c r="B138" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16461,52 +16462,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>458792</v>
+        <v>459078</v>
       </c>
       <c r="R138" t="n">
-        <v>7031270</v>
+        <v>7031631</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16539,6 +16531,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16565,10 +16562,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122958966</v>
+        <v>122969909</v>
       </c>
       <c r="B139" t="n">
-        <v>77699</v>
+        <v>56688</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16577,38 +16574,52 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228579</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>459519</v>
+        <v>458792</v>
       </c>
       <c r="R139" t="n">
-        <v>7031234</v>
+        <v>7031270</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16638,24 +16649,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>På gammal gran 13 cm i diameter</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16670,22 +16666,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122969826</v>
+        <v>122972033</v>
       </c>
       <c r="B140" t="n">
-        <v>77699</v>
+        <v>56680</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16698,34 +16694,48 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>459083</v>
+        <v>459073</v>
       </c>
       <c r="R140" t="n">
-        <v>7031317</v>
+        <v>7031471</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16755,24 +16765,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16787,22 +16782,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122965408</v>
+        <v>122961954</v>
       </c>
       <c r="B141" t="n">
-        <v>77699</v>
+        <v>56680</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16815,34 +16810,44 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>459226</v>
+        <v>459411</v>
       </c>
       <c r="R141" t="n">
-        <v>7031188</v>
+        <v>7031295</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16872,24 +16877,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16900,16 +16895,21 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -31146,10 +31146,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122973242</v>
+        <v>122970637</v>
       </c>
       <c r="B268" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -31162,39 +31162,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>459034</v>
+        <v>459026</v>
       </c>
       <c r="R268" t="n">
-        <v>7031669</v>
+        <v>7031279</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31224,14 +31219,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31246,22 +31251,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122973321</v>
+        <v>122988606</v>
       </c>
       <c r="B269" t="n">
-        <v>74863</v>
+        <v>79355</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -31274,34 +31279,34 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>459145</v>
+        <v>458994</v>
       </c>
       <c r="R269" t="n">
-        <v>7031597</v>
+        <v>7031677</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31331,24 +31336,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31363,22 +31353,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122974670</v>
+        <v>122968157</v>
       </c>
       <c r="B270" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -31391,37 +31381,37 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>459150</v>
+        <v>459185</v>
       </c>
       <c r="R270" t="n">
-        <v>7031679</v>
+        <v>7031279</v>
       </c>
       <c r="S270" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -31450,7 +31440,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -31460,12 +31450,12 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31480,22 +31470,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122988662</v>
+        <v>122970502</v>
       </c>
       <c r="B271" t="n">
-        <v>78766</v>
+        <v>79813</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -31504,38 +31494,38 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>459509</v>
+        <v>459119</v>
       </c>
       <c r="R271" t="n">
-        <v>7031229</v>
+        <v>7031386</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31565,9 +31555,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>På gammal sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31582,22 +31587,22 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122988656</v>
+        <v>122960004</v>
       </c>
       <c r="B272" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -31610,37 +31615,37 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>459032</v>
+        <v>459479</v>
       </c>
       <c r="R272" t="n">
-        <v>7031453</v>
+        <v>7031277</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -31667,9 +31672,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 17 cm i diameter</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31684,22 +31704,22 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122961228</v>
+        <v>122973321</v>
       </c>
       <c r="B273" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -31712,34 +31732,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>459379</v>
+        <v>459145</v>
       </c>
       <c r="R273" t="n">
-        <v>7031278</v>
+        <v>7031597</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31771,7 +31791,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -31781,12 +31801,12 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov tallhögstubbe i gammal granskog vid bäck</t>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31801,22 +31821,22 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122970637</v>
+        <v>122974670</v>
       </c>
       <c r="B274" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31829,37 +31849,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>459026</v>
+        <v>459150</v>
       </c>
       <c r="R274" t="n">
-        <v>7031279</v>
+        <v>7031679</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31888,7 +31908,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -31898,12 +31918,12 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -31918,22 +31938,22 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122988606</v>
+        <v>122988662</v>
       </c>
       <c r="B275" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31946,21 +31966,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -31970,10 +31990,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>458994</v>
+        <v>459509</v>
       </c>
       <c r="R275" t="n">
-        <v>7031677</v>
+        <v>7031229</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -32032,10 +32052,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122968157</v>
+        <v>122988656</v>
       </c>
       <c r="B276" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -32048,34 +32068,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>459185</v>
+        <v>459032</v>
       </c>
       <c r="R276" t="n">
-        <v>7031279</v>
+        <v>7031453</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -32105,24 +32125,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -32137,22 +32142,22 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122970502</v>
+        <v>122961228</v>
       </c>
       <c r="B277" t="n">
-        <v>79813</v>
+        <v>79384</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -32161,25 +32166,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>229748</v>
+        <v>6453</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -32189,10 +32194,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>459119</v>
+        <v>459379</v>
       </c>
       <c r="R277" t="n">
-        <v>7031386</v>
+        <v>7031278</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32224,7 +32229,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -32234,12 +32239,12 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>På gammal sälglåga i gammal granskog</t>
+          <t>På kolad ved på gammal grov tallhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -32266,10 +32271,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122960004</v>
+        <v>122973242</v>
       </c>
       <c r="B278" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32282,37 +32287,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>459479</v>
+        <v>459034</v>
       </c>
       <c r="R278" t="n">
-        <v>7031277</v>
+        <v>7031669</v>
       </c>
       <c r="S278" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32339,24 +32349,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>På gammal gran ca 17 cm i diameter</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -32371,12 +32371,12 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -33466,10 +33466,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>123010800</v>
+        <v>123010803</v>
       </c>
       <c r="B288" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -33482,21 +33482,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -33506,10 +33506,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>459400</v>
+        <v>459515</v>
       </c>
       <c r="R288" t="n">
-        <v>7031215</v>
+        <v>7031203</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -33551,7 +33551,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -33578,7 +33578,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>123010803</v>
+        <v>123010814</v>
       </c>
       <c r="B289" t="n">
         <v>77699</v>
@@ -33618,10 +33618,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>459515</v>
+        <v>459557</v>
       </c>
       <c r="R289" t="n">
-        <v>7031203</v>
+        <v>7031212</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -33663,7 +33663,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -33690,10 +33690,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>123010814</v>
+        <v>123010800</v>
       </c>
       <c r="B290" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -33706,21 +33706,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -33730,10 +33730,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>459557</v>
+        <v>459400</v>
       </c>
       <c r="R290" t="n">
-        <v>7031212</v>
+        <v>7031215</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -33765,7 +33765,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -33775,7 +33775,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -34707,10 +34707,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>123010756</v>
+        <v>123010799</v>
       </c>
       <c r="B299" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -34723,21 +34723,21 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -34747,10 +34747,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>459065</v>
+        <v>459399</v>
       </c>
       <c r="R299" t="n">
-        <v>7031224</v>
+        <v>7031218</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34782,7 +34782,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -34792,7 +34792,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -34819,10 +34819,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>123010768</v>
+        <v>123010796</v>
       </c>
       <c r="B300" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -34835,21 +34835,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -34859,10 +34859,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>459060</v>
+        <v>459341</v>
       </c>
       <c r="R300" t="n">
-        <v>7031110</v>
+        <v>7031193</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34931,7 +34931,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>123010801</v>
+        <v>123010756</v>
       </c>
       <c r="B301" t="n">
         <v>78766</v>
@@ -34971,10 +34971,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>459485</v>
+        <v>459065</v>
       </c>
       <c r="R301" t="n">
-        <v>7031184</v>
+        <v>7031224</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -35006,7 +35006,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -35043,10 +35043,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>123010799</v>
+        <v>123010768</v>
       </c>
       <c r="B302" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -35059,21 +35059,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -35083,10 +35083,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>459399</v>
+        <v>459060</v>
       </c>
       <c r="R302" t="n">
-        <v>7031218</v>
+        <v>7031110</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -35118,7 +35118,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -35128,7 +35128,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -35155,10 +35155,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>123010796</v>
+        <v>123010801</v>
       </c>
       <c r="B303" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -35171,21 +35171,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -35195,10 +35195,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>459341</v>
+        <v>459485</v>
       </c>
       <c r="R303" t="n">
-        <v>7031193</v>
+        <v>7031184</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -35267,10 +35267,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>123010786</v>
+        <v>122972997</v>
       </c>
       <c r="B304" t="n">
-        <v>78766</v>
+        <v>78848</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -35283,37 +35283,46 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>459165</v>
+        <v>459111</v>
       </c>
       <c r="R304" t="n">
-        <v>7031178</v>
+        <v>7031582</v>
       </c>
       <c r="S304" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -35342,7 +35351,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -35352,7 +35361,12 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>På döda grenar på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -35363,23 +35377,38 @@
       </c>
       <c r="AG304" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ304" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK304" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO304" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>123010795</v>
+        <v>123010786</v>
       </c>
       <c r="B305" t="n">
         <v>78766</v>
@@ -35419,10 +35448,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>459331</v>
+        <v>459165</v>
       </c>
       <c r="R305" t="n">
-        <v>7031199</v>
+        <v>7031178</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -35454,7 +35483,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -35464,7 +35493,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -35491,7 +35520,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>123010740</v>
+        <v>123010795</v>
       </c>
       <c r="B306" t="n">
         <v>78766</v>
@@ -35531,10 +35560,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>459016</v>
+        <v>459331</v>
       </c>
       <c r="R306" t="n">
-        <v>7031806</v>
+        <v>7031199</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -35566,7 +35595,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -35576,7 +35605,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -35603,7 +35632,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>123010751</v>
+        <v>123010740</v>
       </c>
       <c r="B307" t="n">
         <v>78766</v>
@@ -35643,10 +35672,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>459111</v>
+        <v>459016</v>
       </c>
       <c r="R307" t="n">
-        <v>7031436</v>
+        <v>7031806</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -35678,7 +35707,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -35688,7 +35717,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -35715,7 +35744,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>123010780</v>
+        <v>123010751</v>
       </c>
       <c r="B308" t="n">
         <v>78766</v>
@@ -35755,10 +35784,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>459222</v>
+        <v>459111</v>
       </c>
       <c r="R308" t="n">
-        <v>7031039</v>
+        <v>7031436</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -35790,7 +35819,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -35800,7 +35829,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -35827,10 +35856,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122972997</v>
+        <v>123010780</v>
       </c>
       <c r="B309" t="n">
-        <v>78848</v>
+        <v>78766</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -35843,46 +35872,37 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>459111</v>
+        <v>459222</v>
       </c>
       <c r="R309" t="n">
-        <v>7031582</v>
+        <v>7031039</v>
       </c>
       <c r="S309" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -35911,7 +35931,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -35921,12 +35941,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>På döda grenar på gamla granar i gammal granskog</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -35937,41 +35952,26 @@
       </c>
       <c r="AG309" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ309" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK309" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO309" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122972364</v>
+        <v>122961559</v>
       </c>
       <c r="B310" t="n">
-        <v>97378</v>
+        <v>79847</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -35980,41 +35980,52 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>221063</v>
+        <v>6458</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>458996</v>
+        <v>459334</v>
       </c>
       <c r="R310" t="n">
-        <v>7031467</v>
+        <v>7031154</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -36043,7 +36054,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -36053,12 +36064,12 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>Ca 40 cm upp på sälg</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -36067,43 +36078,29 @@
       <c r="AE310" t="b">
         <v>0</v>
       </c>
+      <c r="AF310" t="inlineStr"/>
       <c r="AG310" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ310" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK310" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO310" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>123010793</v>
+        <v>123010742</v>
       </c>
       <c r="B311" t="n">
-        <v>80743</v>
+        <v>78766</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -36116,21 +36113,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>229436</v>
+        <v>6425</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -36140,10 +36137,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>459331</v>
+        <v>459019</v>
       </c>
       <c r="R311" t="n">
-        <v>7031199</v>
+        <v>7031749</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -36175,7 +36172,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -36185,7 +36182,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -36212,10 +36209,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>123010810</v>
+        <v>123010816</v>
       </c>
       <c r="B312" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -36228,21 +36225,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -36252,10 +36249,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459550</v>
+        <v>459547</v>
       </c>
       <c r="R312" t="n">
-        <v>7031204</v>
+        <v>7031227</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -36287,7 +36284,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -36297,7 +36294,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -36324,7 +36321,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>123010742</v>
+        <v>123010790</v>
       </c>
       <c r="B313" t="n">
         <v>78766</v>
@@ -36364,10 +36361,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>459019</v>
+        <v>459239</v>
       </c>
       <c r="R313" t="n">
-        <v>7031749</v>
+        <v>7031208</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -36399,7 +36396,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -36409,7 +36406,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -36436,10 +36433,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>123010816</v>
+        <v>122972364</v>
       </c>
       <c r="B314" t="n">
-        <v>74863</v>
+        <v>97378</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -36448,38 +36445,38 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6440</v>
+        <v>221063</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>459547</v>
+        <v>458996</v>
       </c>
       <c r="R314" t="n">
-        <v>7031227</v>
+        <v>7031467</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -36511,7 +36508,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -36521,7 +36518,12 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>Ca 40 cm upp på sälg</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -36532,26 +36534,41 @@
       </c>
       <c r="AG314" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>123010790</v>
+        <v>123010793</v>
       </c>
       <c r="B315" t="n">
-        <v>78766</v>
+        <v>80743</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -36564,21 +36581,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6425</v>
+        <v>229436</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -36588,10 +36605,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>459239</v>
+        <v>459331</v>
       </c>
       <c r="R315" t="n">
-        <v>7031208</v>
+        <v>7031199</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -36623,7 +36640,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -36633,7 +36650,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -36660,10 +36677,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122961559</v>
+        <v>123010810</v>
       </c>
       <c r="B316" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -36676,48 +36693,37 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>459334</v>
+        <v>459550</v>
       </c>
       <c r="R316" t="n">
-        <v>7031154</v>
+        <v>7031204</v>
       </c>
       <c r="S316" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -36746,7 +36752,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -36756,12 +36762,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -36770,19 +36771,18 @@
       <c r="AE316" t="b">
         <v>0</v>
       </c>
-      <c r="AF316" t="inlineStr"/>
       <c r="AG316" t="b">
         <v>0</v>
       </c>
       <c r="AT316" t="inlineStr"/>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
@@ -38406,10 +38406,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>123010755</v>
+        <v>123010764</v>
       </c>
       <c r="B331" t="n">
-        <v>90917</v>
+        <v>79848</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -38418,25 +38418,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -38446,10 +38446,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>459139</v>
+        <v>459027</v>
       </c>
       <c r="R331" t="n">
-        <v>7031244</v>
+        <v>7031097</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -38518,10 +38518,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>123010815</v>
+        <v>123010755</v>
       </c>
       <c r="B332" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -38530,25 +38530,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -38558,10 +38558,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>459547</v>
+        <v>459139</v>
       </c>
       <c r="R332" t="n">
-        <v>7031215</v>
+        <v>7031244</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -38593,7 +38593,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -38603,7 +38603,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -38630,10 +38630,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>123015282</v>
+        <v>123010815</v>
       </c>
       <c r="B333" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -38642,45 +38642,38 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>458996</v>
+        <v>459547</v>
       </c>
       <c r="R333" t="n">
-        <v>7031467</v>
+        <v>7031215</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -38712,7 +38705,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -38722,12 +38715,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC333" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg i gammal granskog</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -38736,44 +38724,28 @@
       <c r="AE333" t="b">
         <v>0</v>
       </c>
-      <c r="AF333" t="inlineStr"/>
       <c r="AG333" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ333" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK333" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO333" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>123010764</v>
+        <v>122961603</v>
       </c>
       <c r="B334" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -38786,37 +38758,48 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>459027</v>
+        <v>459333</v>
       </c>
       <c r="R334" t="n">
-        <v>7031097</v>
+        <v>7031154</v>
       </c>
       <c r="S334" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -38845,7 +38828,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -38855,7 +38838,12 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -38864,28 +38852,29 @@
       <c r="AE334" t="b">
         <v>0</v>
       </c>
+      <c r="AF334" t="inlineStr"/>
       <c r="AG334" t="b">
         <v>0</v>
       </c>
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122961603</v>
+        <v>123015282</v>
       </c>
       <c r="B335" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -38894,52 +38883,48 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, Jmt</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>459333</v>
+        <v>458996</v>
       </c>
       <c r="R335" t="n">
-        <v>7031154</v>
+        <v>7031467</v>
       </c>
       <c r="S335" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -38968,7 +38953,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -38978,12 +38963,12 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Rikligt på gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -38996,15 +38981,30 @@
       <c r="AG335" t="b">
         <v>0</v>
       </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO335" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT335" t="inlineStr"/>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
@@ -39479,10 +39479,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>123010792</v>
+        <v>122961873</v>
       </c>
       <c r="B340" t="n">
-        <v>56680</v>
+        <v>74858</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -39495,39 +39495,37 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>102612</v>
+        <v>310</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>459312</v>
+        <v>459357</v>
       </c>
       <c r="R340" t="n">
-        <v>7031201</v>
+        <v>7031297</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -39559,7 +39557,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -39569,7 +39567,12 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -39578,18 +39581,19 @@
       <c r="AE340" t="b">
         <v>0</v>
       </c>
+      <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="b">
         <v>0</v>
       </c>
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
@@ -39932,10 +39936,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122961873</v>
+        <v>123010792</v>
       </c>
       <c r="B344" t="n">
-        <v>74858</v>
+        <v>56680</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -39948,37 +39952,39 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>310</v>
+        <v>102612</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>459357</v>
+        <v>459312</v>
       </c>
       <c r="R344" t="n">
-        <v>7031297</v>
+        <v>7031201</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -40010,7 +40016,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -40020,12 +40026,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC344" t="inlineStr">
-        <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal granskog vid bäck</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -40034,19 +40035,18 @@
       <c r="AE344" t="b">
         <v>0</v>
       </c>
-      <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="b">
         <v>0</v>
       </c>
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -5283,10 +5283,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122965369</v>
+        <v>122988608</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5299,34 +5299,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459220</v>
+        <v>458859</v>
       </c>
       <c r="R43" t="n">
-        <v>7031200</v>
+        <v>7031391</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5356,24 +5356,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122988647</v>
+        <v>122988609</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5416,21 +5401,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5440,10 +5425,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459096</v>
+        <v>458845</v>
       </c>
       <c r="R44" t="n">
-        <v>7031557</v>
+        <v>7031403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5502,10 +5487,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122988662</v>
+        <v>122962434</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5518,37 +5503,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459509</v>
+        <v>459411</v>
       </c>
       <c r="R45" t="n">
-        <v>7031229</v>
+        <v>7031335</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5580,6 +5570,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en liggande levande smal sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5588,26 +5583,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122959894</v>
+        <v>122965369</v>
       </c>
       <c r="B46" t="n">
-        <v>74847</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5616,25 +5636,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5644,10 +5664,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459316</v>
+        <v>459220</v>
       </c>
       <c r="R46" t="n">
-        <v>7031273</v>
+        <v>7031200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,9 +5697,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5694,19 +5729,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122960423</v>
+        <v>122988647</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5742,17 +5777,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459452</v>
+        <v>459096</v>
       </c>
       <c r="R47" t="n">
-        <v>7031305</v>
+        <v>7031557</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5792,48 +5827,23 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122964811</v>
+        <v>122988662</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5869,17 +5879,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459297</v>
+        <v>459509</v>
       </c>
       <c r="R48" t="n">
-        <v>7031211</v>
+        <v>7031229</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5911,11 +5921,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ymnigt med garnlav på många granar.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5924,51 +5929,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122961958</v>
+        <v>122959894</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,43 +5957,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459174</v>
+        <v>459316</v>
       </c>
       <c r="R49" t="n">
-        <v>7031337</v>
+        <v>7031273</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,10 +6047,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122970386</v>
+        <v>122960423</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6088,21 +6063,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6112,13 +6087,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459049</v>
+        <v>459452</v>
       </c>
       <c r="R50" t="n">
-        <v>7031298</v>
+        <v>7031305</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6145,26 +6120,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 20 cm i diameter</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6173,26 +6133,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122971604</v>
+        <v>122964811</v>
       </c>
       <c r="B51" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6201,41 +6186,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458996</v>
+        <v>459297</v>
       </c>
       <c r="R51" t="n">
-        <v>7031467</v>
+        <v>7031211</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6262,24 +6247,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Ymnigt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6290,26 +6265,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122988617</v>
+        <v>122961958</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6322,39 +6322,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459070</v>
+        <v>459174</v>
       </c>
       <c r="R52" t="n">
-        <v>7031592</v>
+        <v>7031337</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6401,22 +6401,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122963067</v>
+        <v>122970386</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6429,39 +6429,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459234</v>
+        <v>459049</v>
       </c>
       <c r="R53" t="n">
-        <v>7031238</v>
+        <v>7031298</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6491,14 +6486,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6513,22 +6518,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122961711</v>
+        <v>122971604</v>
       </c>
       <c r="B54" t="n">
-        <v>56680</v>
+        <v>79875</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6537,48 +6542,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459420</v>
+        <v>458996</v>
       </c>
       <c r="R54" t="n">
-        <v>7031306</v>
+        <v>7031467</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6608,14 +6603,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snön. I flerskiktad gammal granskog.</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6626,31 +6631,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122971421</v>
+        <v>122988617</v>
       </c>
       <c r="B55" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6663,34 +6663,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459019</v>
+        <v>459070</v>
       </c>
       <c r="R55" t="n">
-        <v>7031429</v>
+        <v>7031592</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6720,24 +6725,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 22 cm i diameter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6752,22 +6742,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122988608</v>
+        <v>122963067</v>
       </c>
       <c r="B56" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6780,34 +6770,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458859</v>
+        <v>459234</v>
       </c>
       <c r="R56" t="n">
-        <v>7031391</v>
+        <v>7031238</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6842,6 +6837,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6854,22 +6854,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122988609</v>
+        <v>122961711</v>
       </c>
       <c r="B57" t="n">
-        <v>90952</v>
+        <v>56680</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6882,34 +6882,44 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458845</v>
+        <v>459420</v>
       </c>
       <c r="R57" t="n">
-        <v>7031403</v>
+        <v>7031306</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6944,6 +6954,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snön. I flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6952,26 +6967,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122962434</v>
+        <v>122971421</v>
       </c>
       <c r="B58" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6984,42 +7004,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459411</v>
+        <v>459019</v>
       </c>
       <c r="R58" t="n">
-        <v>7031335</v>
+        <v>7031429</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7046,14 +7061,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>På gammal gran ca 22 cm i diameter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7064,51 +7089,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122959266</v>
+        <v>122961361</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7121,34 +7121,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459462</v>
+        <v>459379</v>
       </c>
       <c r="R59" t="n">
-        <v>7031193</v>
+        <v>7031278</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7178,9 +7178,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov tallhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7195,22 +7210,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122959711</v>
+        <v>122970502</v>
       </c>
       <c r="B60" t="n">
-        <v>74863</v>
+        <v>79813</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7219,41 +7234,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459502</v>
+        <v>459119</v>
       </c>
       <c r="R60" t="n">
-        <v>7031267</v>
+        <v>7031386</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7282,7 +7297,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7292,12 +7307,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På senvuxen gran 10 cm i diameter</t>
+          <t>På gammal sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7312,19 +7327,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122958529</v>
+        <v>122959266</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -7364,13 +7379,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459568</v>
+        <v>459462</v>
       </c>
       <c r="R61" t="n">
-        <v>7031256</v>
+        <v>7031193</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7410,31 +7425,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7451,10 +7441,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122988630</v>
+        <v>122959711</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7467,37 +7457,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459228</v>
+        <v>459502</v>
       </c>
       <c r="R62" t="n">
-        <v>7031281</v>
+        <v>7031267</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7524,9 +7514,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På senvuxen gran 10 cm i diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7541,19 +7546,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122970161</v>
+        <v>122958529</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -7593,13 +7598,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459355</v>
+        <v>459568</v>
       </c>
       <c r="R63" t="n">
-        <v>7031426</v>
+        <v>7031256</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7629,11 +7634,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7685,7 +7685,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122972658</v>
+        <v>122988630</v>
       </c>
       <c r="B64" t="n">
         <v>79847</v>
@@ -7721,14 +7721,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459098</v>
+        <v>459228</v>
       </c>
       <c r="R64" t="n">
-        <v>7031549</v>
+        <v>7031281</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7775,22 +7775,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122970876</v>
+        <v>122970161</v>
       </c>
       <c r="B65" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7803,21 +7803,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459100</v>
+        <v>459355</v>
       </c>
       <c r="R65" t="n">
-        <v>7031235</v>
+        <v>7031426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7865,6 +7865,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7873,6 +7878,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7889,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122988596</v>
+        <v>122972658</v>
       </c>
       <c r="B66" t="n">
-        <v>77709</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7905,34 +7935,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459327</v>
+        <v>459098</v>
       </c>
       <c r="R66" t="n">
-        <v>7031305</v>
+        <v>7031549</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7979,22 +8009,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122969035</v>
+        <v>122970876</v>
       </c>
       <c r="B67" t="n">
-        <v>78411</v>
+        <v>90970</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8007,34 +8037,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459370</v>
+        <v>459100</v>
       </c>
       <c r="R67" t="n">
-        <v>7031370</v>
+        <v>7031235</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8064,24 +8094,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8096,22 +8111,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122958513</v>
+        <v>122988596</v>
       </c>
       <c r="B68" t="n">
-        <v>74849</v>
+        <v>77709</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8120,38 +8135,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459544</v>
+        <v>459327</v>
       </c>
       <c r="R68" t="n">
-        <v>7031238</v>
+        <v>7031305</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8181,26 +8196,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8209,41 +8209,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122988607</v>
+        <v>122969035</v>
       </c>
       <c r="B69" t="n">
-        <v>90952</v>
+        <v>78411</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8256,34 +8241,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458882</v>
+        <v>459370</v>
       </c>
       <c r="R69" t="n">
-        <v>7031377</v>
+        <v>7031370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8313,9 +8298,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8330,22 +8330,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122970650</v>
+        <v>122958513</v>
       </c>
       <c r="B70" t="n">
-        <v>74786</v>
+        <v>74849</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8354,46 +8354,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1460</v>
+        <v>306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459119</v>
+        <v>459544</v>
       </c>
       <c r="R70" t="n">
-        <v>7031393</v>
+        <v>7031238</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8422,7 +8417,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8432,12 +8427,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (40 cm dbh) i gammal granskog</t>
+          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8448,6 +8443,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8464,10 +8474,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122958278</v>
+        <v>122988607</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8480,39 +8490,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459570</v>
+        <v>458882</v>
       </c>
       <c r="R71" t="n">
-        <v>7031254</v>
+        <v>7031377</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8547,11 +8552,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8564,22 +8564,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122972616</v>
+        <v>122970650</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>74786</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8592,42 +8592,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459060</v>
+        <v>459119</v>
       </c>
       <c r="R72" t="n">
-        <v>7031573</v>
+        <v>7031393</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal sälg (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8686,19 +8686,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122968756</v>
+        <v>122958278</v>
       </c>
       <c r="B73" t="n">
         <v>57478</v>
@@ -8734,7 +8734,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458952</v>
+        <v>459570</v>
       </c>
       <c r="R73" t="n">
-        <v>7031223</v>
+        <v>7031254</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8810,10 +8810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122961361</v>
+        <v>122972616</v>
       </c>
       <c r="B74" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8826,37 +8826,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459379</v>
+        <v>459060</v>
       </c>
       <c r="R74" t="n">
-        <v>7031278</v>
+        <v>7031573</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8885,7 +8890,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8895,12 +8900,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov tallhögstubbe i gammal granskog vid bäck</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8915,22 +8920,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122970502</v>
+        <v>122968756</v>
       </c>
       <c r="B75" t="n">
-        <v>79813</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8939,38 +8944,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459119</v>
+        <v>458952</v>
       </c>
       <c r="R75" t="n">
-        <v>7031386</v>
+        <v>7031223</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9000,24 +9010,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gammal sälglåga i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9032,22 +9032,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122960970</v>
+        <v>122968114</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9060,37 +9060,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459435</v>
+        <v>459106</v>
       </c>
       <c r="R76" t="n">
-        <v>7031306</v>
+        <v>7031128</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9122,6 +9127,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9130,31 +9140,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9171,10 +9156,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122959133</v>
+        <v>122988621</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9187,37 +9172,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459510</v>
+        <v>459222</v>
       </c>
       <c r="R77" t="n">
-        <v>7031239</v>
+        <v>7031244</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9244,24 +9234,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gammal gran 15 cm I diameter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9276,22 +9251,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122970354</v>
+        <v>122958335</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9304,34 +9279,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Offerdal, Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459170</v>
+        <v>459567</v>
       </c>
       <c r="R78" t="n">
-        <v>7031379</v>
+        <v>7031253</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9361,24 +9341,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Möjligt gammalt bohål för TTH</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9393,22 +9363,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122988669</v>
+        <v>122960970</v>
       </c>
       <c r="B79" t="n">
-        <v>77694</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9421,37 +9391,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459002</v>
+        <v>459435</v>
       </c>
       <c r="R79" t="n">
-        <v>7031384</v>
+        <v>7031306</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9491,26 +9461,51 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122968592</v>
+        <v>122959133</v>
       </c>
       <c r="B80" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9523,21 +9518,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9547,13 +9542,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459172</v>
+        <v>459510</v>
       </c>
       <c r="R80" t="n">
-        <v>7031415</v>
+        <v>7031239</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9582,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9592,12 +9587,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På svagt lutande gran</t>
+          <t>På gammal gran 15 cm I diameter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9612,22 +9607,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122968114</v>
+        <v>122970354</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9640,39 +9635,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459106</v>
+        <v>459170</v>
       </c>
       <c r="R81" t="n">
-        <v>7031128</v>
+        <v>7031379</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9702,14 +9692,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9724,22 +9724,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122988621</v>
+        <v>122968238</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9752,39 +9752,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459222</v>
+        <v>459187</v>
       </c>
       <c r="R82" t="n">
-        <v>7031244</v>
+        <v>7031280</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9814,9 +9809,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9831,22 +9836,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122958335</v>
+        <v>122974666</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9859,42 +9864,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Offerdal, Sönnestmyren, Offerdal, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459567</v>
+        <v>459159</v>
       </c>
       <c r="R83" t="n">
-        <v>7031253</v>
+        <v>7031681</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9921,14 +9921,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Möjligt gammalt bohål för TTH</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9943,22 +9953,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122968238</v>
+        <v>122988669</v>
       </c>
       <c r="B84" t="n">
-        <v>78766</v>
+        <v>77694</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9971,34 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459187</v>
+        <v>459002</v>
       </c>
       <c r="R84" t="n">
-        <v>7031280</v>
+        <v>7031384</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10028,19 +10038,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10055,22 +10055,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122974666</v>
+        <v>122968592</v>
       </c>
       <c r="B85" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10083,37 +10083,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459159</v>
+        <v>459172</v>
       </c>
       <c r="R85" t="n">
-        <v>7031681</v>
+        <v>7031415</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På svagt lutande gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -18164,10 +18164,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122970637</v>
+        <v>122988619</v>
       </c>
       <c r="B156" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18180,34 +18180,39 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>459026</v>
+        <v>459028</v>
       </c>
       <c r="R156" t="n">
-        <v>7031279</v>
+        <v>7031497</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18237,26 +18242,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -18265,26 +18255,31 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Gammal tall med grov bark</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122958211</v>
+        <v>122969276</v>
       </c>
       <c r="B157" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18297,34 +18292,39 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>459591</v>
+        <v>458861</v>
       </c>
       <c r="R157" t="n">
-        <v>7031255</v>
+        <v>7031270</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18354,24 +18354,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18386,22 +18376,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122961690</v>
+        <v>122988620</v>
       </c>
       <c r="B158" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18414,37 +18404,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>459386</v>
+        <v>459240</v>
       </c>
       <c r="R158" t="n">
-        <v>7031293</v>
+        <v>7031331</v>
       </c>
       <c r="S158" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18471,24 +18466,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 23 cm i diameter</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18503,22 +18483,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122975034</v>
+        <v>122970637</v>
       </c>
       <c r="B159" t="n">
-        <v>78502</v>
+        <v>77699</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18531,34 +18511,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>228579</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>459079</v>
+        <v>459026</v>
       </c>
       <c r="R159" t="n">
-        <v>7031697</v>
+        <v>7031279</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18590,7 +18570,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18600,12 +18580,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18620,22 +18600,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122988661</v>
+        <v>122958211</v>
       </c>
       <c r="B160" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18648,34 +18628,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>458998</v>
+        <v>459591</v>
       </c>
       <c r="R160" t="n">
-        <v>7031366</v>
+        <v>7031255</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18705,9 +18685,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18722,22 +18717,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122988601</v>
+        <v>122961690</v>
       </c>
       <c r="B161" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18750,37 +18745,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>458858</v>
+        <v>459386</v>
       </c>
       <c r="R161" t="n">
-        <v>7031397</v>
+        <v>7031293</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18807,9 +18802,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 23 cm i diameter</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18824,22 +18834,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122962975</v>
+        <v>122975034</v>
       </c>
       <c r="B162" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18852,42 +18862,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>459414</v>
+        <v>459079</v>
       </c>
       <c r="R162" t="n">
-        <v>7031352</v>
+        <v>7031697</v>
       </c>
       <c r="S162" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18914,14 +18919,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
+          <t>På kolad ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18932,51 +18947,26 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122970190</v>
+        <v>122988661</v>
       </c>
       <c r="B163" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18989,37 +18979,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>459221</v>
+        <v>458998</v>
       </c>
       <c r="R163" t="n">
-        <v>7031408</v>
+        <v>7031366</v>
       </c>
       <c r="S163" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19046,24 +19036,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19078,22 +19053,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122960090</v>
+        <v>122988601</v>
       </c>
       <c r="B164" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19106,34 +19081,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>459481</v>
+        <v>458858</v>
       </c>
       <c r="R164" t="n">
-        <v>7031293</v>
+        <v>7031397</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19163,19 +19138,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19190,22 +19155,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122961947</v>
+        <v>122962975</v>
       </c>
       <c r="B165" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19218,26 +19183,27 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1000</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -19246,13 +19212,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>459174</v>
+        <v>459414</v>
       </c>
       <c r="R165" t="n">
-        <v>7031335</v>
+        <v>7031352</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19286,7 +19252,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Garnlavsrikt område</t>
+          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19297,6 +19263,31 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -19313,10 +19304,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122970661</v>
+        <v>122970190</v>
       </c>
       <c r="B166" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19329,21 +19320,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19353,13 +19344,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>459099</v>
+        <v>459221</v>
       </c>
       <c r="R166" t="n">
-        <v>7031510</v>
+        <v>7031408</v>
       </c>
       <c r="S166" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19388,7 +19379,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19398,12 +19389,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>På gammal sälg och på gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19430,10 +19421,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122960215</v>
+        <v>122960090</v>
       </c>
       <c r="B167" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19446,34 +19437,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>459403</v>
+        <v>459481</v>
       </c>
       <c r="R167" t="n">
-        <v>7031251</v>
+        <v>7031293</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19505,7 +19496,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19515,12 +19506,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal sumpgranskog vid bäck</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19535,22 +19521,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122988619</v>
+        <v>122961947</v>
       </c>
       <c r="B168" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19563,39 +19549,38 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1000</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>459028</v>
+        <v>459174</v>
       </c>
       <c r="R168" t="n">
-        <v>7031497</v>
+        <v>7031335</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19630,6 +19615,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt område</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -19638,31 +19628,26 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Gammal tall med grov bark</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122969276</v>
+        <v>122970661</v>
       </c>
       <c r="B169" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19675,42 +19660,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>458861</v>
+        <v>459099</v>
       </c>
       <c r="R169" t="n">
-        <v>7031270</v>
+        <v>7031510</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19737,14 +19717,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg och på gran</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19759,22 +19749,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122988620</v>
+        <v>122960215</v>
       </c>
       <c r="B170" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19787,39 +19777,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>459240</v>
+        <v>459403</v>
       </c>
       <c r="R170" t="n">
-        <v>7031331</v>
+        <v>7031251</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19849,9 +19834,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal sumpgranskog vid bäck</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19866,12 +19866,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -23415,10 +23415,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122960503</v>
+        <v>122959761</v>
       </c>
       <c r="B202" t="n">
-        <v>79022</v>
+        <v>90952</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23427,38 +23427,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>459393</v>
+        <v>459325</v>
       </c>
       <c r="R202" t="n">
-        <v>7031232</v>
+        <v>7031265</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23488,24 +23488,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>På död gren på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23520,22 +23505,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122959373</v>
+        <v>122961785</v>
       </c>
       <c r="B203" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23548,21 +23533,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23572,10 +23557,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>459513</v>
+        <v>459199</v>
       </c>
       <c r="R203" t="n">
-        <v>7031242</v>
+        <v>7031334</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23605,24 +23590,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>På gammal gran 30 cm I diameter</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23637,22 +23607,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122959761</v>
+        <v>122973259</v>
       </c>
       <c r="B204" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23665,34 +23635,39 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>459325</v>
+        <v>459035</v>
       </c>
       <c r="R204" t="n">
-        <v>7031265</v>
+        <v>7031669</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23725,6 +23700,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23751,10 +23731,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122961785</v>
+        <v>122969084</v>
       </c>
       <c r="B205" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23767,34 +23747,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>459199</v>
+        <v>458878</v>
       </c>
       <c r="R205" t="n">
-        <v>7031334</v>
+        <v>7031241</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23827,6 +23812,11 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23853,10 +23843,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122988624</v>
+        <v>122963217</v>
       </c>
       <c r="B206" t="n">
-        <v>91645</v>
+        <v>57478</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23865,38 +23855,43 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>459021</v>
+        <v>459236</v>
       </c>
       <c r="R206" t="n">
-        <v>7031753</v>
+        <v>7031209</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23931,6 +23926,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
@@ -23939,28 +23939,23 @@
       </c>
       <c r="AG206" t="b">
         <v>0</v>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>Klen, knäckt gran.</t>
-        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122973259</v>
+        <v>122968079</v>
       </c>
       <c r="B207" t="n">
         <v>57478</v>
@@ -23996,22 +23991,22 @@
       <c r="I207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>459035</v>
+        <v>459056</v>
       </c>
       <c r="R207" t="n">
-        <v>7031669</v>
+        <v>7031368</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -24038,14 +24033,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24060,22 +24065,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122969084</v>
+        <v>122960503</v>
       </c>
       <c r="B208" t="n">
-        <v>57478</v>
+        <v>79022</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24084,43 +24089,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>458878</v>
+        <v>459393</v>
       </c>
       <c r="R208" t="n">
-        <v>7031241</v>
+        <v>7031232</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24150,14 +24150,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På död gren på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24172,22 +24182,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122963217</v>
+        <v>122959373</v>
       </c>
       <c r="B209" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -24200,39 +24210,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>459236</v>
+        <v>459513</v>
       </c>
       <c r="R209" t="n">
-        <v>7031209</v>
+        <v>7031242</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24262,14 +24267,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran 30 cm I diameter</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24284,22 +24299,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122968079</v>
+        <v>122988624</v>
       </c>
       <c r="B210" t="n">
-        <v>57478</v>
+        <v>91645</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -24308,46 +24323,41 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>459056</v>
+        <v>459021</v>
       </c>
       <c r="R210" t="n">
-        <v>7031368</v>
+        <v>7031753</v>
       </c>
       <c r="S210" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24374,26 +24384,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>På död gran</t>
-        </is>
-      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
@@ -24402,16 +24397,21 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>Klen, knäckt gran.</t>
+        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
@@ -30666,10 +30666,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122958453</v>
+        <v>122988604</v>
       </c>
       <c r="B265" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -30682,44 +30682,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>459574</v>
+        <v>459513</v>
       </c>
       <c r="R265" t="n">
-        <v>7031253</v>
+        <v>7031221</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30754,11 +30744,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD265" t="b">
         <v>0</v>
       </c>
@@ -30767,51 +30752,26 @@
       </c>
       <c r="AG265" t="b">
         <v>0</v>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122988604</v>
+        <v>122968274</v>
       </c>
       <c r="B266" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -30824,37 +30784,37 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>459513</v>
+        <v>459452</v>
       </c>
       <c r="R266" t="n">
-        <v>7031221</v>
+        <v>7031354</v>
       </c>
       <c r="S266" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -30886,6 +30846,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD266" t="b">
         <v>0</v>
       </c>
@@ -30894,26 +30859,51 @@
       </c>
       <c r="AG266" t="b">
         <v>0</v>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122968274</v>
+        <v>122961832</v>
       </c>
       <c r="B267" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -30926,21 +30916,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -30950,13 +30940,13 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>459452</v>
+        <v>459199</v>
       </c>
       <c r="R267" t="n">
-        <v>7031354</v>
+        <v>7031334</v>
       </c>
       <c r="S267" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -30988,11 +30978,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD267" t="b">
         <v>0</v>
       </c>
@@ -31001,31 +30986,6 @@
       </c>
       <c r="AG267" t="b">
         <v>0</v>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
@@ -31042,10 +31002,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122961832</v>
+        <v>122970966</v>
       </c>
       <c r="B268" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -31058,37 +31018,42 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>459199</v>
+        <v>459064</v>
       </c>
       <c r="R268" t="n">
-        <v>7031334</v>
+        <v>7031505</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -31115,9 +31080,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>På nedfallen, gammal sälg</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31132,19 +31112,19 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122970966</v>
+        <v>122964051</v>
       </c>
       <c r="B269" t="n">
         <v>79847</v>
@@ -31180,7 +31160,7 @@
       <c r="I269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
@@ -31189,13 +31169,13 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>459064</v>
+        <v>459393</v>
       </c>
       <c r="R269" t="n">
-        <v>7031505</v>
+        <v>7031334</v>
       </c>
       <c r="S269" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -31222,24 +31202,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>På nedfallen, gammal sälg</t>
+          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31250,23 +31220,48 @@
       </c>
       <c r="AG269" t="b">
         <v>0</v>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122964051</v>
+        <v>122972459</v>
       </c>
       <c r="B270" t="n">
         <v>79847</v>
@@ -31300,24 +31295,19 @@
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>459393</v>
+        <v>459056</v>
       </c>
       <c r="R270" t="n">
-        <v>7031334</v>
+        <v>7031578</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -31344,14 +31334,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
+          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31362,51 +31362,26 @@
       </c>
       <c r="AG270" t="b">
         <v>0</v>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122972459</v>
+        <v>122960216</v>
       </c>
       <c r="B271" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -31419,21 +31394,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -31443,10 +31418,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>459056</v>
+        <v>459482</v>
       </c>
       <c r="R271" t="n">
-        <v>7031578</v>
+        <v>7031303</v>
       </c>
       <c r="S271" t="n">
         <v>9</v>
@@ -31476,24 +31451,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>På nedfallen sälg</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31504,26 +31469,51 @@
       </c>
       <c r="AG271" t="b">
         <v>0</v>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122960216</v>
+        <v>122962699</v>
       </c>
       <c r="B272" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -31532,38 +31522,43 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>459482</v>
+        <v>459414</v>
       </c>
       <c r="R272" t="n">
-        <v>7031303</v>
+        <v>7031347</v>
       </c>
       <c r="S272" t="n">
         <v>9</v>
@@ -31598,11 +31593,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD272" t="b">
         <v>0</v>
       </c>
@@ -31619,22 +31609,22 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT272" t="inlineStr"/>
@@ -31652,10 +31642,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122962699</v>
+        <v>122967503</v>
       </c>
       <c r="B273" t="n">
-        <v>79883</v>
+        <v>74863</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -31664,46 +31654,41 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>459414</v>
+        <v>459227</v>
       </c>
       <c r="R273" t="n">
-        <v>7031347</v>
+        <v>7031245</v>
       </c>
       <c r="S273" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -31730,11 +31715,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 30 cm i diameter</t>
+        </is>
+      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
@@ -31743,51 +31743,26 @@
       </c>
       <c r="AG273" t="b">
         <v>0</v>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122967503</v>
+        <v>122968293</v>
       </c>
       <c r="B274" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31800,21 +31775,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -31824,13 +31799,13 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>459227</v>
+        <v>459120</v>
       </c>
       <c r="R274" t="n">
-        <v>7031245</v>
+        <v>7031399</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31859,7 +31834,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -31869,12 +31844,12 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -31889,22 +31864,22 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122968293</v>
+        <v>122960559</v>
       </c>
       <c r="B275" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31917,37 +31892,51 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>459120</v>
+        <v>459390</v>
       </c>
       <c r="R275" t="n">
-        <v>7031399</v>
+        <v>7031224</v>
       </c>
       <c r="S275" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31976,7 +31965,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -31986,12 +31975,12 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -32011,17 +32000,17 @@
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122960559</v>
+        <v>122958453</v>
       </c>
       <c r="B276" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -32034,36 +32023,32 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
@@ -32072,13 +32057,13 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>459390</v>
+        <v>459574</v>
       </c>
       <c r="R276" t="n">
-        <v>7031224</v>
+        <v>7031253</v>
       </c>
       <c r="S276" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -32105,24 +32090,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -32133,16 +32108,41 @@
       </c>
       <c r="AG276" t="b">
         <v>0</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -34360,10 +34360,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>123010766</v>
+        <v>123010781</v>
       </c>
       <c r="B296" t="n">
-        <v>74847</v>
+        <v>77699</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -34372,25 +34372,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -34400,10 +34400,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>459067</v>
+        <v>459191</v>
       </c>
       <c r="R296" t="n">
-        <v>7031089</v>
+        <v>7031091</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -34445,7 +34445,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -34472,10 +34472,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>123010804</v>
+        <v>123010766</v>
       </c>
       <c r="B297" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -34484,25 +34484,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -34512,10 +34512,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>459515</v>
+        <v>459067</v>
       </c>
       <c r="R297" t="n">
-        <v>7031203</v>
+        <v>7031089</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -34547,7 +34547,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -34557,7 +34557,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -34584,10 +34584,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>123010791</v>
+        <v>123010804</v>
       </c>
       <c r="B298" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -34596,25 +34596,25 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -34624,7 +34624,7 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>459278</v>
+        <v>459515</v>
       </c>
       <c r="R298" t="n">
         <v>7031203</v>
@@ -34659,7 +34659,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -34669,7 +34669,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -34696,10 +34696,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>123010773</v>
+        <v>123010791</v>
       </c>
       <c r="B299" t="n">
-        <v>74863</v>
+        <v>74847</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -34708,25 +34708,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -34736,10 +34736,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>459131</v>
+        <v>459278</v>
       </c>
       <c r="R299" t="n">
-        <v>7031087</v>
+        <v>7031203</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34771,7 +34771,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -34808,10 +34808,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>123010765</v>
+        <v>123010773</v>
       </c>
       <c r="B300" t="n">
-        <v>90952</v>
+        <v>74863</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -34824,21 +34824,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -34848,10 +34848,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>459062</v>
+        <v>459131</v>
       </c>
       <c r="R300" t="n">
-        <v>7031083</v>
+        <v>7031087</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34883,7 +34883,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -34893,7 +34893,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34920,10 +34920,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>123010781</v>
+        <v>123010765</v>
       </c>
       <c r="B301" t="n">
-        <v>77699</v>
+        <v>90952</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -34936,21 +34936,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -34960,10 +34960,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>459191</v>
+        <v>459062</v>
       </c>
       <c r="R301" t="n">
-        <v>7031091</v>
+        <v>7031083</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -34995,7 +34995,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -35005,7 +35005,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -35032,10 +35032,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>123010811</v>
+        <v>123010793</v>
       </c>
       <c r="B302" t="n">
-        <v>74863</v>
+        <v>80743</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -35048,21 +35048,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6440</v>
+        <v>229436</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -35072,10 +35072,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>459550</v>
+        <v>459331</v>
       </c>
       <c r="R302" t="n">
-        <v>7031204</v>
+        <v>7031199</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -35144,10 +35144,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>123010769</v>
+        <v>123010767</v>
       </c>
       <c r="B303" t="n">
-        <v>78766</v>
+        <v>74854</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -35156,25 +35156,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -35184,10 +35184,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>459079</v>
+        <v>459067</v>
       </c>
       <c r="R303" t="n">
-        <v>7031108</v>
+        <v>7031089</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -35219,7 +35219,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -35229,7 +35229,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -35240,6 +35240,21 @@
       </c>
       <c r="AG303" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO303" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
@@ -35256,10 +35271,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>123010767</v>
+        <v>123010811</v>
       </c>
       <c r="B304" t="n">
-        <v>74854</v>
+        <v>74863</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -35268,25 +35283,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -35296,10 +35311,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>459067</v>
+        <v>459550</v>
       </c>
       <c r="R304" t="n">
-        <v>7031089</v>
+        <v>7031204</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -35331,7 +35346,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -35341,7 +35356,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -35352,21 +35367,6 @@
       </c>
       <c r="AG304" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ304" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK304" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO304" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
@@ -35383,10 +35383,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>123010744</v>
+        <v>123010769</v>
       </c>
       <c r="B305" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -35399,39 +35399,34 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>459056</v>
+        <v>459079</v>
       </c>
       <c r="R305" t="n">
-        <v>7031661</v>
+        <v>7031108</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -35463,7 +35458,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -35473,12 +35468,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC305" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -35505,10 +35495,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>123010793</v>
+        <v>123010744</v>
       </c>
       <c r="B306" t="n">
-        <v>80743</v>
+        <v>57478</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -35521,34 +35511,39 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>229436</v>
+        <v>100109</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>459331</v>
+        <v>459056</v>
       </c>
       <c r="R306" t="n">
-        <v>7031199</v>
+        <v>7031661</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -35580,7 +35575,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -35590,7 +35585,12 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -35953,7 +35953,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>123010800</v>
+        <v>123010790</v>
       </c>
       <c r="B310" t="n">
         <v>78766</v>
@@ -35993,10 +35993,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>459400</v>
+        <v>459239</v>
       </c>
       <c r="R310" t="n">
-        <v>7031215</v>
+        <v>7031208</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -36028,7 +36028,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -36038,7 +36038,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -36065,7 +36065,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>123010780</v>
+        <v>123010800</v>
       </c>
       <c r="B311" t="n">
         <v>78766</v>
@@ -36105,10 +36105,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>459222</v>
+        <v>459400</v>
       </c>
       <c r="R311" t="n">
-        <v>7031039</v>
+        <v>7031215</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -36140,7 +36140,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -36177,7 +36177,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>123010795</v>
+        <v>123010780</v>
       </c>
       <c r="B312" t="n">
         <v>78766</v>
@@ -36217,10 +36217,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459331</v>
+        <v>459222</v>
       </c>
       <c r="R312" t="n">
-        <v>7031199</v>
+        <v>7031039</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -36252,7 +36252,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -36262,7 +36262,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -36289,7 +36289,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>123010790</v>
+        <v>123010795</v>
       </c>
       <c r="B313" t="n">
         <v>78766</v>
@@ -36329,10 +36329,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>459239</v>
+        <v>459331</v>
       </c>
       <c r="R313" t="n">
-        <v>7031208</v>
+        <v>7031199</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -36364,7 +36364,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -36899,10 +36899,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>123012467</v>
+        <v>123010803</v>
       </c>
       <c r="B318" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -36911,44 +36911,41 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>459017</v>
+        <v>459515</v>
       </c>
       <c r="R318" t="n">
-        <v>7031714</v>
+        <v>7031203</v>
       </c>
       <c r="S318" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -36975,35 +36972,29 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA318" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AD318" t="b">
         <v>0</v>
       </c>
       <c r="AE318" t="b">
         <v>0</v>
       </c>
-      <c r="AF318" t="inlineStr"/>
       <c r="AG318" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ318" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK318" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO318" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
@@ -37020,10 +37011,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>123010755</v>
+        <v>123012467</v>
       </c>
       <c r="B319" t="n">
-        <v>90917</v>
+        <v>79751</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -37036,37 +37027,40 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>459139</v>
+        <v>459017</v>
       </c>
       <c r="R319" t="n">
-        <v>7031244</v>
+        <v>7031714</v>
       </c>
       <c r="S319" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -37093,29 +37087,35 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD319" t="b">
         <v>0</v>
       </c>
       <c r="AE319" t="b">
         <v>0</v>
       </c>
+      <c r="AF319" t="inlineStr"/>
       <c r="AG319" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
@@ -37132,10 +37132,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>123010803</v>
+        <v>123010755</v>
       </c>
       <c r="B320" t="n">
-        <v>77699</v>
+        <v>90917</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -37144,25 +37144,25 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
@@ -37172,10 +37172,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>459515</v>
+        <v>459139</v>
       </c>
       <c r="R320" t="n">
-        <v>7031203</v>
+        <v>7031244</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -37207,7 +37207,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -37244,10 +37244,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>123010788</v>
+        <v>123010756</v>
       </c>
       <c r="B321" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -37260,21 +37260,21 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
@@ -37284,10 +37284,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>459229</v>
+        <v>459065</v>
       </c>
       <c r="R321" t="n">
-        <v>7031215</v>
+        <v>7031224</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -37319,7 +37319,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -37329,7 +37329,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -37340,21 +37340,6 @@
       </c>
       <c r="AG321" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ321" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK321" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO321" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
@@ -37364,14 +37349,14 @@
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>123010756</v>
+        <v>123010779</v>
       </c>
       <c r="B322" t="n">
         <v>78766</v>
@@ -37411,10 +37396,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>459065</v>
+        <v>459170</v>
       </c>
       <c r="R322" t="n">
-        <v>7031224</v>
+        <v>7031086</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -37446,7 +37431,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -37456,7 +37441,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -37483,10 +37468,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>123010779</v>
+        <v>123010770</v>
       </c>
       <c r="B323" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -37499,21 +37484,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -37523,10 +37508,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>459170</v>
+        <v>459079</v>
       </c>
       <c r="R323" t="n">
-        <v>7031086</v>
+        <v>7031108</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -37558,7 +37543,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -37568,7 +37553,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -37595,10 +37580,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>123010770</v>
+        <v>123010788</v>
       </c>
       <c r="B324" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -37611,21 +37596,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -37635,10 +37620,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>459079</v>
+        <v>459229</v>
       </c>
       <c r="R324" t="n">
-        <v>7031108</v>
+        <v>7031215</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -37670,7 +37655,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -37680,7 +37665,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -37691,6 +37676,21 @@
       </c>
       <c r="AG324" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
@@ -37700,7 +37700,7 @@
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
@@ -38545,10 +38545,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122962441</v>
+        <v>123010740</v>
       </c>
       <c r="B332" t="n">
-        <v>91890</v>
+        <v>78766</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -38557,45 +38557,38 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>459345</v>
+        <v>459016</v>
       </c>
       <c r="R332" t="n">
-        <v>7031322</v>
+        <v>7031806</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -38627,7 +38620,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -38637,12 +38630,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>På marken längs med bäck, gamla fruktkroppar från hösten 2024</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -38651,29 +38639,28 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122961873</v>
+        <v>122962441</v>
       </c>
       <c r="B333" t="n">
-        <v>74858</v>
+        <v>91890</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -38682,41 +38669,45 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>310</v>
+        <v>4769</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>459357</v>
+        <v>459345</v>
       </c>
       <c r="R333" t="n">
-        <v>7031297</v>
+        <v>7031322</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -38748,7 +38739,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -38758,12 +38749,12 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal granskog vid bäck</t>
+          <t>På marken längs med bäck, gamla fruktkroppar från hösten 2024</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -38791,10 +38782,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>123010740</v>
+        <v>122961873</v>
       </c>
       <c r="B334" t="n">
-        <v>78766</v>
+        <v>74858</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -38807,34 +38798,37 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>459016</v>
+        <v>459357</v>
       </c>
       <c r="R334" t="n">
-        <v>7031806</v>
+        <v>7031297</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -38866,7 +38860,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -38876,7 +38870,12 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -38885,18 +38884,19 @@
       <c r="AE334" t="b">
         <v>0</v>
       </c>
+      <c r="AF334" t="inlineStr"/>
       <c r="AG334" t="b">
         <v>0</v>
       </c>
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -3501,10 +3501,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122967741</v>
+        <v>122974179</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3517,46 +3517,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459127</v>
+        <v>459242</v>
       </c>
       <c r="R27" t="n">
-        <v>7031301</v>
+        <v>7031483</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3583,24 +3579,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,26 +3597,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122974179</v>
+        <v>122961564</v>
       </c>
       <c r="B28" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3643,42 +3654,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459242</v>
+        <v>459425</v>
       </c>
       <c r="R28" t="n">
-        <v>7031483</v>
+        <v>7031306</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3712,7 +3723,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>Fertil garnlav i gammal granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,27 +3737,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3764,7 +3775,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122961564</v>
+        <v>122967741</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3797,10 +3808,14 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3809,13 +3824,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459425</v>
+        <v>459127</v>
       </c>
       <c r="R29" t="n">
-        <v>7031306</v>
+        <v>7031301</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3842,14 +3857,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Fertil garnlav i gammal granskog.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,41 +3885,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -14241,10 +14241,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122973380</v>
+        <v>122962195</v>
       </c>
       <c r="B122" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14257,37 +14257,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>458999</v>
+        <v>459158</v>
       </c>
       <c r="R122" t="n">
-        <v>7031647</v>
+        <v>7031220</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14314,9 +14319,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14331,22 +14351,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122959601</v>
+        <v>122973380</v>
       </c>
       <c r="B123" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14359,34 +14379,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>459390</v>
+        <v>458999</v>
       </c>
       <c r="R123" t="n">
-        <v>7031232</v>
+        <v>7031647</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14445,10 +14465,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122988646</v>
+        <v>122959601</v>
       </c>
       <c r="B124" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14461,34 +14481,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458844</v>
+        <v>459390</v>
       </c>
       <c r="R124" t="n">
-        <v>7031429</v>
+        <v>7031232</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14535,22 +14555,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122962307</v>
+        <v>122972105</v>
       </c>
       <c r="B125" t="n">
-        <v>79883</v>
+        <v>56688</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14563,27 +14583,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14592,13 +14622,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>459411</v>
+        <v>459267</v>
       </c>
       <c r="R125" t="n">
-        <v>7031338</v>
+        <v>7031413</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14632,7 +14662,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>Gott om spillning (uppåt ca 1x7 cm) på ca 7 m2 yta under en tall med utglesad krona med tydliga tecken på tjäderns födosök.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14646,27 +14676,7 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14684,7 +14694,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122968238</v>
+        <v>122988646</v>
       </c>
       <c r="B126" t="n">
         <v>78766</v>
@@ -14720,14 +14730,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>459187</v>
+        <v>458844</v>
       </c>
       <c r="R126" t="n">
-        <v>7031280</v>
+        <v>7031429</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14757,19 +14767,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14784,22 +14784,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122958529</v>
+        <v>122962307</v>
       </c>
       <c r="B127" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14808,41 +14808,46 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>459568</v>
+        <v>459411</v>
       </c>
       <c r="R127" t="n">
-        <v>7031256</v>
+        <v>7031338</v>
       </c>
       <c r="S127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14874,6 +14879,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>På en liggande levande smal sälg.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -14890,22 +14900,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14923,10 +14933,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122988631</v>
+        <v>122968238</v>
       </c>
       <c r="B128" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14939,34 +14949,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458987</v>
+        <v>459187</v>
       </c>
       <c r="R128" t="n">
-        <v>7031383</v>
+        <v>7031280</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14996,9 +15006,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15013,19 +15033,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122972416</v>
+        <v>122958529</v>
       </c>
       <c r="B129" t="n">
         <v>78766</v>
@@ -15065,13 +15085,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>459239</v>
+        <v>459568</v>
       </c>
       <c r="R129" t="n">
-        <v>7031397</v>
+        <v>7031256</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15101,11 +15121,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Gott om bålar på många granar.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15157,10 +15172,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122972105</v>
+        <v>122988631</v>
       </c>
       <c r="B130" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15169,56 +15184,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>459267</v>
+        <v>458987</v>
       </c>
       <c r="R130" t="n">
-        <v>7031413</v>
+        <v>7031383</v>
       </c>
       <c r="S130" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15250,11 +15250,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Gott om spillning (uppåt ca 1x7 cm) på ca 7 m2 yta under en tall med utglesad krona med tydliga tecken på tjäderns födosök.</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -15263,31 +15258,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122962195</v>
+        <v>122972416</v>
       </c>
       <c r="B131" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15300,42 +15290,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>459158</v>
+        <v>459239</v>
       </c>
       <c r="R131" t="n">
-        <v>7031220</v>
+        <v>7031397</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15362,24 +15347,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Gott om bålar på många granar.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15390,16 +15365,41 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -17203,10 +17203,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122973242</v>
+        <v>122968592</v>
       </c>
       <c r="B148" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17219,42 +17219,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>459034</v>
+        <v>459172</v>
       </c>
       <c r="R148" t="n">
-        <v>7031669</v>
+        <v>7031415</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17281,14 +17276,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På svagt lutande gran</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17303,22 +17308,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122968592</v>
+        <v>122962442</v>
       </c>
       <c r="B149" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17331,21 +17336,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17355,13 +17360,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>459172</v>
+        <v>459349</v>
       </c>
       <c r="R149" t="n">
-        <v>7031415</v>
+        <v>7031335</v>
       </c>
       <c r="S149" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17390,7 +17395,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17400,12 +17405,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>På svagt lutande gran</t>
+          <t>På gammal gran ca 25 cm i diameter intill bäck</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17420,22 +17425,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122962442</v>
+        <v>122973517</v>
       </c>
       <c r="B150" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17448,21 +17453,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17472,13 +17477,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>459349</v>
+        <v>459211</v>
       </c>
       <c r="R150" t="n">
-        <v>7031335</v>
+        <v>7031461</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17505,26 +17510,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 25 cm i diameter intill bäck</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -17533,26 +17523,51 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122973517</v>
+        <v>122960503</v>
       </c>
       <c r="B151" t="n">
-        <v>78766</v>
+        <v>79022</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17561,41 +17576,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>459211</v>
+        <v>459393</v>
       </c>
       <c r="R151" t="n">
-        <v>7031461</v>
+        <v>7031232</v>
       </c>
       <c r="S151" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17622,11 +17637,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På död gren på gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -17635,51 +17665,26 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122960503</v>
+        <v>122961591</v>
       </c>
       <c r="B152" t="n">
-        <v>79022</v>
+        <v>78766</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17688,38 +17693,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>459393</v>
+        <v>459379</v>
       </c>
       <c r="R152" t="n">
-        <v>7031232</v>
+        <v>7031278</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17751,7 +17756,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17761,12 +17766,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17793,10 +17798,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122961591</v>
+        <v>122959711</v>
       </c>
       <c r="B153" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17809,37 +17814,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>459379</v>
+        <v>459502</v>
       </c>
       <c r="R153" t="n">
-        <v>7031278</v>
+        <v>7031267</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17868,7 +17873,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17878,12 +17883,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog vid bäck</t>
+          <t>På senvuxen gran 10 cm i diameter</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17898,19 +17903,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122959711</v>
+        <v>122969870</v>
       </c>
       <c r="B154" t="n">
         <v>74863</v>
@@ -17950,13 +17955,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>459502</v>
+        <v>459089</v>
       </c>
       <c r="R154" t="n">
-        <v>7031267</v>
+        <v>7031327</v>
       </c>
       <c r="S154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17985,7 +17990,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17995,12 +18000,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På senvuxen gran 10 cm i diameter</t>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18027,10 +18032,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122969870</v>
+        <v>122973126</v>
       </c>
       <c r="B155" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18043,34 +18048,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>459089</v>
+        <v>459081</v>
       </c>
       <c r="R155" t="n">
-        <v>7031327</v>
+        <v>7031628</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18100,24 +18105,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18132,22 +18122,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122973126</v>
+        <v>122961713</v>
       </c>
       <c r="B156" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18160,37 +18150,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>459081</v>
+        <v>459384</v>
       </c>
       <c r="R156" t="n">
-        <v>7031628</v>
+        <v>7031293</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18217,9 +18207,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 23 cm i diameter</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18234,22 +18239,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122961713</v>
+        <v>122968031</v>
       </c>
       <c r="B157" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18262,37 +18267,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>459384</v>
+        <v>459187</v>
       </c>
       <c r="R157" t="n">
-        <v>7031293</v>
+        <v>7031105</v>
       </c>
       <c r="S157" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18319,24 +18329,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 23 cm i diameter</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18351,22 +18346,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122968031</v>
+        <v>122973242</v>
       </c>
       <c r="B158" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18379,39 +18374,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>459187</v>
+        <v>459034</v>
       </c>
       <c r="R158" t="n">
-        <v>7031105</v>
+        <v>7031669</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18444,6 +18439,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18470,10 +18470,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122962736</v>
+        <v>122962434</v>
       </c>
       <c r="B159" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18482,41 +18482,46 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>459417</v>
+        <v>459411</v>
       </c>
       <c r="R159" t="n">
-        <v>7031346</v>
+        <v>7031335</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18546,6 +18551,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18597,10 +18607,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122970190</v>
+        <v>122988624</v>
       </c>
       <c r="B160" t="n">
-        <v>74863</v>
+        <v>91645</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18609,41 +18619,41 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>459221</v>
+        <v>459021</v>
       </c>
       <c r="R160" t="n">
-        <v>7031408</v>
+        <v>7031753</v>
       </c>
       <c r="S160" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18670,26 +18680,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -18698,26 +18693,31 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Klen, knäckt gran.</t>
+        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122959489</v>
+        <v>122960642</v>
       </c>
       <c r="B161" t="n">
-        <v>78766</v>
+        <v>80723</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18730,34 +18730,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>459522</v>
+        <v>459396</v>
       </c>
       <c r="R161" t="n">
-        <v>7031236</v>
+        <v>7031227</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18789,7 +18789,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18799,12 +18799,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ett femtiotal bålar på ett tiotal granar inom 5 m radie</t>
+          <t>På lucker ved på gammal dimensionsavverkningsstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18819,22 +18819,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122988600</v>
+        <v>122962736</v>
       </c>
       <c r="B162" t="n">
-        <v>74863</v>
+        <v>79882</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18843,41 +18843,41 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>459372</v>
+        <v>459417</v>
       </c>
       <c r="R162" t="n">
-        <v>7031245</v>
+        <v>7031346</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18917,26 +18917,51 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122972658</v>
+        <v>122988598</v>
       </c>
       <c r="B163" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18949,34 +18974,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>459098</v>
+        <v>459410</v>
       </c>
       <c r="R163" t="n">
-        <v>7031549</v>
+        <v>7031233</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19023,22 +19048,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122959890</v>
+        <v>122967371</v>
       </c>
       <c r="B164" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19051,37 +19076,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>459505</v>
+        <v>459315</v>
       </c>
       <c r="R164" t="n">
-        <v>7031278</v>
+        <v>7031164</v>
       </c>
       <c r="S164" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19108,11 +19133,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -19121,51 +19161,26 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122973351</v>
+        <v>122970190</v>
       </c>
       <c r="B165" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19178,42 +19193,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>459019</v>
+        <v>459221</v>
       </c>
       <c r="R165" t="n">
-        <v>7031671</v>
+        <v>7031408</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19240,14 +19250,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19262,22 +19282,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122958910</v>
+        <v>122959489</v>
       </c>
       <c r="B166" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19290,39 +19310,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>459496</v>
+        <v>459522</v>
       </c>
       <c r="R166" t="n">
-        <v>7031207</v>
+        <v>7031236</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19352,14 +19367,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ett femtiotal bålar på ett tiotal granar inom 5 m radie</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19374,22 +19399,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122958453</v>
+        <v>122988600</v>
       </c>
       <c r="B167" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19402,44 +19427,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>459574</v>
+        <v>459372</v>
       </c>
       <c r="R167" t="n">
-        <v>7031253</v>
+        <v>7031245</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19474,11 +19489,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -19487,51 +19497,26 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122960004</v>
+        <v>122972658</v>
       </c>
       <c r="B168" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19544,37 +19529,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>459479</v>
+        <v>459098</v>
       </c>
       <c r="R168" t="n">
-        <v>7031277</v>
+        <v>7031549</v>
       </c>
       <c r="S168" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19601,24 +19586,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 17 cm i diameter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19633,22 +19603,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122988633</v>
+        <v>122959890</v>
       </c>
       <c r="B169" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19661,37 +19631,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>459572</v>
+        <v>459505</v>
       </c>
       <c r="R169" t="n">
-        <v>7031236</v>
+        <v>7031278</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19731,26 +19701,51 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122967515</v>
+        <v>122973351</v>
       </c>
       <c r="B170" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19763,37 +19758,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>459212</v>
+        <v>459019</v>
       </c>
       <c r="R170" t="n">
-        <v>7031247</v>
+        <v>7031671</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19820,24 +19820,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19852,22 +19842,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122988598</v>
+        <v>122958910</v>
       </c>
       <c r="B171" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19880,34 +19870,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>459410</v>
+        <v>459496</v>
       </c>
       <c r="R171" t="n">
-        <v>7031233</v>
+        <v>7031207</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19942,6 +19937,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
@@ -19954,22 +19954,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122967371</v>
+        <v>122958453</v>
       </c>
       <c r="B172" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19982,34 +19982,44 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>459315</v>
+        <v>459574</v>
       </c>
       <c r="R172" t="n">
-        <v>7031164</v>
+        <v>7031253</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20039,24 +20049,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20067,16 +20067,41 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
@@ -20185,10 +20210,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122962434</v>
+        <v>122960004</v>
       </c>
       <c r="B174" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20201,42 +20226,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>459411</v>
+        <v>459479</v>
       </c>
       <c r="R174" t="n">
-        <v>7031335</v>
+        <v>7031277</v>
       </c>
       <c r="S174" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20263,14 +20283,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>På gammal gran ca 17 cm i diameter</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20281,51 +20311,26 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122988624</v>
+        <v>122988633</v>
       </c>
       <c r="B175" t="n">
-        <v>91645</v>
+        <v>77699</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20334,25 +20339,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>67</v>
+        <v>228579</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20362,10 +20367,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>459021</v>
+        <v>459572</v>
       </c>
       <c r="R175" t="n">
-        <v>7031753</v>
+        <v>7031236</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20408,11 +20413,6 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Klen, knäckt gran.</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
@@ -20429,10 +20429,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122960642</v>
+        <v>122967515</v>
       </c>
       <c r="B176" t="n">
-        <v>80723</v>
+        <v>77699</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20445,16 +20445,16 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1049</v>
+        <v>228579</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -20465,17 +20465,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>459396</v>
+        <v>459212</v>
       </c>
       <c r="R176" t="n">
-        <v>7031227</v>
+        <v>7031247</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20514,12 +20514,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>På lucker ved på gammal dimensionsavverkningsstubbe i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20534,22 +20534,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122969826</v>
+        <v>122959761</v>
       </c>
       <c r="B177" t="n">
-        <v>77699</v>
+        <v>90952</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20562,21 +20562,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20586,10 +20586,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>459083</v>
+        <v>459325</v>
       </c>
       <c r="R177" t="n">
-        <v>7031317</v>
+        <v>7031265</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20619,24 +20619,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20651,22 +20636,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122965408</v>
+        <v>122963121</v>
       </c>
       <c r="B178" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20679,37 +20664,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>459226</v>
+        <v>459427</v>
       </c>
       <c r="R178" t="n">
-        <v>7031188</v>
+        <v>7031349</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20736,24 +20726,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På en yngre gran intill en gammal sälg med skrovellav.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20764,26 +20744,51 @@
       </c>
       <c r="AG178" t="b">
         <v>0</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122959761</v>
+        <v>122960559</v>
       </c>
       <c r="B179" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20796,37 +20801,51 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>459325</v>
+        <v>459390</v>
       </c>
       <c r="R179" t="n">
-        <v>7031265</v>
+        <v>7031224</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20853,9 +20872,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20870,22 +20904,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122963121</v>
+        <v>122975225</v>
       </c>
       <c r="B180" t="n">
-        <v>79848</v>
+        <v>79236</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20898,42 +20932,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2081</v>
+        <v>1797</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>459427</v>
+        <v>459052</v>
       </c>
       <c r="R180" t="n">
-        <v>7031349</v>
+        <v>7031667</v>
       </c>
       <c r="S180" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20960,14 +20989,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>På en yngre gran intill en gammal sälg med skrovellav.</t>
+          <t>På bark på stam av levande gammal gran, vid basen,  i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20978,51 +21017,26 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122960559</v>
+        <v>122962973</v>
       </c>
       <c r="B181" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21035,36 +21049,31 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -21073,13 +21082,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>459390</v>
+        <v>459220</v>
       </c>
       <c r="R181" t="n">
-        <v>7031224</v>
+        <v>7031245</v>
       </c>
       <c r="S181" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21106,24 +21115,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21138,22 +21137,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122975225</v>
+        <v>122962387</v>
       </c>
       <c r="B182" t="n">
-        <v>79236</v>
+        <v>79847</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21166,37 +21165,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1797</v>
+        <v>6458</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>459052</v>
+        <v>459409</v>
       </c>
       <c r="R182" t="n">
-        <v>7031667</v>
+        <v>7031325</v>
       </c>
       <c r="S182" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21223,24 +21222,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran, vid basen,  i gammal granskog vid bäck</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21251,23 +21240,48 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122962973</v>
+        <v>122988642</v>
       </c>
       <c r="B183" t="n">
         <v>78766</v>
@@ -21300,26 +21314,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>459220</v>
+        <v>458897</v>
       </c>
       <c r="R183" t="n">
-        <v>7031245</v>
+        <v>7031354</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21354,11 +21359,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
-        </is>
-      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
@@ -21371,22 +21371,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122962387</v>
+        <v>122959207</v>
       </c>
       <c r="B184" t="n">
-        <v>79847</v>
+        <v>74675</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21395,41 +21395,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>459409</v>
+        <v>459497</v>
       </c>
       <c r="R184" t="n">
-        <v>7031325</v>
+        <v>7031235</v>
       </c>
       <c r="S184" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21456,14 +21456,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>På ved på gren på gammal gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21474,48 +21484,23 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122988642</v>
+        <v>122967256</v>
       </c>
       <c r="B185" t="n">
         <v>78766</v>
@@ -21551,14 +21536,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>458897</v>
+        <v>459232</v>
       </c>
       <c r="R185" t="n">
-        <v>7031354</v>
+        <v>7031241</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21588,9 +21573,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21605,22 +21600,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122959207</v>
+        <v>122972586</v>
       </c>
       <c r="B186" t="n">
-        <v>74675</v>
+        <v>78766</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21629,38 +21624,42 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>459497</v>
+        <v>459094</v>
       </c>
       <c r="R186" t="n">
-        <v>7031235</v>
+        <v>7031545</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21690,24 +21689,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>På ved på gren på gammal gran i gammal granskog vid bäck</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21722,19 +21711,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122967256</v>
+        <v>122970708</v>
       </c>
       <c r="B187" t="n">
         <v>78766</v>
@@ -21774,10 +21763,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>459232</v>
+        <v>459331</v>
       </c>
       <c r="R187" t="n">
-        <v>7031241</v>
+        <v>7031363</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21807,19 +21796,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Relativt gott om långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21830,26 +21814,51 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122972586</v>
+        <v>122969276</v>
       </c>
       <c r="B188" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21862,38 +21871,39 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1000</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>459094</v>
+        <v>458861</v>
       </c>
       <c r="R188" t="n">
-        <v>7031545</v>
+        <v>7031270</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21930,7 +21940,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21957,10 +21967,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122970708</v>
+        <v>122961536</v>
       </c>
       <c r="B189" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21973,34 +21983,39 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>459331</v>
+        <v>459209</v>
       </c>
       <c r="R189" t="n">
-        <v>7031363</v>
+        <v>7031350</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22037,7 +22052,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Relativt gott om långväxta bålar på flera granar.</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22048,31 +22063,6 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
@@ -22089,10 +22079,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122969276</v>
+        <v>122969826</v>
       </c>
       <c r="B190" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -22105,39 +22095,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>458861</v>
+        <v>459083</v>
       </c>
       <c r="R190" t="n">
-        <v>7031270</v>
+        <v>7031317</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22167,14 +22152,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22189,22 +22184,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122961536</v>
+        <v>122965408</v>
       </c>
       <c r="B191" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22217,39 +22212,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>459209</v>
+        <v>459226</v>
       </c>
       <c r="R191" t="n">
-        <v>7031350</v>
+        <v>7031188</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22279,14 +22269,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22301,12 +22301,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -28135,10 +28135,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122967565</v>
+        <v>122968241</v>
       </c>
       <c r="B242" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -28151,21 +28151,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -28175,13 +28175,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>459190</v>
+        <v>459060</v>
       </c>
       <c r="R242" t="n">
-        <v>7031278</v>
+        <v>7031144</v>
       </c>
       <c r="S242" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -28208,24 +28208,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>På lite lutande gran</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28240,22 +28230,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122988626</v>
+        <v>122960970</v>
       </c>
       <c r="B243" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -28268,37 +28258,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>459229</v>
+        <v>459435</v>
       </c>
       <c r="R243" t="n">
-        <v>7031286</v>
+        <v>7031306</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -28338,26 +28328,51 @@
       </c>
       <c r="AG243" t="b">
         <v>0</v>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122960794</v>
+        <v>122988661</v>
       </c>
       <c r="B244" t="n">
-        <v>95911</v>
+        <v>78766</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -28370,34 +28385,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>459259</v>
+        <v>458998</v>
       </c>
       <c r="R244" t="n">
-        <v>7031322</v>
+        <v>7031366</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28444,22 +28459,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122968241</v>
+        <v>122988650</v>
       </c>
       <c r="B245" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -28472,34 +28487,34 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>459060</v>
+        <v>459321</v>
       </c>
       <c r="R245" t="n">
-        <v>7031144</v>
+        <v>7031305</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28534,11 +28549,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD245" t="b">
         <v>0</v>
       </c>
@@ -28551,22 +28561,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122960970</v>
+        <v>122971788</v>
       </c>
       <c r="B246" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28579,37 +28589,42 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>459435</v>
+        <v>459134</v>
       </c>
       <c r="R246" t="n">
-        <v>7031306</v>
+        <v>7031417</v>
       </c>
       <c r="S246" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28641,6 +28656,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28649,31 +28669,6 @@
       </c>
       <c r="AG246" t="b">
         <v>0</v>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
@@ -28690,10 +28685,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122988661</v>
+        <v>122988621</v>
       </c>
       <c r="B247" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28706,34 +28701,39 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>458998</v>
+        <v>459222</v>
       </c>
       <c r="R247" t="n">
-        <v>7031366</v>
+        <v>7031244</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28792,10 +28792,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122988650</v>
+        <v>122961711</v>
       </c>
       <c r="B248" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28808,34 +28808,44 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>459321</v>
+        <v>459420</v>
       </c>
       <c r="R248" t="n">
-        <v>7031305</v>
+        <v>7031306</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28870,6 +28880,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snön. I flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
@@ -28878,26 +28893,31 @@
       </c>
       <c r="AG248" t="b">
         <v>0</v>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122971788</v>
+        <v>122967565</v>
       </c>
       <c r="B249" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28910,42 +28930,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>459134</v>
+        <v>459190</v>
       </c>
       <c r="R249" t="n">
-        <v>7031417</v>
+        <v>7031278</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28972,14 +28987,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På lite lutande gran</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28994,22 +29019,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122988621</v>
+        <v>122988626</v>
       </c>
       <c r="B250" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -29022,39 +29047,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>459222</v>
+        <v>459229</v>
       </c>
       <c r="R250" t="n">
-        <v>7031244</v>
+        <v>7031286</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29113,10 +29133,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122961711</v>
+        <v>122960794</v>
       </c>
       <c r="B251" t="n">
-        <v>56680</v>
+        <v>95911</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -29129,44 +29149,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>459420</v>
+        <v>459259</v>
       </c>
       <c r="R251" t="n">
-        <v>7031306</v>
+        <v>7031322</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29201,11 +29211,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snön. I flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD251" t="b">
         <v>0</v>
       </c>
@@ -29214,11 +29219,6 @@
       </c>
       <c r="AG251" t="b">
         <v>0</v>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
@@ -29352,10 +29352,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122988604</v>
+        <v>122961313</v>
       </c>
       <c r="B253" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -29368,37 +29368,37 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>459513</v>
+        <v>459398</v>
       </c>
       <c r="R253" t="n">
-        <v>7031221</v>
+        <v>7031291</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -29425,9 +29425,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>På levande gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29442,22 +29457,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122960048</v>
+        <v>122961322</v>
       </c>
       <c r="B254" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -29470,21 +29485,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -29494,13 +29509,13 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>459483</v>
+        <v>459218</v>
       </c>
       <c r="R254" t="n">
-        <v>7031282</v>
+        <v>7031361</v>
       </c>
       <c r="S254" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -29527,24 +29542,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 17 cm i diameter</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29559,22 +29559,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122965369</v>
+        <v>122969437</v>
       </c>
       <c r="B255" t="n">
-        <v>74863</v>
+        <v>74854</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -29583,41 +29583,55 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>459220</v>
+        <v>459333</v>
       </c>
       <c r="R255" t="n">
-        <v>7031200</v>
+        <v>7031413</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29646,7 +29660,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29656,12 +29670,12 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på ved på gammal björkhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29676,22 +29690,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122964624</v>
+        <v>122988604</v>
       </c>
       <c r="B256" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -29704,34 +29718,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>459329</v>
+        <v>459513</v>
       </c>
       <c r="R256" t="n">
-        <v>7031240</v>
+        <v>7031221</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29766,11 +29780,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Gott om långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD256" t="b">
         <v>0</v>
       </c>
@@ -29779,51 +29788,26 @@
       </c>
       <c r="AG256" t="b">
         <v>0</v>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122988656</v>
+        <v>122960048</v>
       </c>
       <c r="B257" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -29836,37 +29820,37 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>459032</v>
+        <v>459483</v>
       </c>
       <c r="R257" t="n">
-        <v>7031453</v>
+        <v>7031282</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29893,9 +29877,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 17 cm i diameter</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29910,22 +29909,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122988651</v>
+        <v>122965369</v>
       </c>
       <c r="B258" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -29938,34 +29937,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>459404</v>
+        <v>459220</v>
       </c>
       <c r="R258" t="n">
-        <v>7031192</v>
+        <v>7031200</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29995,9 +29994,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -30012,19 +30026,19 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122960423</v>
+        <v>122964624</v>
       </c>
       <c r="B259" t="n">
         <v>78766</v>
@@ -30064,13 +30078,13 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>459452</v>
+        <v>459329</v>
       </c>
       <c r="R259" t="n">
-        <v>7031305</v>
+        <v>7031240</v>
       </c>
       <c r="S259" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -30102,6 +30116,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Gott om långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD259" t="b">
         <v>0</v>
       </c>
@@ -30113,7 +30132,7 @@
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ259" t="inlineStr">
@@ -30128,12 +30147,12 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT259" t="inlineStr"/>
@@ -30151,10 +30170,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122971604</v>
+        <v>122988656</v>
       </c>
       <c r="B260" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -30163,38 +30182,38 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>458996</v>
+        <v>459032</v>
       </c>
       <c r="R260" t="n">
-        <v>7031467</v>
+        <v>7031453</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30224,24 +30243,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30256,22 +30260,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122961313</v>
+        <v>122988651</v>
       </c>
       <c r="B261" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -30284,37 +30288,37 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>459398</v>
+        <v>459404</v>
       </c>
       <c r="R261" t="n">
-        <v>7031291</v>
+        <v>7031192</v>
       </c>
       <c r="S261" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -30341,24 +30345,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>På levande gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30373,22 +30362,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122961322</v>
+        <v>122960423</v>
       </c>
       <c r="B262" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -30401,21 +30390,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -30425,13 +30414,13 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>459218</v>
+        <v>459452</v>
       </c>
       <c r="R262" t="n">
-        <v>7031361</v>
+        <v>7031305</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -30471,6 +30460,31 @@
       </c>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
@@ -30487,10 +30501,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122969437</v>
+        <v>122971604</v>
       </c>
       <c r="B263" t="n">
-        <v>74854</v>
+        <v>79875</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -30499,55 +30513,41 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>492</v>
+        <v>6461</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>459333</v>
+        <v>458996</v>
       </c>
       <c r="R263" t="n">
-        <v>7031413</v>
+        <v>7031467</v>
       </c>
       <c r="S263" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -30586,12 +30586,12 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Rikligt på ved på gammal björkhögstubbe i gammal granskog vid bäck</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -33159,10 +33159,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>123010791</v>
+        <v>123010769</v>
       </c>
       <c r="B286" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -33171,25 +33171,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -33199,10 +33199,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>459278</v>
+        <v>459079</v>
       </c>
       <c r="R286" t="n">
-        <v>7031203</v>
+        <v>7031108</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -33234,7 +33234,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -33271,7 +33271,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>123010769</v>
+        <v>123010795</v>
       </c>
       <c r="B287" t="n">
         <v>78766</v>
@@ -33311,10 +33311,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>459079</v>
+        <v>459331</v>
       </c>
       <c r="R287" t="n">
-        <v>7031108</v>
+        <v>7031199</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -33346,7 +33346,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -33383,10 +33383,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>123010795</v>
+        <v>123010791</v>
       </c>
       <c r="B288" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -33395,25 +33395,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -33423,10 +33423,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>459331</v>
+        <v>459278</v>
       </c>
       <c r="R288" t="n">
-        <v>7031199</v>
+        <v>7031203</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -33468,7 +33468,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -34176,10 +34176,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>123010786</v>
+        <v>122972364</v>
       </c>
       <c r="B295" t="n">
-        <v>78766</v>
+        <v>97378</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -34188,38 +34188,38 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>459165</v>
+        <v>458996</v>
       </c>
       <c r="R295" t="n">
-        <v>7031178</v>
+        <v>7031467</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -34251,7 +34251,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -34261,7 +34261,12 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>Ca 40 cm upp på sälg</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -34272,26 +34277,41 @@
       </c>
       <c r="AG295" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>123010785</v>
+        <v>123010786</v>
       </c>
       <c r="B296" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -34304,21 +34324,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -34400,10 +34420,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>123010777</v>
+        <v>123010785</v>
       </c>
       <c r="B297" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -34416,21 +34436,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -34440,10 +34460,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>459144</v>
+        <v>459165</v>
       </c>
       <c r="R297" t="n">
-        <v>7031092</v>
+        <v>7031178</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -34475,7 +34495,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -34485,7 +34505,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -34496,21 +34516,6 @@
       </c>
       <c r="AG297" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ297" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK297" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO297" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
@@ -34527,10 +34532,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>123010773</v>
+        <v>123010777</v>
       </c>
       <c r="B298" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -34543,21 +34548,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -34567,10 +34572,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>459131</v>
+        <v>459144</v>
       </c>
       <c r="R298" t="n">
-        <v>7031087</v>
+        <v>7031092</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -34602,7 +34607,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -34612,7 +34617,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -34623,6 +34628,21 @@
       </c>
       <c r="AG298" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT298" t="inlineStr"/>
       <c r="AW298" t="inlineStr">
@@ -34639,10 +34659,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122972364</v>
+        <v>123010773</v>
       </c>
       <c r="B299" t="n">
-        <v>97378</v>
+        <v>74863</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -34651,38 +34671,38 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>221063</v>
+        <v>6440</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>458996</v>
+        <v>459131</v>
       </c>
       <c r="R299" t="n">
-        <v>7031467</v>
+        <v>7031087</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34714,7 +34734,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -34724,12 +34744,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>Ca 40 cm upp på sälg</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -34740,31 +34755,16 @@
       </c>
       <c r="AG299" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO299" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
@@ -35726,10 +35726,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>123010799</v>
+        <v>122962441</v>
       </c>
       <c r="B308" t="n">
-        <v>82553</v>
+        <v>91890</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -35738,38 +35738,45 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>459399</v>
+        <v>459345</v>
       </c>
       <c r="R308" t="n">
-        <v>7031218</v>
+        <v>7031322</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -35801,7 +35808,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -35811,7 +35818,12 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>På marken längs med bäck, gamla fruktkroppar från hösten 2024</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -35820,28 +35832,29 @@
       <c r="AE308" t="b">
         <v>0</v>
       </c>
+      <c r="AF308" t="inlineStr"/>
       <c r="AG308" t="b">
         <v>0</v>
       </c>
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>123010752</v>
+        <v>122968192</v>
       </c>
       <c r="B309" t="n">
-        <v>78766</v>
+        <v>74858</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -35854,34 +35867,37 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>459136</v>
+        <v>459419</v>
       </c>
       <c r="R309" t="n">
-        <v>7031333</v>
+        <v>7031354</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -35913,7 +35929,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -35923,7 +35939,12 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -35932,28 +35953,29 @@
       <c r="AE309" t="b">
         <v>0</v>
       </c>
+      <c r="AF309" t="inlineStr"/>
       <c r="AG309" t="b">
         <v>0</v>
       </c>
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122962441</v>
+        <v>122973098</v>
       </c>
       <c r="B310" t="n">
-        <v>91890</v>
+        <v>78847</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -35962,45 +35984,38 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
-      <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>459345</v>
+        <v>459120</v>
       </c>
       <c r="R310" t="n">
-        <v>7031322</v>
+        <v>7031572</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -36032,7 +36047,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -36042,12 +36057,12 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>På marken längs med bäck, gamla fruktkroppar från hösten 2024</t>
+          <t>På tunna grenar på gammal levande gran (1 cm dbh) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -36056,9 +36071,23 @@
       <c r="AE310" t="b">
         <v>0</v>
       </c>
-      <c r="AF310" t="inlineStr"/>
       <c r="AG310" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ310" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK310" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO310" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
@@ -36075,10 +36104,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122968192</v>
+        <v>123010799</v>
       </c>
       <c r="B311" t="n">
-        <v>74858</v>
+        <v>82553</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -36091,37 +36120,34 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>310</v>
+        <v>1312</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>459419</v>
+        <v>459399</v>
       </c>
       <c r="R311" t="n">
-        <v>7031354</v>
+        <v>7031218</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -36153,7 +36179,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -36163,12 +36189,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC311" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -36177,29 +36198,28 @@
       <c r="AE311" t="b">
         <v>0</v>
       </c>
-      <c r="AF311" t="inlineStr"/>
       <c r="AG311" t="b">
         <v>0</v>
       </c>
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122973098</v>
+        <v>123010752</v>
       </c>
       <c r="B312" t="n">
-        <v>78847</v>
+        <v>78766</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -36212,34 +36232,34 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459120</v>
+        <v>459136</v>
       </c>
       <c r="R312" t="n">
-        <v>7031572</v>
+        <v>7031333</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -36271,7 +36291,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -36281,12 +36301,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>På tunna grenar på gammal levande gran (1 cm dbh) i gammal gransumpskog</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -36297,31 +36312,16 @@
       </c>
       <c r="AG312" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ312" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK312" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO312" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
@@ -38083,10 +38083,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>123012467</v>
+        <v>123010796</v>
       </c>
       <c r="B328" t="n">
-        <v>79751</v>
+        <v>82553</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -38095,44 +38095,41 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>459017</v>
+        <v>459341</v>
       </c>
       <c r="R328" t="n">
-        <v>7031714</v>
+        <v>7031193</v>
       </c>
       <c r="S328" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -38159,35 +38156,29 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA328" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD328" t="b">
         <v>0</v>
       </c>
       <c r="AE328" t="b">
         <v>0</v>
       </c>
-      <c r="AF328" t="inlineStr"/>
       <c r="AG328" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ328" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK328" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO328" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
@@ -38204,10 +38195,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>123010797</v>
+        <v>123012467</v>
       </c>
       <c r="B329" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -38216,41 +38207,44 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>459374</v>
+        <v>459017</v>
       </c>
       <c r="R329" t="n">
-        <v>7031220</v>
+        <v>7031714</v>
       </c>
       <c r="S329" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -38277,29 +38271,35 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA329" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD329" t="b">
         <v>0</v>
       </c>
       <c r="AE329" t="b">
         <v>0</v>
       </c>
+      <c r="AF329" t="inlineStr"/>
       <c r="AG329" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT329" t="inlineStr"/>
       <c r="AW329" t="inlineStr">
@@ -38316,10 +38316,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>123010796</v>
+        <v>123010797</v>
       </c>
       <c r="B330" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -38332,21 +38332,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -38356,10 +38356,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>459341</v>
+        <v>459374</v>
       </c>
       <c r="R330" t="n">
-        <v>7031193</v>
+        <v>7031220</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -38391,7 +38391,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -38401,7 +38401,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -38428,10 +38428,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>123010781</v>
+        <v>123010801</v>
       </c>
       <c r="B331" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -38444,21 +38444,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -38468,10 +38468,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>459191</v>
+        <v>459485</v>
       </c>
       <c r="R331" t="n">
-        <v>7031091</v>
+        <v>7031184</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -38540,10 +38540,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>123010793</v>
+        <v>123010781</v>
       </c>
       <c r="B332" t="n">
-        <v>80743</v>
+        <v>77699</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -38556,21 +38556,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>229436</v>
+        <v>228579</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -38580,10 +38580,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>459331</v>
+        <v>459191</v>
       </c>
       <c r="R332" t="n">
-        <v>7031199</v>
+        <v>7031091</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -38615,7 +38615,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -38625,7 +38625,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -38652,10 +38652,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>123010801</v>
+        <v>123010793</v>
       </c>
       <c r="B333" t="n">
-        <v>78766</v>
+        <v>80743</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -38668,21 +38668,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6425</v>
+        <v>229436</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -38692,10 +38692,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>459485</v>
+        <v>459331</v>
       </c>
       <c r="R333" t="n">
-        <v>7031184</v>
+        <v>7031199</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -38727,7 +38727,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -39558,10 +39558,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>123010800</v>
+        <v>123010764</v>
       </c>
       <c r="B341" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -39574,21 +39574,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -39598,10 +39598,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>459400</v>
+        <v>459027</v>
       </c>
       <c r="R341" t="n">
-        <v>7031215</v>
+        <v>7031097</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -39633,7 +39633,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -39643,7 +39643,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -39670,7 +39670,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>123010751</v>
+        <v>123010800</v>
       </c>
       <c r="B342" t="n">
         <v>78766</v>
@@ -39710,10 +39710,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>459111</v>
+        <v>459400</v>
       </c>
       <c r="R342" t="n">
-        <v>7031436</v>
+        <v>7031215</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -39745,7 +39745,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -39755,7 +39755,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -39782,10 +39782,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122963099</v>
+        <v>123010751</v>
       </c>
       <c r="B343" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -39794,54 +39794,38 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>459295</v>
+        <v>459111</v>
       </c>
       <c r="R343" t="n">
-        <v>7031196</v>
+        <v>7031436</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -39873,7 +39857,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -39883,12 +39867,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>Fyra gröna plantor och 1 vinterståndare på marken i gammal barrblandskog</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -39897,29 +39876,28 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
-      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>123010764</v>
+        <v>122963099</v>
       </c>
       <c r="B344" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -39928,38 +39906,54 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>459027</v>
+        <v>459295</v>
       </c>
       <c r="R344" t="n">
-        <v>7031097</v>
+        <v>7031196</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -39991,7 +39985,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -40001,7 +39995,12 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>Fyra gröna plantor och 1 vinterståndare på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -40010,18 +40009,19 @@
       <c r="AE344" t="b">
         <v>0</v>
       </c>
+      <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="b">
         <v>0</v>
       </c>
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122988666</v>
+        <v>122969909</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459327</v>
+        <v>458792</v>
       </c>
       <c r="R2" t="n">
-        <v>7031306</v>
+        <v>7031270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122969185</v>
+        <v>122971232</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +807,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459114</v>
+        <v>459151</v>
       </c>
       <c r="R3" t="n">
-        <v>7031298</v>
+        <v>7031320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,19 +869,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122988599</v>
+        <v>122963067</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459094</v>
+        <v>459234</v>
       </c>
       <c r="R4" t="n">
-        <v>7031558</v>
+        <v>7031238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +986,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122988602</v>
+        <v>122988666</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458932</v>
+        <v>459327</v>
       </c>
       <c r="R5" t="n">
-        <v>7031315</v>
+        <v>7031306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122960575</v>
+        <v>122969185</v>
       </c>
       <c r="B6" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459264</v>
+        <v>459114</v>
       </c>
       <c r="R6" t="n">
-        <v>7031333</v>
+        <v>7031298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1190,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1217,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122971004</v>
+        <v>122988599</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,51 +1245,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459301</v>
+        <v>459094</v>
       </c>
       <c r="R7" t="n">
-        <v>7031350</v>
+        <v>7031558</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,11 +1307,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med långväxta bålar på många granar. Fertila bålar med apothecier förekommer.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1300,51 +1315,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122962324</v>
+        <v>122988602</v>
       </c>
       <c r="B8" t="n">
-        <v>79882</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,41 +1343,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459407</v>
+        <v>458932</v>
       </c>
       <c r="R8" t="n">
-        <v>7031333</v>
+        <v>7031315</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,11 +1409,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en liggande levande smal sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1432,51 +1417,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122988648</v>
+        <v>122960575</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,38 +1445,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459321</v>
+        <v>459264</v>
       </c>
       <c r="R9" t="n">
-        <v>7031297</v>
+        <v>7031333</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,19 +1523,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122988653</v>
+        <v>122971004</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1608,20 +1568,34 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459438</v>
+        <v>459301</v>
       </c>
       <c r="R10" t="n">
-        <v>7031232</v>
+        <v>7031350</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,6 +1627,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med långväxta bålar på många granar. Fertila bålar med apothecier förekommer.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1661,26 +1640,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122971232</v>
+        <v>122962324</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,46 +1693,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459151</v>
+        <v>459407</v>
       </c>
       <c r="R11" t="n">
-        <v>7031320</v>
+        <v>7031333</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1761,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,6 +1772,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1789,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122963067</v>
+        <v>122988648</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,39 +1829,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459234</v>
+        <v>459321</v>
       </c>
       <c r="R12" t="n">
-        <v>7031238</v>
+        <v>7031297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,11 +1891,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1889,22 +1903,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969909</v>
+        <v>122988653</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,52 +1927,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458792</v>
+        <v>459438</v>
       </c>
       <c r="R13" t="n">
-        <v>7031270</v>
+        <v>7031232</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,12 +2005,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122988667</v>
+        <v>122960512</v>
       </c>
       <c r="B35" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4492,37 +4492,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458894</v>
+        <v>459447</v>
       </c>
       <c r="R35" t="n">
-        <v>7031350</v>
+        <v>7031281</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,9 +4549,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,22 +4581,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122988608</v>
+        <v>122988662</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4594,21 +4609,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4618,10 +4633,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458859</v>
+        <v>459509</v>
       </c>
       <c r="R36" t="n">
-        <v>7031391</v>
+        <v>7031229</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,10 +4695,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122958541</v>
+        <v>122959266</v>
       </c>
       <c r="B37" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4696,21 +4711,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4720,10 +4735,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459525</v>
+        <v>459462</v>
       </c>
       <c r="R37" t="n">
-        <v>7031282</v>
+        <v>7031193</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4782,10 +4797,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122970650</v>
+        <v>122960006</v>
       </c>
       <c r="B38" t="n">
-        <v>74786</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4798,42 +4813,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459119</v>
+        <v>459491</v>
       </c>
       <c r="R38" t="n">
-        <v>7031393</v>
+        <v>7031303</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4860,26 +4870,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg (40 cm dbh) i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4888,26 +4883,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122970920</v>
+        <v>122988629</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4920,39 +4940,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459100</v>
+        <v>458990</v>
       </c>
       <c r="R39" t="n">
-        <v>7031235</v>
+        <v>7031684</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4987,11 +5002,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5004,22 +5014,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122973259</v>
+        <v>122964051</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5032,39 +5042,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459035</v>
+        <v>459393</v>
       </c>
       <c r="R40" t="n">
-        <v>7031669</v>
+        <v>7031334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5101,7 +5111,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5112,6 +5122,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5128,10 +5163,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122973056</v>
+        <v>122961958</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5144,39 +5179,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459078</v>
+        <v>459174</v>
       </c>
       <c r="R41" t="n">
-        <v>7031631</v>
+        <v>7031337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5209,11 +5244,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5240,10 +5270,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122988614</v>
+        <v>122988667</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5256,39 +5286,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459069</v>
+        <v>458894</v>
       </c>
       <c r="R42" t="n">
-        <v>7031625</v>
+        <v>7031350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5347,10 +5372,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122961195</v>
+        <v>122988608</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5363,42 +5388,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459334</v>
+        <v>458859</v>
       </c>
       <c r="R43" t="n">
-        <v>7031182</v>
+        <v>7031391</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5425,24 +5445,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På död gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5457,22 +5462,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122962411</v>
+        <v>122958541</v>
       </c>
       <c r="B44" t="n">
-        <v>97378</v>
+        <v>90970</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5481,38 +5486,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221063</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459345</v>
+        <v>459525</v>
       </c>
       <c r="R44" t="n">
-        <v>7031322</v>
+        <v>7031282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5542,24 +5547,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt på marken längs med naturlig skogsbäck</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5574,22 +5564,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122961088</v>
+        <v>122970650</v>
       </c>
       <c r="B45" t="n">
-        <v>77699</v>
+        <v>74786</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5602,37 +5592,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>1460</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459429</v>
+        <v>459119</v>
       </c>
       <c r="R45" t="n">
-        <v>7031286</v>
+        <v>7031393</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5661,7 +5656,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5671,12 +5666,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran ca 14 cm i diameter</t>
+          <t>På bark på stam av levande gammal sälg (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5691,22 +5686,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122988606</v>
+        <v>122970920</v>
       </c>
       <c r="B46" t="n">
-        <v>79355</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5719,34 +5714,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458994</v>
+        <v>459100</v>
       </c>
       <c r="R46" t="n">
-        <v>7031677</v>
+        <v>7031235</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,6 +5781,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5793,22 +5798,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122959785</v>
+        <v>122973259</v>
       </c>
       <c r="B47" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5821,34 +5826,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459495</v>
+        <v>459035</v>
       </c>
       <c r="R47" t="n">
-        <v>7031265</v>
+        <v>7031669</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5878,24 +5888,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran 25 cm i diameter</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5910,22 +5910,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122960512</v>
+        <v>122973056</v>
       </c>
       <c r="B48" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5938,37 +5938,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459447</v>
+        <v>459078</v>
       </c>
       <c r="R48" t="n">
-        <v>7031281</v>
+        <v>7031631</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5995,24 +6000,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran ca 20 cm i diameter</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6027,22 +6022,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122988662</v>
+        <v>122988614</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6055,34 +6050,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459509</v>
+        <v>459069</v>
       </c>
       <c r="R49" t="n">
-        <v>7031229</v>
+        <v>7031625</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,10 +6141,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122959266</v>
+        <v>122961195</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6157,37 +6157,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459462</v>
+        <v>459334</v>
       </c>
       <c r="R50" t="n">
-        <v>7031193</v>
+        <v>7031182</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6214,9 +6219,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6231,22 +6251,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122960006</v>
+        <v>122962411</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>97378</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6255,41 +6275,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459491</v>
+        <v>459345</v>
       </c>
       <c r="R51" t="n">
-        <v>7031303</v>
+        <v>7031322</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6316,11 +6336,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt på marken längs med naturlig skogsbäck</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6329,51 +6364,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122988629</v>
+        <v>122961088</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6386,37 +6396,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458990</v>
+        <v>459429</v>
       </c>
       <c r="R52" t="n">
-        <v>7031684</v>
+        <v>7031286</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6443,9 +6453,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 14 cm i diameter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6460,22 +6485,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122964051</v>
+        <v>122988606</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>79355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6488,39 +6513,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459393</v>
+        <v>458994</v>
       </c>
       <c r="R53" t="n">
-        <v>7031334</v>
+        <v>7031677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6555,11 +6575,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6568,51 +6583,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122961958</v>
+        <v>122959785</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6625,39 +6615,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459174</v>
+        <v>459495</v>
       </c>
       <c r="R54" t="n">
-        <v>7031337</v>
+        <v>7031265</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6687,9 +6672,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gammal gran 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6704,12 +6704,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -10839,10 +10839,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122988627</v>
+        <v>122960798</v>
       </c>
       <c r="B92" t="n">
-        <v>56078</v>
+        <v>57631</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10855,37 +10855,46 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>458807</v>
+        <v>459430</v>
       </c>
       <c r="R92" t="n">
-        <v>7031401</v>
+        <v>7031305</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10929,22 +10938,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122970637</v>
+        <v>122988635</v>
       </c>
       <c r="B93" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10953,38 +10962,47 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459026</v>
+        <v>459043</v>
       </c>
       <c r="R93" t="n">
-        <v>7031279</v>
+        <v>7031643</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11014,24 +11032,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11046,22 +11049,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122961785</v>
+        <v>122988627</v>
       </c>
       <c r="B94" t="n">
-        <v>82553</v>
+        <v>56078</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11074,34 +11077,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>206004</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459199</v>
+        <v>458807</v>
       </c>
       <c r="R94" t="n">
-        <v>7031334</v>
+        <v>7031401</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11148,22 +11151,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122958831</v>
+        <v>122970637</v>
       </c>
       <c r="B95" t="n">
-        <v>79022</v>
+        <v>77699</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11172,43 +11175,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459540</v>
+        <v>459026</v>
       </c>
       <c r="R95" t="n">
-        <v>7031232</v>
+        <v>7031279</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11240,7 +11238,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11250,12 +11248,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På klen äldre gran</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11275,17 +11273,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122959894</v>
+        <v>122961785</v>
       </c>
       <c r="B96" t="n">
-        <v>74847</v>
+        <v>82553</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11294,25 +11292,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6439</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11322,10 +11320,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459316</v>
+        <v>459199</v>
       </c>
       <c r="R96" t="n">
-        <v>7031273</v>
+        <v>7031334</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11384,10 +11382,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122988669</v>
+        <v>122960043</v>
       </c>
       <c r="B97" t="n">
-        <v>77694</v>
+        <v>95911</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11400,34 +11398,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6487</v>
+        <v>53</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459002</v>
+        <v>459290</v>
       </c>
       <c r="R97" t="n">
-        <v>7031384</v>
+        <v>7031285</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11474,22 +11472,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122960216</v>
+        <v>122958831</v>
       </c>
       <c r="B98" t="n">
-        <v>78766</v>
+        <v>79022</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11498,41 +11496,46 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>459482</v>
+        <v>459540</v>
       </c>
       <c r="R98" t="n">
-        <v>7031303</v>
+        <v>7031232</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11559,14 +11562,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På klen äldre gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11577,51 +11590,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122988655</v>
+        <v>122959894</v>
       </c>
       <c r="B99" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11630,38 +11618,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458992</v>
+        <v>459316</v>
       </c>
       <c r="R99" t="n">
-        <v>7031302</v>
+        <v>7031273</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11708,22 +11696,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122964120</v>
+        <v>122988669</v>
       </c>
       <c r="B100" t="n">
-        <v>79847</v>
+        <v>77694</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11736,39 +11724,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>459380</v>
+        <v>459002</v>
       </c>
       <c r="R100" t="n">
-        <v>7031341</v>
+        <v>7031384</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11803,11 +11786,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en gran intill en gammal grovbarkad sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11816,51 +11794,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122968293</v>
+        <v>122960216</v>
       </c>
       <c r="B101" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11873,21 +11826,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11897,13 +11850,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>459120</v>
+        <v>459482</v>
       </c>
       <c r="R101" t="n">
-        <v>7031399</v>
+        <v>7031303</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11930,24 +11883,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11958,26 +11901,51 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122972517</v>
+        <v>122988655</v>
       </c>
       <c r="B102" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11990,39 +11958,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>459054</v>
+        <v>458992</v>
       </c>
       <c r="R102" t="n">
-        <v>7031521</v>
+        <v>7031302</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12069,22 +12032,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122988619</v>
+        <v>122964120</v>
       </c>
       <c r="B103" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12097,39 +12060,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>459028</v>
+        <v>459380</v>
       </c>
       <c r="R103" t="n">
-        <v>7031497</v>
+        <v>7031341</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12164,6 +12127,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en gran intill en gammal grovbarkad sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12173,30 +12141,50 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Gammal tall med grov bark</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122969979</v>
+        <v>122968293</v>
       </c>
       <c r="B104" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12209,47 +12197,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>459400</v>
+        <v>459120</v>
       </c>
       <c r="R104" t="n">
-        <v>7031412</v>
+        <v>7031399</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12276,14 +12254,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12294,51 +12282,26 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122988635</v>
+        <v>122972517</v>
       </c>
       <c r="B105" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12347,47 +12310,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>459043</v>
+        <v>459054</v>
       </c>
       <c r="R105" t="n">
-        <v>7031643</v>
+        <v>7031521</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12434,22 +12393,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122960043</v>
+        <v>122988619</v>
       </c>
       <c r="B106" t="n">
-        <v>95911</v>
+        <v>57478</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12462,34 +12421,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459290</v>
+        <v>459028</v>
       </c>
       <c r="R106" t="n">
-        <v>7031285</v>
+        <v>7031497</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12533,25 +12497,30 @@
       <c r="AG106" t="b">
         <v>0</v>
       </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Gammal tall med grov bark</t>
+        </is>
+      </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122960798</v>
+        <v>122969979</v>
       </c>
       <c r="B107" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12564,31 +12533,32 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12597,10 +12567,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459430</v>
+        <v>459400</v>
       </c>
       <c r="R107" t="n">
-        <v>7031305</v>
+        <v>7031412</v>
       </c>
       <c r="S107" t="n">
         <v>9</v>
@@ -12635,6 +12605,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12643,6 +12618,31 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12659,10 +12659,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122970353</v>
+        <v>122972595</v>
       </c>
       <c r="B108" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12675,21 +12675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12699,13 +12699,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>459174</v>
+        <v>459067</v>
       </c>
       <c r="R108" t="n">
-        <v>7031377</v>
+        <v>7031526</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12764,22 +12764,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122972474</v>
+        <v>122958993</v>
       </c>
       <c r="B109" t="n">
-        <v>91645</v>
+        <v>77699</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12788,38 +12788,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>67</v>
+        <v>228579</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>459051</v>
+        <v>459493</v>
       </c>
       <c r="R109" t="n">
-        <v>7031523</v>
+        <v>7031237</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12849,9 +12849,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (170 år, 14 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12866,22 +12881,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122988668</v>
+        <v>122971421</v>
       </c>
       <c r="B110" t="n">
-        <v>88303</v>
+        <v>77699</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12894,34 +12909,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>459033</v>
+        <v>459019</v>
       </c>
       <c r="R110" t="n">
-        <v>7031486</v>
+        <v>7031429</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12951,9 +12966,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 22 cm i diameter</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12968,22 +12998,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122968686</v>
+        <v>122970353</v>
       </c>
       <c r="B111" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12992,41 +13022,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459364</v>
+        <v>459174</v>
       </c>
       <c r="R111" t="n">
-        <v>7031404</v>
+        <v>7031377</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13055,7 +13085,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13065,12 +13095,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13085,22 +13115,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122958245</v>
+        <v>122972474</v>
       </c>
       <c r="B112" t="n">
-        <v>74863</v>
+        <v>91645</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13109,41 +13139,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>459590</v>
+        <v>459051</v>
       </c>
       <c r="R112" t="n">
-        <v>7031260</v>
+        <v>7031523</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13170,24 +13200,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13202,22 +13217,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122969476</v>
+        <v>122988668</v>
       </c>
       <c r="B113" t="n">
-        <v>74863</v>
+        <v>88303</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13230,34 +13245,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458820</v>
+        <v>459033</v>
       </c>
       <c r="R113" t="n">
-        <v>7031282</v>
+        <v>7031486</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13304,22 +13319,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122988663</v>
+        <v>122968686</v>
       </c>
       <c r="B114" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13328,20 +13343,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -13352,14 +13367,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>459127</v>
+        <v>459364</v>
       </c>
       <c r="R114" t="n">
-        <v>7031202</v>
+        <v>7031404</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13389,9 +13404,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13406,22 +13436,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122974308</v>
+        <v>122958245</v>
       </c>
       <c r="B115" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13434,46 +13464,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>459138</v>
+        <v>459590</v>
       </c>
       <c r="R115" t="n">
-        <v>7031684</v>
+        <v>7031260</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13502,7 +13523,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13512,7 +13533,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -13544,10 +13565,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122972595</v>
+        <v>122969476</v>
       </c>
       <c r="B116" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13560,21 +13581,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13584,10 +13605,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>459067</v>
+        <v>458820</v>
       </c>
       <c r="R116" t="n">
-        <v>7031526</v>
+        <v>7031282</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13617,24 +13638,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13649,22 +13655,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122958993</v>
+        <v>122988663</v>
       </c>
       <c r="B117" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13677,34 +13683,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>459493</v>
+        <v>459127</v>
       </c>
       <c r="R117" t="n">
-        <v>7031237</v>
+        <v>7031202</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13734,24 +13740,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (170 år, 14 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13766,22 +13757,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122971421</v>
+        <v>122974308</v>
       </c>
       <c r="B118" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13794,34 +13785,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>459019</v>
+        <v>459138</v>
       </c>
       <c r="R118" t="n">
-        <v>7031429</v>
+        <v>7031684</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13863,12 +13863,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På gammal gran ca 22 cm i diameter</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13883,12 +13883,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -22201,10 +22201,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122988607</v>
+        <v>122971413</v>
       </c>
       <c r="B191" t="n">
-        <v>90952</v>
+        <v>74863</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22217,34 +22217,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>458882</v>
+        <v>459013</v>
       </c>
       <c r="R191" t="n">
-        <v>7031377</v>
+        <v>7031443</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22274,9 +22274,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22291,22 +22306,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122988637</v>
+        <v>122988632</v>
       </c>
       <c r="B192" t="n">
-        <v>90970</v>
+        <v>79883</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22315,25 +22330,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22343,10 +22358,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>459515</v>
+        <v>459229</v>
       </c>
       <c r="R192" t="n">
-        <v>7031220</v>
+        <v>7031281</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22405,10 +22420,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122972647</v>
+        <v>122970161</v>
       </c>
       <c r="B193" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22421,34 +22436,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>459098</v>
+        <v>459355</v>
       </c>
       <c r="R193" t="n">
-        <v>7031549</v>
+        <v>7031426</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22483,6 +22498,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -22491,6 +22511,31 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
@@ -22507,10 +22552,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122961346</v>
+        <v>122961954</v>
       </c>
       <c r="B194" t="n">
-        <v>82553</v>
+        <v>56680</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22523,34 +22568,44 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>459218</v>
+        <v>459411</v>
       </c>
       <c r="R194" t="n">
-        <v>7031359</v>
+        <v>7031295</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22585,6 +22640,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -22593,6 +22653,11 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
@@ -22609,7 +22674,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122988609</v>
+        <v>122988607</v>
       </c>
       <c r="B195" t="n">
         <v>90952</v>
@@ -22649,10 +22714,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>458845</v>
+        <v>458882</v>
       </c>
       <c r="R195" t="n">
-        <v>7031403</v>
+        <v>7031377</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22711,10 +22776,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122958513</v>
+        <v>122988637</v>
       </c>
       <c r="B196" t="n">
-        <v>74849</v>
+        <v>90970</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22723,38 +22788,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>459544</v>
+        <v>459515</v>
       </c>
       <c r="R196" t="n">
-        <v>7031238</v>
+        <v>7031220</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22784,26 +22849,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
@@ -22812,41 +22862,26 @@
       </c>
       <c r="AG196" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122959882</v>
+        <v>122972647</v>
       </c>
       <c r="B197" t="n">
-        <v>78845</v>
+        <v>79848</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22859,48 +22894,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>459439</v>
+        <v>459098</v>
       </c>
       <c r="R197" t="n">
-        <v>7031261</v>
+        <v>7031549</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22930,24 +22951,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22962,22 +22968,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122971413</v>
+        <v>122961346</v>
       </c>
       <c r="B198" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22990,34 +22996,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>459013</v>
+        <v>459218</v>
       </c>
       <c r="R198" t="n">
-        <v>7031443</v>
+        <v>7031359</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23047,24 +23053,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23079,22 +23070,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122970161</v>
+        <v>122988609</v>
       </c>
       <c r="B199" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -23107,34 +23098,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>459355</v>
+        <v>458845</v>
       </c>
       <c r="R199" t="n">
-        <v>7031426</v>
+        <v>7031403</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23169,11 +23160,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
@@ -23182,51 +23168,26 @@
       </c>
       <c r="AG199" t="b">
         <v>0</v>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122961954</v>
+        <v>122958513</v>
       </c>
       <c r="B200" t="n">
-        <v>56680</v>
+        <v>74849</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -23235,48 +23196,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>102612</v>
+        <v>306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>459411</v>
+        <v>459544</v>
       </c>
       <c r="R200" t="n">
-        <v>7031295</v>
+        <v>7031238</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23306,14 +23257,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23325,30 +23286,40 @@
       <c r="AG200" t="b">
         <v>0</v>
       </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122988632</v>
+        <v>122959882</v>
       </c>
       <c r="B201" t="n">
-        <v>79883</v>
+        <v>78845</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23357,38 +23328,52 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>459229</v>
+        <v>459439</v>
       </c>
       <c r="R201" t="n">
-        <v>7031281</v>
+        <v>7031261</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23418,9 +23403,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23435,12 +23435,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -35273,10 +35273,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>123010774</v>
+        <v>123010753</v>
       </c>
       <c r="B304" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -35289,34 +35289,39 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P304" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>459131</v>
+        <v>459203</v>
       </c>
       <c r="R304" t="n">
-        <v>7031087</v>
+        <v>7031325</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -35348,7 +35353,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -35358,7 +35363,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -35385,10 +35390,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>123010763</v>
+        <v>123010774</v>
       </c>
       <c r="B305" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -35401,21 +35406,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -35425,10 +35430,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>459019</v>
+        <v>459131</v>
       </c>
       <c r="R305" t="n">
-        <v>7031119</v>
+        <v>7031087</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -35460,7 +35465,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -35470,7 +35475,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -35497,10 +35502,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>123010753</v>
+        <v>123010763</v>
       </c>
       <c r="B306" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -35513,39 +35518,34 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>459203</v>
+        <v>459019</v>
       </c>
       <c r="R306" t="n">
-        <v>7031325</v>
+        <v>7031119</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -35577,7 +35577,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -35587,7 +35587,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -37032,10 +37032,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>123010755</v>
+        <v>123010762</v>
       </c>
       <c r="B319" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -37044,25 +37044,25 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
@@ -37072,10 +37072,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>459139</v>
+        <v>458998</v>
       </c>
       <c r="R319" t="n">
-        <v>7031244</v>
+        <v>7031118</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -37107,7 +37107,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -37117,7 +37117,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -37144,7 +37144,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>123010762</v>
+        <v>123010765</v>
       </c>
       <c r="B320" t="n">
         <v>90952</v>
@@ -37184,10 +37184,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>458998</v>
+        <v>459062</v>
       </c>
       <c r="R320" t="n">
-        <v>7031118</v>
+        <v>7031083</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -37219,7 +37219,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -37229,7 +37229,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -37256,10 +37256,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>123010765</v>
+        <v>123010747</v>
       </c>
       <c r="B321" t="n">
-        <v>90952</v>
+        <v>74854</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -37268,25 +37268,25 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
@@ -37296,10 +37296,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>459062</v>
+        <v>459044</v>
       </c>
       <c r="R321" t="n">
-        <v>7031083</v>
+        <v>7031517</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -37331,7 +37331,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -37352,6 +37352,21 @@
       </c>
       <c r="AG321" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
@@ -37361,17 +37376,17 @@
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>123010747</v>
+        <v>123010783</v>
       </c>
       <c r="B322" t="n">
-        <v>74854</v>
+        <v>90917</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -37380,25 +37395,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>492</v>
+        <v>5447</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -37408,10 +37423,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>459044</v>
+        <v>459162</v>
       </c>
       <c r="R322" t="n">
-        <v>7031517</v>
+        <v>7031130</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -37443,7 +37458,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -37453,7 +37468,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -37464,21 +37479,6 @@
       </c>
       <c r="AG322" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK322" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO322" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
@@ -37488,17 +37488,17 @@
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>123010783</v>
+        <v>123010756</v>
       </c>
       <c r="B323" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -37507,25 +37507,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -37535,10 +37535,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>459162</v>
+        <v>459065</v>
       </c>
       <c r="R323" t="n">
-        <v>7031130</v>
+        <v>7031224</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -37570,7 +37570,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -37607,10 +37607,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>123010756</v>
+        <v>123010755</v>
       </c>
       <c r="B324" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -37619,25 +37619,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -37647,10 +37647,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>459065</v>
+        <v>459139</v>
       </c>
       <c r="R324" t="n">
-        <v>7031224</v>
+        <v>7031244</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -37682,7 +37682,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -37692,7 +37692,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -38652,10 +38652,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>123010815</v>
+        <v>123010810</v>
       </c>
       <c r="B333" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -38668,21 +38668,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -38692,10 +38692,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>459547</v>
+        <v>459550</v>
       </c>
       <c r="R333" t="n">
-        <v>7031215</v>
+        <v>7031204</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -38727,7 +38727,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -38764,10 +38764,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>123010810</v>
+        <v>123010815</v>
       </c>
       <c r="B334" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -38780,21 +38780,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -38804,10 +38804,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>459550</v>
+        <v>459547</v>
       </c>
       <c r="R334" t="n">
-        <v>7031204</v>
+        <v>7031215</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -38839,7 +38839,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -38849,7 +38849,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -39446,10 +39446,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>123010764</v>
+        <v>123010800</v>
       </c>
       <c r="B340" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -39462,21 +39462,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -39486,10 +39486,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>459027</v>
+        <v>459400</v>
       </c>
       <c r="R340" t="n">
-        <v>7031097</v>
+        <v>7031215</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -39521,7 +39521,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -39531,7 +39531,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -39558,7 +39558,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>123010800</v>
+        <v>123010751</v>
       </c>
       <c r="B341" t="n">
         <v>78766</v>
@@ -39598,10 +39598,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>459400</v>
+        <v>459111</v>
       </c>
       <c r="R341" t="n">
-        <v>7031215</v>
+        <v>7031436</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -39633,7 +39633,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -39643,7 +39643,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -39670,10 +39670,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>123010751</v>
+        <v>122963099</v>
       </c>
       <c r="B342" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -39682,38 +39682,54 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>459111</v>
+        <v>459295</v>
       </c>
       <c r="R342" t="n">
-        <v>7031436</v>
+        <v>7031196</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -39745,7 +39761,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -39755,7 +39771,12 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>Fyra gröna plantor och 1 vinterståndare på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -39764,28 +39785,29 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
       <c r="AT342" t="inlineStr"/>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122963099</v>
+        <v>123010764</v>
       </c>
       <c r="B343" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -39794,54 +39816,38 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>459295</v>
+        <v>459027</v>
       </c>
       <c r="R343" t="n">
-        <v>7031196</v>
+        <v>7031097</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -39873,7 +39879,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -39883,12 +39889,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>Fyra gröna plantor och 1 vinterståndare på marken i gammal barrblandskog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -39897,19 +39898,18 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
-      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122969909</v>
+        <v>122988666</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458792</v>
+        <v>459327</v>
       </c>
       <c r="R2" t="n">
-        <v>7031270</v>
+        <v>7031306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122971232</v>
+        <v>122969185</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459151</v>
+        <v>459114</v>
       </c>
       <c r="R3" t="n">
-        <v>7031320</v>
+        <v>7031298</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,14 +850,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122963067</v>
+        <v>122988599</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459234</v>
+        <v>459094</v>
       </c>
       <c r="R4" t="n">
-        <v>7031238</v>
+        <v>7031558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,11 +967,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122988666</v>
+        <v>122988602</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459327</v>
+        <v>458932</v>
       </c>
       <c r="R5" t="n">
-        <v>7031306</v>
+        <v>7031315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122969185</v>
+        <v>122960575</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459114</v>
+        <v>459264</v>
       </c>
       <c r="R6" t="n">
-        <v>7031298</v>
+        <v>7031333</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,19 +1166,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122988599</v>
+        <v>122971004</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,37 +1211,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459094</v>
+        <v>459301</v>
       </c>
       <c r="R7" t="n">
-        <v>7031558</v>
+        <v>7031350</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,6 +1287,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med långväxta bålar på många granar. Fertila bålar med apothecier förekommer.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1315,26 +1300,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122988602</v>
+        <v>122962324</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>79882</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,41 +1353,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458932</v>
+        <v>459407</v>
       </c>
       <c r="R8" t="n">
-        <v>7031315</v>
+        <v>7031333</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,6 +1419,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en liggande levande smal sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1417,26 +1432,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122960575</v>
+        <v>122988648</v>
       </c>
       <c r="B9" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,38 +1485,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459264</v>
+        <v>459321</v>
       </c>
       <c r="R9" t="n">
-        <v>7031333</v>
+        <v>7031297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,19 +1563,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122971004</v>
+        <v>122988653</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1568,34 +1608,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459301</v>
+        <v>459438</v>
       </c>
       <c r="R10" t="n">
-        <v>7031350</v>
+        <v>7031232</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,11 +1653,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med långväxta bålar på många granar. Fertila bålar med apothecier förekommer.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1640,51 +1661,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122962324</v>
+        <v>122971232</v>
       </c>
       <c r="B11" t="n">
-        <v>79882</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,41 +1689,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459407</v>
+        <v>459151</v>
       </c>
       <c r="R11" t="n">
-        <v>7031333</v>
+        <v>7031320</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1762,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,31 +1773,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1813,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122988648</v>
+        <v>122963067</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,34 +1805,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459321</v>
+        <v>459234</v>
       </c>
       <c r="R12" t="n">
-        <v>7031297</v>
+        <v>7031238</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,6 +1872,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1903,22 +1889,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122988653</v>
+        <v>122969909</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,38 +1913,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459438</v>
+        <v>458792</v>
       </c>
       <c r="R13" t="n">
-        <v>7031232</v>
+        <v>7031270</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,12 +2005,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -22201,10 +22201,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122971413</v>
+        <v>122988607</v>
       </c>
       <c r="B191" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22217,34 +22217,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>459013</v>
+        <v>458882</v>
       </c>
       <c r="R191" t="n">
-        <v>7031443</v>
+        <v>7031377</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22274,24 +22274,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22306,22 +22291,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122988632</v>
+        <v>122988637</v>
       </c>
       <c r="B192" t="n">
-        <v>79883</v>
+        <v>90970</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22330,25 +22315,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22358,10 +22343,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>459229</v>
+        <v>459515</v>
       </c>
       <c r="R192" t="n">
-        <v>7031281</v>
+        <v>7031220</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22420,10 +22405,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122970161</v>
+        <v>122972647</v>
       </c>
       <c r="B193" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22436,34 +22421,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>459355</v>
+        <v>459098</v>
       </c>
       <c r="R193" t="n">
-        <v>7031426</v>
+        <v>7031549</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22498,11 +22483,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -22511,31 +22491,6 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
@@ -22552,10 +22507,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122961954</v>
+        <v>122961346</v>
       </c>
       <c r="B194" t="n">
-        <v>56680</v>
+        <v>82553</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22568,44 +22523,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>459411</v>
+        <v>459218</v>
       </c>
       <c r="R194" t="n">
-        <v>7031295</v>
+        <v>7031359</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22640,11 +22585,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -22653,11 +22593,6 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
@@ -22674,7 +22609,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122988607</v>
+        <v>122988609</v>
       </c>
       <c r="B195" t="n">
         <v>90952</v>
@@ -22714,10 +22649,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>458882</v>
+        <v>458845</v>
       </c>
       <c r="R195" t="n">
-        <v>7031377</v>
+        <v>7031403</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22776,10 +22711,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122988637</v>
+        <v>122958513</v>
       </c>
       <c r="B196" t="n">
-        <v>90970</v>
+        <v>74849</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22788,38 +22723,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>459515</v>
+        <v>459544</v>
       </c>
       <c r="R196" t="n">
-        <v>7031220</v>
+        <v>7031238</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22849,11 +22784,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
@@ -22862,26 +22812,41 @@
       </c>
       <c r="AG196" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122972647</v>
+        <v>122959882</v>
       </c>
       <c r="B197" t="n">
-        <v>79848</v>
+        <v>78845</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22894,34 +22859,48 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>459098</v>
+        <v>459439</v>
       </c>
       <c r="R197" t="n">
-        <v>7031549</v>
+        <v>7031261</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22951,9 +22930,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22968,22 +22962,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122961346</v>
+        <v>122971413</v>
       </c>
       <c r="B198" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22996,34 +22990,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>459218</v>
+        <v>459013</v>
       </c>
       <c r="R198" t="n">
-        <v>7031359</v>
+        <v>7031443</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23053,9 +23047,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23070,22 +23079,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122988609</v>
+        <v>122970161</v>
       </c>
       <c r="B199" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -23098,34 +23107,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>458845</v>
+        <v>459355</v>
       </c>
       <c r="R199" t="n">
-        <v>7031403</v>
+        <v>7031426</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23160,6 +23169,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
@@ -23168,26 +23182,51 @@
       </c>
       <c r="AG199" t="b">
         <v>0</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122958513</v>
+        <v>122961954</v>
       </c>
       <c r="B200" t="n">
-        <v>74849</v>
+        <v>56680</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -23196,38 +23235,48 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>306</v>
+        <v>102612</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>459544</v>
+        <v>459411</v>
       </c>
       <c r="R200" t="n">
-        <v>7031238</v>
+        <v>7031295</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23257,24 +23306,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23286,40 +23325,30 @@
       <c r="AG200" t="b">
         <v>0</v>
       </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122959882</v>
+        <v>122988632</v>
       </c>
       <c r="B201" t="n">
-        <v>78845</v>
+        <v>79883</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23328,52 +23357,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>459439</v>
+        <v>459229</v>
       </c>
       <c r="R201" t="n">
-        <v>7031261</v>
+        <v>7031281</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23403,24 +23418,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23435,22 +23435,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122988647</v>
+        <v>122964182</v>
       </c>
       <c r="B202" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23463,34 +23463,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>459096</v>
+        <v>459389</v>
       </c>
       <c r="R202" t="n">
-        <v>7031557</v>
+        <v>7031331</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23525,6 +23525,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>På en gran där det även växer rikligt med lunglav.</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -23533,26 +23538,51 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122968728</v>
+        <v>122960215</v>
       </c>
       <c r="B203" t="n">
-        <v>79384</v>
+        <v>90970</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23565,34 +23595,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>459140</v>
+        <v>459403</v>
       </c>
       <c r="R203" t="n">
-        <v>7031307</v>
+        <v>7031251</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23624,7 +23654,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23634,12 +23664,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>På ved av lutade bränd tallhögstubbe</t>
+          <t>På gammal gran i gammal sumpgranskog vid bäck</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23654,22 +23684,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122968503</v>
+        <v>122963043</v>
       </c>
       <c r="B204" t="n">
-        <v>79384</v>
+        <v>79848</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23682,37 +23712,42 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>459372</v>
+        <v>459415</v>
       </c>
       <c r="R204" t="n">
-        <v>7031370</v>
+        <v>7031339</v>
       </c>
       <c r="S204" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23739,24 +23774,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal barrblandskog</t>
+          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23767,26 +23792,51 @@
       </c>
       <c r="AG204" t="b">
         <v>0</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122967968</v>
+        <v>122959139</v>
       </c>
       <c r="B205" t="n">
-        <v>74863</v>
+        <v>77709</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23799,37 +23849,37 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>459057</v>
+        <v>459493</v>
       </c>
       <c r="R205" t="n">
-        <v>7031331</v>
+        <v>7031246</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23858,7 +23908,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23868,12 +23918,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på undersidan av död gren på gammal levande gran (14 cm dbh, ca 160 år gammal) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23884,26 +23934,41 @@
       </c>
       <c r="AG205" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122988605</v>
+        <v>122968157</v>
       </c>
       <c r="B206" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23916,34 +23981,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>459515</v>
+        <v>459185</v>
       </c>
       <c r="R206" t="n">
-        <v>7031218</v>
+        <v>7031279</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23973,9 +24038,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23990,22 +24070,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122974681</v>
+        <v>122973324</v>
       </c>
       <c r="B207" t="n">
-        <v>79883</v>
+        <v>77699</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24014,41 +24094,41 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>459157</v>
+        <v>459137</v>
       </c>
       <c r="R207" t="n">
-        <v>7031692</v>
+        <v>7031595</v>
       </c>
       <c r="S207" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -24077,7 +24157,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -24087,12 +24167,12 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal gransumpskog vid bäck</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24107,22 +24187,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122972459</v>
+        <v>122988647</v>
       </c>
       <c r="B208" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24135,37 +24215,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>459056</v>
+        <v>459096</v>
       </c>
       <c r="R208" t="n">
-        <v>7031578</v>
+        <v>7031557</v>
       </c>
       <c r="S208" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -24192,24 +24272,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24224,22 +24289,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122962699</v>
+        <v>122968728</v>
       </c>
       <c r="B209" t="n">
-        <v>79883</v>
+        <v>79384</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -24248,46 +24313,41 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>459414</v>
+        <v>459140</v>
       </c>
       <c r="R209" t="n">
-        <v>7031347</v>
+        <v>7031307</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24314,11 +24374,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>På ved av lutade bränd tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
@@ -24327,51 +24402,26 @@
       </c>
       <c r="AG209" t="b">
         <v>0</v>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122970576</v>
+        <v>122968503</v>
       </c>
       <c r="B210" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -24384,37 +24434,37 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>459023</v>
+        <v>459372</v>
       </c>
       <c r="R210" t="n">
-        <v>7031279</v>
+        <v>7031370</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24443,7 +24493,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -24453,12 +24503,12 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På ved på gammal tallhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24473,22 +24523,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122988622</v>
+        <v>122967968</v>
       </c>
       <c r="B211" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24501,42 +24551,37 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>459013</v>
+        <v>459057</v>
       </c>
       <c r="R211" t="n">
-        <v>7031407</v>
+        <v>7031331</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24563,14 +24608,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>I midjehöjd i senvuxen gran i gles sumpskog.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24585,22 +24640,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122969084</v>
+        <v>122988605</v>
       </c>
       <c r="B212" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24613,39 +24668,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>458878</v>
+        <v>459515</v>
       </c>
       <c r="R212" t="n">
-        <v>7031241</v>
+        <v>7031218</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24680,11 +24730,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
@@ -24697,22 +24742,22 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122968157</v>
+        <v>122974681</v>
       </c>
       <c r="B213" t="n">
-        <v>77699</v>
+        <v>79883</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24721,41 +24766,41 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>459185</v>
+        <v>459157</v>
       </c>
       <c r="R213" t="n">
-        <v>7031279</v>
+        <v>7031692</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24784,7 +24829,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24794,12 +24839,12 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24814,22 +24859,22 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122973324</v>
+        <v>122972459</v>
       </c>
       <c r="B214" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24842,37 +24887,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>459137</v>
+        <v>459056</v>
       </c>
       <c r="R214" t="n">
-        <v>7031595</v>
+        <v>7031578</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24901,7 +24946,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24911,12 +24956,12 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal gransumpskog vid bäck</t>
+          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24931,22 +24976,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122964182</v>
+        <v>122962699</v>
       </c>
       <c r="B215" t="n">
-        <v>79848</v>
+        <v>79883</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24955,41 +25000,46 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>459389</v>
+        <v>459414</v>
       </c>
       <c r="R215" t="n">
-        <v>7031331</v>
+        <v>7031347</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -25021,11 +25071,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>På en gran där det även växer rikligt med lunglav.</t>
-        </is>
-      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
@@ -25042,22 +25087,22 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr"/>
@@ -25075,10 +25120,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122960215</v>
+        <v>122970576</v>
       </c>
       <c r="B216" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -25091,34 +25136,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>459403</v>
+        <v>459023</v>
       </c>
       <c r="R216" t="n">
-        <v>7031251</v>
+        <v>7031279</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25150,7 +25195,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -25160,12 +25205,12 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal sumpgranskog vid bäck</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25180,22 +25225,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122963043</v>
+        <v>122988622</v>
       </c>
       <c r="B217" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -25208,42 +25253,42 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>459415</v>
+        <v>459013</v>
       </c>
       <c r="R217" t="n">
-        <v>7031339</v>
+        <v>7031407</v>
       </c>
       <c r="S217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -25277,7 +25322,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
+          <t>I midjehöjd i senvuxen gran i gles sumpskog.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25288,51 +25333,26 @@
       </c>
       <c r="AG217" t="b">
         <v>0</v>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122959139</v>
+        <v>122969084</v>
       </c>
       <c r="B218" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -25345,37 +25365,42 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>459493</v>
+        <v>458878</v>
       </c>
       <c r="R218" t="n">
-        <v>7031246</v>
+        <v>7031241</v>
       </c>
       <c r="S218" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25402,24 +25427,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran (14 cm dbh, ca 160 år gammal) i gammal granskog vid bäck</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25430,31 +25445,16 @@
       </c>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
@@ -35614,10 +35614,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122962441</v>
+        <v>123010799</v>
       </c>
       <c r="B307" t="n">
-        <v>91890</v>
+        <v>82553</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -35626,45 +35626,38 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>459345</v>
+        <v>459399</v>
       </c>
       <c r="R307" t="n">
-        <v>7031322</v>
+        <v>7031218</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -35696,7 +35689,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -35706,12 +35699,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC307" t="inlineStr">
-        <is>
-          <t>På marken längs med bäck, gamla fruktkroppar från hösten 2024</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -35720,29 +35708,28 @@
       <c r="AE307" t="b">
         <v>0</v>
       </c>
-      <c r="AF307" t="inlineStr"/>
       <c r="AG307" t="b">
         <v>0</v>
       </c>
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122968192</v>
+        <v>123010752</v>
       </c>
       <c r="B308" t="n">
-        <v>74858</v>
+        <v>78766</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -35755,37 +35742,34 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>459419</v>
+        <v>459136</v>
       </c>
       <c r="R308" t="n">
-        <v>7031354</v>
+        <v>7031333</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -35817,7 +35801,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -35827,12 +35811,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -35841,29 +35820,28 @@
       <c r="AE308" t="b">
         <v>0</v>
       </c>
-      <c r="AF308" t="inlineStr"/>
       <c r="AG308" t="b">
         <v>0</v>
       </c>
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122973098</v>
+        <v>122962441</v>
       </c>
       <c r="B309" t="n">
-        <v>78847</v>
+        <v>91890</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -35872,38 +35850,45 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>459120</v>
+        <v>459345</v>
       </c>
       <c r="R309" t="n">
-        <v>7031572</v>
+        <v>7031322</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -35935,7 +35920,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -35945,12 +35930,12 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>På tunna grenar på gammal levande gran (1 cm dbh) i gammal gransumpskog</t>
+          <t>På marken längs med bäck, gamla fruktkroppar från hösten 2024</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -35959,23 +35944,9 @@
       <c r="AE309" t="b">
         <v>0</v>
       </c>
+      <c r="AF309" t="inlineStr"/>
       <c r="AG309" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ309" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK309" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO309" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
@@ -35992,10 +35963,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>123010799</v>
+        <v>122968192</v>
       </c>
       <c r="B310" t="n">
-        <v>82553</v>
+        <v>74858</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -36008,34 +35979,37 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1312</v>
+        <v>310</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>459399</v>
+        <v>459419</v>
       </c>
       <c r="R310" t="n">
-        <v>7031218</v>
+        <v>7031354</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -36067,7 +36041,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -36077,7 +36051,12 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -36086,28 +36065,29 @@
       <c r="AE310" t="b">
         <v>0</v>
       </c>
+      <c r="AF310" t="inlineStr"/>
       <c r="AG310" t="b">
         <v>0</v>
       </c>
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>123010752</v>
+        <v>122973098</v>
       </c>
       <c r="B311" t="n">
-        <v>78766</v>
+        <v>78847</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -36120,34 +36100,34 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>459136</v>
+        <v>459120</v>
       </c>
       <c r="R311" t="n">
-        <v>7031333</v>
+        <v>7031572</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -36179,7 +36159,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -36189,7 +36169,12 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>På tunna grenar på gammal levande gran (1 cm dbh) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -36200,16 +36185,31 @@
       </c>
       <c r="AG311" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
@@ -38652,10 +38652,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>123010810</v>
+        <v>123010815</v>
       </c>
       <c r="B333" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -38668,21 +38668,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -38692,10 +38692,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>459550</v>
+        <v>459547</v>
       </c>
       <c r="R333" t="n">
-        <v>7031204</v>
+        <v>7031215</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -38727,7 +38727,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -38764,10 +38764,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>123010815</v>
+        <v>123010810</v>
       </c>
       <c r="B334" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -38780,21 +38780,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -38804,10 +38804,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>459547</v>
+        <v>459550</v>
       </c>
       <c r="R334" t="n">
-        <v>7031215</v>
+        <v>7031204</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -38839,7 +38839,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -38849,7 +38849,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -39446,10 +39446,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>123010800</v>
+        <v>123010764</v>
       </c>
       <c r="B340" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -39462,21 +39462,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -39486,10 +39486,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>459400</v>
+        <v>459027</v>
       </c>
       <c r="R340" t="n">
-        <v>7031215</v>
+        <v>7031097</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -39521,7 +39521,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -39531,7 +39531,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -39558,7 +39558,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>123010751</v>
+        <v>123010800</v>
       </c>
       <c r="B341" t="n">
         <v>78766</v>
@@ -39598,10 +39598,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>459111</v>
+        <v>459400</v>
       </c>
       <c r="R341" t="n">
-        <v>7031436</v>
+        <v>7031215</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -39633,7 +39633,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -39643,7 +39643,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -39670,10 +39670,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122963099</v>
+        <v>123010751</v>
       </c>
       <c r="B342" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -39682,54 +39682,38 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>459295</v>
+        <v>459111</v>
       </c>
       <c r="R342" t="n">
-        <v>7031196</v>
+        <v>7031436</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -39761,7 +39745,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -39771,12 +39755,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC342" t="inlineStr">
-        <is>
-          <t>Fyra gröna plantor och 1 vinterståndare på marken i gammal barrblandskog</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -39785,29 +39764,28 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
-      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
       <c r="AT342" t="inlineStr"/>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>123010764</v>
+        <v>122963099</v>
       </c>
       <c r="B343" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -39816,38 +39794,54 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>459027</v>
+        <v>459295</v>
       </c>
       <c r="R343" t="n">
-        <v>7031097</v>
+        <v>7031196</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -39879,7 +39873,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -39889,7 +39883,12 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>Fyra gröna plantor och 1 vinterståndare på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -39898,18 +39897,19 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -4626,10 +4626,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122973517</v>
+        <v>122969276</v>
       </c>
       <c r="B36" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4642,37 +4642,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459211</v>
+        <v>458861</v>
       </c>
       <c r="R36" t="n">
-        <v>7031461</v>
+        <v>7031270</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4704,6 +4709,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4712,31 +4722,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4753,10 +4738,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122960709</v>
+        <v>122988627</v>
       </c>
       <c r="B37" t="n">
-        <v>90984</v>
+        <v>56081</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4769,34 +4754,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459258</v>
+        <v>458807</v>
       </c>
       <c r="R37" t="n">
-        <v>7031322</v>
+        <v>7031401</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4843,22 +4828,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122958541</v>
+        <v>122973517</v>
       </c>
       <c r="B38" t="n">
-        <v>90984</v>
+        <v>78775</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4871,21 +4856,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4895,13 +4880,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459525</v>
+        <v>459211</v>
       </c>
       <c r="R38" t="n">
-        <v>7031282</v>
+        <v>7031461</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4941,6 +4926,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4957,10 +4967,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122969276</v>
+        <v>122960709</v>
       </c>
       <c r="B39" t="n">
-        <v>57481</v>
+        <v>90984</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4973,39 +4983,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>458861</v>
+        <v>459258</v>
       </c>
       <c r="R39" t="n">
-        <v>7031270</v>
+        <v>7031322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5038,11 +5043,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122988627</v>
+        <v>122958541</v>
       </c>
       <c r="B40" t="n">
-        <v>56081</v>
+        <v>90984</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5085,34 +5085,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458807</v>
+        <v>459525</v>
       </c>
       <c r="R40" t="n">
-        <v>7031401</v>
+        <v>7031282</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5159,12 +5159,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122963646</v>
+        <v>122988628</v>
       </c>
       <c r="B45" t="n">
-        <v>78420</v>
+        <v>97333</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5651,38 +5651,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459232</v>
+        <v>458859</v>
       </c>
       <c r="R45" t="n">
-        <v>7031163</v>
+        <v>7031389</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5729,22 +5729,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122988607</v>
+        <v>122963646</v>
       </c>
       <c r="B46" t="n">
-        <v>90966</v>
+        <v>78420</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5757,34 +5757,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458882</v>
+        <v>459232</v>
       </c>
       <c r="R46" t="n">
-        <v>7031377</v>
+        <v>7031163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5831,22 +5831,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122969437</v>
+        <v>122988607</v>
       </c>
       <c r="B47" t="n">
-        <v>74860</v>
+        <v>90966</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5855,55 +5855,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459333</v>
+        <v>458882</v>
       </c>
       <c r="R47" t="n">
-        <v>7031413</v>
+        <v>7031377</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5930,24 +5916,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt på ved på gammal björkhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5962,19 +5933,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122959877</v>
+        <v>122969437</v>
       </c>
       <c r="B48" t="n">
         <v>74860</v>
@@ -6007,20 +5978,34 @@
           <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459316</v>
+        <v>459333</v>
       </c>
       <c r="R48" t="n">
-        <v>7031273</v>
+        <v>7031413</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6047,9 +6032,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt på ved på gammal björkhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6064,22 +6064,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122988659</v>
+        <v>122959877</v>
       </c>
       <c r="B49" t="n">
-        <v>78775</v>
+        <v>74860</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6088,38 +6088,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458995</v>
+        <v>459316</v>
       </c>
       <c r="R49" t="n">
-        <v>7031695</v>
+        <v>7031273</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6166,22 +6166,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122973197</v>
+        <v>122988659</v>
       </c>
       <c r="B50" t="n">
-        <v>79856</v>
+        <v>78775</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6194,37 +6194,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459229</v>
+        <v>458995</v>
       </c>
       <c r="R50" t="n">
-        <v>7031473</v>
+        <v>7031695</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6256,11 +6256,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På en gran intill en gammal sälg med fertil lunglav.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6269,51 +6264,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122969465</v>
+        <v>122973197</v>
       </c>
       <c r="B51" t="n">
-        <v>74869</v>
+        <v>79856</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,21 +6296,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6350,13 +6320,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459206</v>
+        <v>459229</v>
       </c>
       <c r="R51" t="n">
-        <v>7031330</v>
+        <v>7031473</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6383,24 +6353,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På tjock gammal gran</t>
+          <t>På en gran intill en gammal sälg med fertil lunglav.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6411,26 +6371,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122968031</v>
+        <v>122969465</v>
       </c>
       <c r="B52" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6443,42 +6428,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459187</v>
+        <v>459206</v>
       </c>
       <c r="R52" t="n">
-        <v>7031105</v>
+        <v>7031330</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6505,9 +6485,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tjock gammal gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6522,19 +6517,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122960090</v>
+        <v>122968031</v>
       </c>
       <c r="B53" t="n">
         <v>78775</v>
@@ -6568,16 +6563,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459481</v>
+        <v>459187</v>
       </c>
       <c r="R53" t="n">
-        <v>7031293</v>
+        <v>7031105</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6607,19 +6607,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6634,22 +6624,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122972658</v>
+        <v>122960090</v>
       </c>
       <c r="B54" t="n">
-        <v>79856</v>
+        <v>78775</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6662,34 +6652,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459098</v>
+        <v>459481</v>
       </c>
       <c r="R54" t="n">
-        <v>7031549</v>
+        <v>7031293</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6719,9 +6709,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6736,22 +6736,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122988614</v>
+        <v>122972658</v>
       </c>
       <c r="B55" t="n">
-        <v>57481</v>
+        <v>79856</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6764,39 +6764,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459069</v>
+        <v>459098</v>
       </c>
       <c r="R55" t="n">
-        <v>7031625</v>
+        <v>7031549</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6843,22 +6838,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122964396</v>
+        <v>122988614</v>
       </c>
       <c r="B56" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6871,16 +6866,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6896,14 +6891,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459368</v>
+        <v>459069</v>
       </c>
       <c r="R56" t="n">
-        <v>7031265</v>
+        <v>7031625</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6938,11 +6933,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6951,51 +6941,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122988628</v>
+        <v>122964396</v>
       </c>
       <c r="B57" t="n">
-        <v>97333</v>
+        <v>57497</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7004,38 +6969,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458859</v>
+        <v>459368</v>
       </c>
       <c r="R57" t="n">
-        <v>7031389</v>
+        <v>7031265</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7070,6 +7040,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7078,16 +7053,41 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -12214,10 +12214,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122972459</v>
+        <v>122974179</v>
       </c>
       <c r="B102" t="n">
-        <v>79856</v>
+        <v>79857</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12230,37 +12230,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>459056</v>
+        <v>459242</v>
       </c>
       <c r="R102" t="n">
-        <v>7031578</v>
+        <v>7031483</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12287,24 +12292,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På nedfallen sälg</t>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12315,26 +12310,51 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122974179</v>
+        <v>122961591</v>
       </c>
       <c r="B103" t="n">
-        <v>79857</v>
+        <v>78775</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12347,42 +12367,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>459242</v>
+        <v>459379</v>
       </c>
       <c r="R103" t="n">
-        <v>7031483</v>
+        <v>7031278</v>
       </c>
       <c r="S103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12409,14 +12424,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>Rikligt på gammal gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12427,51 +12452,26 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122961591</v>
+        <v>122975225</v>
       </c>
       <c r="B104" t="n">
-        <v>78775</v>
+        <v>79245</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12484,37 +12484,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>459379</v>
+        <v>459052</v>
       </c>
       <c r="R104" t="n">
-        <v>7031278</v>
+        <v>7031667</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog vid bäck</t>
+          <t>På bark på stam av levande gammal gran, vid basen,  i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12585,10 +12585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122975225</v>
+        <v>122972586</v>
       </c>
       <c r="B105" t="n">
-        <v>79245</v>
+        <v>78775</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12601,37 +12601,41 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>459052</v>
+        <v>459094</v>
       </c>
       <c r="R105" t="n">
-        <v>7031667</v>
+        <v>7031545</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12658,24 +12662,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran, vid basen,  i gammal granskog vid bäck</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12690,22 +12684,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122972586</v>
+        <v>122971514</v>
       </c>
       <c r="B106" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12718,38 +12712,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1000</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459094</v>
+        <v>459123</v>
       </c>
       <c r="R106" t="n">
-        <v>7031545</v>
+        <v>7031364</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12786,7 +12781,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12813,10 +12808,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122970288</v>
+        <v>122970443</v>
       </c>
       <c r="B107" t="n">
-        <v>79892</v>
+        <v>57481</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12825,41 +12820,46 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459169</v>
+        <v>459134</v>
       </c>
       <c r="R107" t="n">
-        <v>7031397</v>
+        <v>7031419</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12930,7 +12930,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122971514</v>
+        <v>122968756</v>
       </c>
       <c r="B108" t="n">
         <v>57481</v>
@@ -12966,7 +12966,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>459123</v>
+        <v>458952</v>
       </c>
       <c r="R108" t="n">
-        <v>7031364</v>
+        <v>7031223</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13042,7 +13042,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122970443</v>
+        <v>122973064</v>
       </c>
       <c r="B109" t="n">
         <v>57481</v>
@@ -13078,22 +13078,22 @@
       <c r="I109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>459134</v>
+        <v>459078</v>
       </c>
       <c r="R109" t="n">
-        <v>7031419</v>
+        <v>7031631</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13120,24 +13120,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13152,22 +13142,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122968756</v>
+        <v>122970288</v>
       </c>
       <c r="B110" t="n">
-        <v>57481</v>
+        <v>79892</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13176,46 +13166,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458952</v>
+        <v>459169</v>
       </c>
       <c r="R110" t="n">
-        <v>7031223</v>
+        <v>7031397</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13242,14 +13227,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13264,22 +13259,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122973064</v>
+        <v>122972459</v>
       </c>
       <c r="B111" t="n">
-        <v>57481</v>
+        <v>79856</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13292,42 +13287,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459078</v>
+        <v>459056</v>
       </c>
       <c r="R111" t="n">
-        <v>7031631</v>
+        <v>7031578</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13354,14 +13344,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13376,12 +13376,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13592,10 +13592,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122968686</v>
+        <v>122969185</v>
       </c>
       <c r="B114" t="n">
-        <v>79891</v>
+        <v>78775</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13604,20 +13604,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -13628,14 +13628,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>459364</v>
+        <v>459114</v>
       </c>
       <c r="R114" t="n">
-        <v>7031404</v>
+        <v>7031298</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13677,12 +13677,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13697,22 +13692,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122969185</v>
+        <v>122960048</v>
       </c>
       <c r="B115" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13725,21 +13720,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13749,13 +13744,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>459114</v>
+        <v>459483</v>
       </c>
       <c r="R115" t="n">
-        <v>7031298</v>
+        <v>7031282</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13784,7 +13779,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13794,7 +13789,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 17 cm i diameter</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13821,7 +13821,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122960048</v>
+        <v>122960512</v>
       </c>
       <c r="B116" t="n">
         <v>74869</v>
@@ -13861,10 +13861,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>459483</v>
+        <v>459447</v>
       </c>
       <c r="R116" t="n">
-        <v>7031282</v>
+        <v>7031281</v>
       </c>
       <c r="S116" t="n">
         <v>7</v>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På gammal gran ca 17 cm i diameter</t>
+          <t>På gammal gran ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13938,10 +13938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122960512</v>
+        <v>122988656</v>
       </c>
       <c r="B117" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13954,37 +13954,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>459447</v>
+        <v>459032</v>
       </c>
       <c r="R117" t="n">
-        <v>7031281</v>
+        <v>7031453</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14011,24 +14011,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14043,22 +14028,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122988656</v>
+        <v>122972105</v>
       </c>
       <c r="B118" t="n">
-        <v>78775</v>
+        <v>56691</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14067,41 +14052,56 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>459032</v>
+        <v>459267</v>
       </c>
       <c r="R118" t="n">
-        <v>7031453</v>
+        <v>7031413</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14133,6 +14133,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Gott om spillning (uppåt ca 1x7 cm) på ca 7 m2 yta under en tall med utglesad krona med tydliga tecken på tjäderns födosök.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -14141,26 +14146,31 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122967974</v>
+        <v>122968686</v>
       </c>
       <c r="B119" t="n">
-        <v>74869</v>
+        <v>79891</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14169,38 +14179,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>459199</v>
+        <v>459364</v>
       </c>
       <c r="R119" t="n">
-        <v>7031090</v>
+        <v>7031404</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14230,9 +14240,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14247,22 +14272,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122972105</v>
+        <v>122967974</v>
       </c>
       <c r="B120" t="n">
-        <v>56691</v>
+        <v>74869</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14271,56 +14296,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>459267</v>
+        <v>459199</v>
       </c>
       <c r="R120" t="n">
-        <v>7031413</v>
+        <v>7031090</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14352,11 +14362,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Gott om spillning (uppåt ca 1x7 cm) på ca 7 m2 yta under en tall med utglesad krona med tydliga tecken på tjäderns födosök.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14365,11 +14370,6 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -14600,10 +14600,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122958831</v>
+        <v>122968592</v>
       </c>
       <c r="B123" t="n">
-        <v>79031</v>
+        <v>82562</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14612,46 +14612,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6459</v>
+        <v>1312</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>459540</v>
+        <v>459172</v>
       </c>
       <c r="R123" t="n">
-        <v>7031232</v>
+        <v>7031415</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14680,7 +14675,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14690,12 +14685,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>På klen äldre gran</t>
+          <t>På svagt lutande gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14710,22 +14705,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122959266</v>
+        <v>122988624</v>
       </c>
       <c r="B124" t="n">
-        <v>78775</v>
+        <v>91659</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14734,38 +14729,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>459462</v>
+        <v>459021</v>
       </c>
       <c r="R124" t="n">
-        <v>7031193</v>
+        <v>7031753</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14809,25 +14804,30 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Klen, knäckt gran.</t>
+        </is>
+      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122967669</v>
+        <v>122988647</v>
       </c>
       <c r="B125" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14840,34 +14840,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>459238</v>
+        <v>459096</v>
       </c>
       <c r="R125" t="n">
-        <v>7031254</v>
+        <v>7031557</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14897,24 +14897,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 18 cm i diameter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14929,22 +14914,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122988601</v>
+        <v>122988666</v>
       </c>
       <c r="B126" t="n">
-        <v>74869</v>
+        <v>82562</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14957,21 +14942,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14981,10 +14966,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>458858</v>
+        <v>459327</v>
       </c>
       <c r="R126" t="n">
-        <v>7031397</v>
+        <v>7031306</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15043,10 +15028,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122969870</v>
+        <v>122988661</v>
       </c>
       <c r="B127" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15059,34 +15044,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>459089</v>
+        <v>458998</v>
       </c>
       <c r="R127" t="n">
-        <v>7031327</v>
+        <v>7031366</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15116,24 +15101,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15148,22 +15118,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122970190</v>
+        <v>122962434</v>
       </c>
       <c r="B128" t="n">
-        <v>74869</v>
+        <v>79857</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15176,37 +15146,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>459221</v>
+        <v>459411</v>
       </c>
       <c r="R128" t="n">
-        <v>7031408</v>
+        <v>7031335</v>
       </c>
       <c r="S128" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15233,24 +15208,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15261,26 +15226,51 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122961150</v>
+        <v>122961664</v>
       </c>
       <c r="B129" t="n">
-        <v>78775</v>
+        <v>74861</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15293,37 +15283,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>459430</v>
+        <v>459375</v>
       </c>
       <c r="R129" t="n">
-        <v>7031287</v>
+        <v>7031277</v>
       </c>
       <c r="S129" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15352,7 +15342,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15362,7 +15352,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På innerbark vid basen av gammal björkhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15377,22 +15372,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122968592</v>
+        <v>122958831</v>
       </c>
       <c r="B130" t="n">
-        <v>82562</v>
+        <v>79031</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15401,41 +15396,46 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1312</v>
+        <v>6459</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>459172</v>
+        <v>459540</v>
       </c>
       <c r="R130" t="n">
-        <v>7031415</v>
+        <v>7031232</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15474,12 +15474,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>På svagt lutande gran</t>
+          <t>På klen äldre gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15494,22 +15494,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122988624</v>
+        <v>122959266</v>
       </c>
       <c r="B131" t="n">
-        <v>91659</v>
+        <v>78775</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15518,38 +15518,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>459021</v>
+        <v>459462</v>
       </c>
       <c r="R131" t="n">
-        <v>7031753</v>
+        <v>7031193</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15593,30 +15593,25 @@
       <c r="AG131" t="b">
         <v>0</v>
       </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Klen, knäckt gran.</t>
-        </is>
-      </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122988647</v>
+        <v>122967669</v>
       </c>
       <c r="B132" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15629,34 +15624,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>459096</v>
+        <v>459238</v>
       </c>
       <c r="R132" t="n">
-        <v>7031557</v>
+        <v>7031254</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15686,9 +15681,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 18 cm i diameter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15703,22 +15713,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122988666</v>
+        <v>122988601</v>
       </c>
       <c r="B133" t="n">
-        <v>82562</v>
+        <v>74869</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15731,21 +15741,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15755,10 +15765,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>459327</v>
+        <v>458858</v>
       </c>
       <c r="R133" t="n">
-        <v>7031306</v>
+        <v>7031397</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15817,10 +15827,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122988661</v>
+        <v>122969870</v>
       </c>
       <c r="B134" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15833,34 +15843,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>458998</v>
+        <v>459089</v>
       </c>
       <c r="R134" t="n">
-        <v>7031366</v>
+        <v>7031327</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15890,9 +15900,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15907,22 +15932,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122962434</v>
+        <v>122970190</v>
       </c>
       <c r="B135" t="n">
-        <v>79857</v>
+        <v>74869</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15935,42 +15960,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>459411</v>
+        <v>459221</v>
       </c>
       <c r="R135" t="n">
-        <v>7031335</v>
+        <v>7031408</v>
       </c>
       <c r="S135" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15997,14 +16017,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16015,51 +16045,26 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122961664</v>
+        <v>122961150</v>
       </c>
       <c r="B136" t="n">
-        <v>74861</v>
+        <v>78775</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16072,37 +16077,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>459375</v>
+        <v>459430</v>
       </c>
       <c r="R136" t="n">
-        <v>7031277</v>
+        <v>7031287</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16131,7 +16136,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16141,12 +16146,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>På innerbark vid basen av gammal björkhögstubbe i gammal granskog vid bäck</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16161,12 +16161,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -16285,10 +16285,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122959785</v>
+        <v>122961346</v>
       </c>
       <c r="B138" t="n">
-        <v>77708</v>
+        <v>82562</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16301,21 +16301,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16325,10 +16325,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>459495</v>
+        <v>459218</v>
       </c>
       <c r="R138" t="n">
-        <v>7031265</v>
+        <v>7031359</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16358,24 +16358,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På gammal gran 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16390,22 +16375,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122961346</v>
+        <v>122960794</v>
       </c>
       <c r="B139" t="n">
-        <v>82562</v>
+        <v>95925</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16418,21 +16403,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16442,10 +16427,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>459218</v>
+        <v>459259</v>
       </c>
       <c r="R139" t="n">
-        <v>7031359</v>
+        <v>7031322</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16504,10 +16489,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122960794</v>
+        <v>122972416</v>
       </c>
       <c r="B140" t="n">
-        <v>95925</v>
+        <v>78775</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16520,21 +16505,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16544,10 +16529,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>459259</v>
+        <v>459239</v>
       </c>
       <c r="R140" t="n">
-        <v>7031322</v>
+        <v>7031397</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16582,6 +16567,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Gott om bålar på många granar.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -16590,6 +16580,31 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -16606,10 +16621,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122972416</v>
+        <v>122958910</v>
       </c>
       <c r="B141" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16622,34 +16637,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>459239</v>
+        <v>459496</v>
       </c>
       <c r="R141" t="n">
-        <v>7031397</v>
+        <v>7031207</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16686,7 +16706,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Gott om bålar på många granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16697,31 +16717,6 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -16738,10 +16733,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122988642</v>
+        <v>122963217</v>
       </c>
       <c r="B142" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16754,34 +16749,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>458897</v>
+        <v>459236</v>
       </c>
       <c r="R142" t="n">
-        <v>7031354</v>
+        <v>7031209</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16816,6 +16816,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16828,22 +16833,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122959133</v>
+        <v>122971788</v>
       </c>
       <c r="B143" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16856,37 +16861,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>459510</v>
+        <v>459134</v>
       </c>
       <c r="R143" t="n">
-        <v>7031239</v>
+        <v>7031417</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16913,24 +16923,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>På gammal gran 15 cm I diameter</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16945,22 +16945,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122967256</v>
+        <v>122973351</v>
       </c>
       <c r="B144" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16973,34 +16973,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>459232</v>
+        <v>459019</v>
       </c>
       <c r="R144" t="n">
-        <v>7031241</v>
+        <v>7031671</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17030,19 +17035,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17057,22 +17057,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122970966</v>
+        <v>122961954</v>
       </c>
       <c r="B145" t="n">
-        <v>79856</v>
+        <v>56683</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17085,27 +17085,32 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -17114,13 +17119,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>459064</v>
+        <v>459411</v>
       </c>
       <c r="R145" t="n">
-        <v>7031505</v>
+        <v>7031295</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17147,24 +17152,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På nedfallen, gammal sälg</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17175,23 +17170,28 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122988641</v>
+        <v>122988642</v>
       </c>
       <c r="B146" t="n">
         <v>78775</v>
@@ -17231,10 +17231,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>459415</v>
+        <v>458897</v>
       </c>
       <c r="R146" t="n">
-        <v>7031212</v>
+        <v>7031354</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17293,10 +17293,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122958910</v>
+        <v>122959133</v>
       </c>
       <c r="B147" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17309,42 +17309,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>459496</v>
+        <v>459510</v>
       </c>
       <c r="R147" t="n">
-        <v>7031207</v>
+        <v>7031239</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17371,14 +17366,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran 15 cm I diameter</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17393,22 +17398,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122963217</v>
+        <v>122967256</v>
       </c>
       <c r="B148" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17421,39 +17426,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>459236</v>
+        <v>459232</v>
       </c>
       <c r="R148" t="n">
-        <v>7031209</v>
+        <v>7031241</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17483,14 +17483,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17505,22 +17510,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122971788</v>
+        <v>122970966</v>
       </c>
       <c r="B149" t="n">
-        <v>57481</v>
+        <v>79856</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17533,27 +17538,27 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17562,13 +17567,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>459134</v>
+        <v>459064</v>
       </c>
       <c r="R149" t="n">
-        <v>7031417</v>
+        <v>7031505</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17595,14 +17600,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På nedfallen, gammal sälg</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17617,22 +17632,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122973351</v>
+        <v>122988641</v>
       </c>
       <c r="B150" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17645,39 +17660,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>459019</v>
+        <v>459415</v>
       </c>
       <c r="R150" t="n">
-        <v>7031671</v>
+        <v>7031212</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17712,11 +17722,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -17729,22 +17734,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122961954</v>
+        <v>122959785</v>
       </c>
       <c r="B151" t="n">
-        <v>56683</v>
+        <v>77708</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17757,44 +17762,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>459411</v>
+        <v>459495</v>
       </c>
       <c r="R151" t="n">
-        <v>7031295</v>
+        <v>7031265</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17824,14 +17819,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>På gammal gran 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17842,21 +17847,16 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -29270,10 +29270,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122970876</v>
+        <v>122960501</v>
       </c>
       <c r="B252" t="n">
-        <v>90984</v>
+        <v>77708</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -29286,21 +29286,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -29310,13 +29310,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>459100</v>
+        <v>459391</v>
       </c>
       <c r="R252" t="n">
-        <v>7031235</v>
+        <v>7031231</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -29343,9 +29343,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29360,22 +29375,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122958511</v>
+        <v>122970637</v>
       </c>
       <c r="B253" t="n">
-        <v>90984</v>
+        <v>77708</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -29388,21 +29403,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -29412,10 +29427,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>459522</v>
+        <v>459026</v>
       </c>
       <c r="R253" t="n">
-        <v>7031275</v>
+        <v>7031279</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29445,9 +29460,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29462,22 +29492,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122970161</v>
+        <v>122973324</v>
       </c>
       <c r="B254" t="n">
-        <v>78775</v>
+        <v>77708</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -29490,37 +29520,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>459355</v>
+        <v>459137</v>
       </c>
       <c r="R254" t="n">
-        <v>7031426</v>
+        <v>7031595</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -29547,14 +29577,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal gran i gammal gransumpskog vid bäck</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29565,51 +29605,26 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122960970</v>
+        <v>122961835</v>
       </c>
       <c r="B255" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -29622,21 +29637,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -29646,13 +29661,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>459435</v>
+        <v>459291</v>
       </c>
       <c r="R255" t="n">
-        <v>7031306</v>
+        <v>7031124</v>
       </c>
       <c r="S255" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29679,11 +29694,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>På kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD255" t="b">
         <v>0</v>
       </c>
@@ -29692,51 +29722,26 @@
       </c>
       <c r="AG255" t="b">
         <v>0</v>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO255" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122962307</v>
+        <v>122971254</v>
       </c>
       <c r="B256" t="n">
-        <v>79892</v>
+        <v>57481</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -29745,31 +29750,31 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29778,10 +29783,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>459411</v>
+        <v>459152</v>
       </c>
       <c r="R256" t="n">
-        <v>7031338</v>
+        <v>7031320</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29818,7 +29823,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>På en liggande levande smal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29829,31 +29834,6 @@
       </c>
       <c r="AG256" t="b">
         <v>0</v>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
@@ -29870,10 +29850,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122959894</v>
+        <v>122988622</v>
       </c>
       <c r="B257" t="n">
-        <v>74853</v>
+        <v>57481</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -29882,38 +29862,43 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>459316</v>
+        <v>459013</v>
       </c>
       <c r="R257" t="n">
-        <v>7031273</v>
+        <v>7031407</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29948,6 +29933,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>I midjehöjd i senvuxen gran i gles sumpskog.</t>
+        </is>
+      </c>
       <c r="AD257" t="b">
         <v>0</v>
       </c>
@@ -29960,22 +29950,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122988632</v>
+        <v>122973327</v>
       </c>
       <c r="B258" t="n">
-        <v>79892</v>
+        <v>57481</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -29984,38 +29974,43 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>459229</v>
+        <v>459017</v>
       </c>
       <c r="R258" t="n">
-        <v>7031281</v>
+        <v>7031666</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -30050,6 +30045,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD258" t="b">
         <v>0</v>
       </c>
@@ -30062,22 +30062,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122973383</v>
+        <v>122962195</v>
       </c>
       <c r="B259" t="n">
-        <v>79856</v>
+        <v>57481</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -30090,37 +30090,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>458999</v>
+        <v>459158</v>
       </c>
       <c r="R259" t="n">
-        <v>7031647</v>
+        <v>7031220</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -30147,9 +30152,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30164,22 +30184,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122988631</v>
+        <v>122970876</v>
       </c>
       <c r="B260" t="n">
-        <v>79856</v>
+        <v>90984</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -30192,34 +30212,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>458987</v>
+        <v>459100</v>
       </c>
       <c r="R260" t="n">
-        <v>7031383</v>
+        <v>7031235</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30266,22 +30286,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122970576</v>
+        <v>122958511</v>
       </c>
       <c r="B261" t="n">
-        <v>74869</v>
+        <v>90984</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -30294,21 +30314,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -30318,10 +30338,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>459023</v>
+        <v>459522</v>
       </c>
       <c r="R261" t="n">
-        <v>7031279</v>
+        <v>7031275</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30351,24 +30371,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30383,22 +30388,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122971254</v>
+        <v>122970161</v>
       </c>
       <c r="B262" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -30411,39 +30416,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>459152</v>
+        <v>459355</v>
       </c>
       <c r="R262" t="n">
-        <v>7031320</v>
+        <v>7031426</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30480,7 +30480,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30491,6 +30491,31 @@
       </c>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
@@ -30507,10 +30532,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122988622</v>
+        <v>122960970</v>
       </c>
       <c r="B263" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -30523,42 +30548,37 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>459013</v>
+        <v>459435</v>
       </c>
       <c r="R263" t="n">
-        <v>7031407</v>
+        <v>7031306</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -30590,11 +30610,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>I midjehöjd i senvuxen gran i gles sumpskog.</t>
-        </is>
-      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
@@ -30603,26 +30618,51 @@
       </c>
       <c r="AG263" t="b">
         <v>0</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122973327</v>
+        <v>122962307</v>
       </c>
       <c r="B264" t="n">
-        <v>57481</v>
+        <v>79892</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -30631,43 +30671,43 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>459017</v>
+        <v>459411</v>
       </c>
       <c r="R264" t="n">
-        <v>7031666</v>
+        <v>7031338</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30704,7 +30744,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en liggande levande smal sälg.</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30715,6 +30755,31 @@
       </c>
       <c r="AG264" t="b">
         <v>0</v>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
@@ -30731,10 +30796,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122962195</v>
+        <v>122959894</v>
       </c>
       <c r="B265" t="n">
-        <v>57481</v>
+        <v>74853</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -30743,46 +30808,41 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>459158</v>
+        <v>459316</v>
       </c>
       <c r="R265" t="n">
-        <v>7031220</v>
+        <v>7031273</v>
       </c>
       <c r="S265" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30809,24 +30869,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30841,22 +30886,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122988635</v>
+        <v>122988632</v>
       </c>
       <c r="B266" t="n">
-        <v>98379</v>
+        <v>79892</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -30865,47 +30910,38 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>459043</v>
+        <v>459229</v>
       </c>
       <c r="R266" t="n">
-        <v>7031643</v>
+        <v>7031281</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30964,10 +31000,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122960501</v>
+        <v>122973383</v>
       </c>
       <c r="B267" t="n">
-        <v>77708</v>
+        <v>79856</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -30980,37 +31016,37 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>459391</v>
+        <v>458999</v>
       </c>
       <c r="R267" t="n">
-        <v>7031231</v>
+        <v>7031647</v>
       </c>
       <c r="S267" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -31037,24 +31073,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -31069,22 +31090,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122970637</v>
+        <v>122988631</v>
       </c>
       <c r="B268" t="n">
-        <v>77708</v>
+        <v>79856</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -31097,34 +31118,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>459026</v>
+        <v>458987</v>
       </c>
       <c r="R268" t="n">
-        <v>7031279</v>
+        <v>7031383</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31154,24 +31175,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31186,22 +31192,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122973324</v>
+        <v>122970576</v>
       </c>
       <c r="B269" t="n">
-        <v>77708</v>
+        <v>74869</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -31214,37 +31220,37 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>459137</v>
+        <v>459023</v>
       </c>
       <c r="R269" t="n">
-        <v>7031595</v>
+        <v>7031279</v>
       </c>
       <c r="S269" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -31273,7 +31279,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -31283,12 +31289,12 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal gransumpskog vid bäck</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31303,22 +31309,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122961835</v>
+        <v>122988635</v>
       </c>
       <c r="B270" t="n">
-        <v>78512</v>
+        <v>98379</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -31327,41 +31333,50 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>459291</v>
+        <v>459043</v>
       </c>
       <c r="R270" t="n">
-        <v>7031124</v>
+        <v>7031643</v>
       </c>
       <c r="S270" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -31388,24 +31403,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31420,12 +31420,12 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
@@ -34764,10 +34764,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>123010770</v>
+        <v>123010786</v>
       </c>
       <c r="B300" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -34780,21 +34780,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -34804,10 +34804,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>459079</v>
+        <v>459165</v>
       </c>
       <c r="R300" t="n">
-        <v>7031108</v>
+        <v>7031178</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34839,7 +34839,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -34849,7 +34849,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34876,10 +34876,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>123010786</v>
+        <v>123010770</v>
       </c>
       <c r="B301" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -34892,21 +34892,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -34916,10 +34916,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>459165</v>
+        <v>459079</v>
       </c>
       <c r="R301" t="n">
-        <v>7031178</v>
+        <v>7031108</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -34951,7 +34951,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -39182,10 +39182,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122972997</v>
+        <v>123010758</v>
       </c>
       <c r="B338" t="n">
-        <v>78854</v>
+        <v>78775</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -39198,46 +39198,37 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>459111</v>
+        <v>458964</v>
       </c>
       <c r="R338" t="n">
-        <v>7031582</v>
+        <v>7031183</v>
       </c>
       <c r="S338" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -39266,7 +39257,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -39276,12 +39267,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>På döda grenar på gamla granar i gammal granskog</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39292,41 +39278,26 @@
       </c>
       <c r="AG338" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ338" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK338" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO338" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>123010758</v>
+        <v>123010778</v>
       </c>
       <c r="B339" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -39339,34 +39310,39 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>458964</v>
+        <v>459160</v>
       </c>
       <c r="R339" t="n">
-        <v>7031183</v>
+        <v>7031091</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -39398,7 +39374,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -39408,7 +39384,12 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -39435,10 +39416,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>123010778</v>
+        <v>123010774</v>
       </c>
       <c r="B340" t="n">
-        <v>57481</v>
+        <v>77708</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -39451,39 +39432,34 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P340" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>459160</v>
+        <v>459131</v>
       </c>
       <c r="R340" t="n">
-        <v>7031091</v>
+        <v>7031087</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -39515,7 +39491,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -39525,12 +39501,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -39557,10 +39528,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>123010774</v>
+        <v>122972997</v>
       </c>
       <c r="B341" t="n">
-        <v>77708</v>
+        <v>78854</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -39573,37 +39544,46 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>228579</v>
+        <v>864</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>459131</v>
+        <v>459111</v>
       </c>
       <c r="R341" t="n">
-        <v>7031087</v>
+        <v>7031582</v>
       </c>
       <c r="S341" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -39632,7 +39612,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -39642,7 +39622,12 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>På döda grenar på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -39653,16 +39638,31 @@
       </c>
       <c r="AG341" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK341" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO341" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT341" t="inlineStr"/>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122967256</v>
+        <v>122958513</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>74861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459232</v>
+        <v>459544</v>
       </c>
       <c r="R2" t="n">
-        <v>7031241</v>
+        <v>7031238</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,26 +776,41 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122973321</v>
+        <v>122959882</v>
       </c>
       <c r="B3" t="n">
-        <v>74875</v>
+        <v>78860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +823,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459145</v>
+        <v>459439</v>
       </c>
       <c r="R3" t="n">
-        <v>7031597</v>
+        <v>7031261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +926,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122960709</v>
+        <v>122967256</v>
       </c>
       <c r="B4" t="n">
-        <v>91001</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +954,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459258</v>
+        <v>459232</v>
       </c>
       <c r="R4" t="n">
-        <v>7031322</v>
+        <v>7031241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,9 +1011,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,19 +1038,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122967968</v>
+        <v>122973321</v>
       </c>
       <c r="B5" t="n">
         <v>74875</v>
@@ -1046,13 +1090,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459057</v>
+        <v>459145</v>
       </c>
       <c r="R5" t="n">
-        <v>7031331</v>
+        <v>7031597</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1135,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1155,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122988642</v>
+        <v>122960709</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>91001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1183,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458897</v>
+        <v>459258</v>
       </c>
       <c r="R6" t="n">
-        <v>7031354</v>
+        <v>7031322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122963043</v>
+        <v>122967968</v>
       </c>
       <c r="B7" t="n">
-        <v>79863</v>
+        <v>74875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,42 +1285,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459415</v>
+        <v>459057</v>
       </c>
       <c r="R7" t="n">
-        <v>7031339</v>
+        <v>7031331</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,14 +1342,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,51 +1370,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122962699</v>
+        <v>122988642</v>
       </c>
       <c r="B8" t="n">
-        <v>79898</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,46 +1398,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459414</v>
+        <v>458897</v>
       </c>
       <c r="R8" t="n">
-        <v>7031347</v>
+        <v>7031354</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,51 +1472,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122958513</v>
+        <v>122963043</v>
       </c>
       <c r="B9" t="n">
-        <v>74861</v>
+        <v>79863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,41 +1500,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459544</v>
+        <v>459415</v>
       </c>
       <c r="R9" t="n">
-        <v>7031238</v>
+        <v>7031339</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,24 +1566,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På insidan av murken björkhögstubbe i gammal granskog på fuktig mark</t>
+          <t>På en sälg med 37 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,40 +1585,50 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122959882</v>
+        <v>122962699</v>
       </c>
       <c r="B10" t="n">
-        <v>78860</v>
+        <v>79898</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,40 +1637,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1680,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459439</v>
+        <v>459414</v>
       </c>
       <c r="R10" t="n">
-        <v>7031261</v>
+        <v>7031347</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,26 +1703,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1741,16 +1716,41 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122988653</v>
+        <v>122972658</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,34 +1885,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459438</v>
+        <v>459098</v>
       </c>
       <c r="R12" t="n">
-        <v>7031232</v>
+        <v>7031549</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,22 +1959,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122975225</v>
+        <v>122971604</v>
       </c>
       <c r="B13" t="n">
-        <v>79251</v>
+        <v>79890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1797</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459052</v>
+        <v>458996</v>
       </c>
       <c r="R13" t="n">
-        <v>7031667</v>
+        <v>7031467</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran, vid basen,  i gammal granskog vid bäck</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122988658</v>
+        <v>122968114</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,34 +2104,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458928</v>
+        <v>459106</v>
       </c>
       <c r="R14" t="n">
-        <v>7031321</v>
+        <v>7031128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,6 +2171,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2178,22 +2188,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122988639</v>
+        <v>122970443</v>
       </c>
       <c r="B15" t="n">
-        <v>91001</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,37 +2216,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459572</v>
+        <v>459134</v>
       </c>
       <c r="R15" t="n">
-        <v>7031236</v>
+        <v>7031419</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2263,9 +2278,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,22 +2310,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122972658</v>
+        <v>122988621</v>
       </c>
       <c r="B16" t="n">
-        <v>79862</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,34 +2338,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459098</v>
+        <v>459222</v>
       </c>
       <c r="R16" t="n">
-        <v>7031549</v>
+        <v>7031244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,22 +2417,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122971604</v>
+        <v>122988614</v>
       </c>
       <c r="B17" t="n">
-        <v>79890</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,38 +2441,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458996</v>
+        <v>459069</v>
       </c>
       <c r="R17" t="n">
-        <v>7031467</v>
+        <v>7031625</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,24 +2507,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,22 +2524,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122968114</v>
+        <v>122958211</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>77714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,39 +2552,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459106</v>
+        <v>459591</v>
       </c>
       <c r="R18" t="n">
-        <v>7031128</v>
+        <v>7031255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,14 +2609,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,22 +2641,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970443</v>
+        <v>122973324</v>
       </c>
       <c r="B19" t="n">
-        <v>57487</v>
+        <v>77714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,42 +2669,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459134</v>
+        <v>459137</v>
       </c>
       <c r="R19" t="n">
-        <v>7031419</v>
+        <v>7031595</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,12 +2738,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På bark på stam av levande gammal gran i gammal gransumpskog vid bäck</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,22 +2758,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122988621</v>
+        <v>122988653</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,39 +2786,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459222</v>
+        <v>459438</v>
       </c>
       <c r="R20" t="n">
-        <v>7031244</v>
+        <v>7031232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2852,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122988614</v>
+        <v>122975225</v>
       </c>
       <c r="B21" t="n">
-        <v>57487</v>
+        <v>79251</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,42 +2888,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1797</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459069</v>
+        <v>459052</v>
       </c>
       <c r="R21" t="n">
-        <v>7031625</v>
+        <v>7031667</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2930,9 +2945,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran, vid basen,  i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,22 +2977,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122958211</v>
+        <v>122988658</v>
       </c>
       <c r="B22" t="n">
-        <v>77714</v>
+        <v>78781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,34 +3005,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459591</v>
+        <v>458928</v>
       </c>
       <c r="R22" t="n">
-        <v>7031255</v>
+        <v>7031321</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,24 +3062,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,22 +3079,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122973324</v>
+        <v>122988639</v>
       </c>
       <c r="B23" t="n">
-        <v>77714</v>
+        <v>91001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,37 +3107,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459137</v>
+        <v>459572</v>
       </c>
       <c r="R23" t="n">
-        <v>7031595</v>
+        <v>7031236</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,24 +3164,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal gransumpskog vid bäck</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,12 +3181,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122959466</v>
+        <v>122961313</v>
       </c>
       <c r="B36" t="n">
-        <v>74866</v>
+        <v>91001</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4549,46 +4549,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459466</v>
+        <v>459398</v>
       </c>
       <c r="R36" t="n">
-        <v>7031243</v>
+        <v>7031291</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4617,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4627,12 +4622,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe vid bäck</t>
+          <t>På levande gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4647,22 +4642,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122961313</v>
+        <v>122959133</v>
       </c>
       <c r="B37" t="n">
-        <v>91001</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4675,21 +4670,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,13 +4694,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459398</v>
+        <v>459510</v>
       </c>
       <c r="R37" t="n">
-        <v>7031291</v>
+        <v>7031239</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4734,7 +4729,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,12 +4739,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På levande gran ca 15 cm i diameter</t>
+          <t>På gammal gran 15 cm I diameter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4776,10 +4771,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122959133</v>
+        <v>122988600</v>
       </c>
       <c r="B38" t="n">
-        <v>78781</v>
+        <v>74875</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4792,37 +4787,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459510</v>
+        <v>459372</v>
       </c>
       <c r="R38" t="n">
-        <v>7031239</v>
+        <v>7031245</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4849,24 +4844,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal gran 15 cm I diameter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4881,22 +4861,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122988600</v>
+        <v>122972616</v>
       </c>
       <c r="B39" t="n">
-        <v>74875</v>
+        <v>57487</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4909,37 +4889,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459372</v>
+        <v>459060</v>
       </c>
       <c r="R39" t="n">
-        <v>7031245</v>
+        <v>7031573</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4966,9 +4951,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4983,22 +4983,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122988628</v>
+        <v>122969276</v>
       </c>
       <c r="B40" t="n">
-        <v>97350</v>
+        <v>57487</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5007,38 +5007,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458859</v>
+        <v>458861</v>
       </c>
       <c r="R40" t="n">
-        <v>7031389</v>
+        <v>7031270</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5073,6 +5078,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5085,22 +5095,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122968514</v>
+        <v>122958278</v>
       </c>
       <c r="B41" t="n">
-        <v>77714</v>
+        <v>57487</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5113,34 +5123,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459137</v>
+        <v>459570</v>
       </c>
       <c r="R41" t="n">
-        <v>7031302</v>
+        <v>7031254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5170,24 +5185,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran ca 20 cm i diameter</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5202,22 +5207,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122960501</v>
+        <v>122971140</v>
       </c>
       <c r="B42" t="n">
-        <v>77714</v>
+        <v>56689</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5230,37 +5235,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459391</v>
+        <v>459300</v>
       </c>
       <c r="R42" t="n">
-        <v>7031231</v>
+        <v>7031390</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5287,24 +5297,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Färsk spillning på snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,26 +5315,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122960503</v>
+        <v>122959466</v>
       </c>
       <c r="B43" t="n">
-        <v>79037</v>
+        <v>74866</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5343,41 +5348,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6459</v>
+        <v>492</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459393</v>
+        <v>459466</v>
       </c>
       <c r="R43" t="n">
-        <v>7031232</v>
+        <v>7031243</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5406,7 +5416,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,12 +5426,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe vid bäck</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5458,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122974666</v>
+        <v>122960503</v>
       </c>
       <c r="B44" t="n">
-        <v>79862</v>
+        <v>79037</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5460,41 +5470,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459159</v>
+        <v>459393</v>
       </c>
       <c r="R44" t="n">
-        <v>7031681</v>
+        <v>7031232</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5523,7 +5533,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,12 +5543,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På död gren på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5553,19 +5563,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122974415</v>
+        <v>122974666</v>
       </c>
       <c r="B45" t="n">
         <v>79862</v>
@@ -5601,14 +5611,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459245</v>
+        <v>459159</v>
       </c>
       <c r="R45" t="n">
-        <v>7031472</v>
+        <v>7031681</v>
       </c>
       <c r="S45" t="n">
         <v>11</v>
@@ -5638,14 +5648,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en gran intill en grov gammal lutande sälg med lunglav.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5656,51 +5676,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122972616</v>
+        <v>122974415</v>
       </c>
       <c r="B46" t="n">
-        <v>57487</v>
+        <v>79862</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5713,42 +5708,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Offerdal, Jo-Nilsvallen, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459060</v>
+        <v>459245</v>
       </c>
       <c r="R46" t="n">
-        <v>7031573</v>
+        <v>7031472</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5775,24 +5765,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På en gran intill en grov gammal lutande sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5803,26 +5783,51 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122969276</v>
+        <v>122988628</v>
       </c>
       <c r="B47" t="n">
-        <v>57487</v>
+        <v>97350</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5831,43 +5836,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458861</v>
+        <v>458859</v>
       </c>
       <c r="R47" t="n">
-        <v>7031270</v>
+        <v>7031389</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5902,11 +5902,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5919,22 +5914,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122958278</v>
+        <v>122968514</v>
       </c>
       <c r="B48" t="n">
-        <v>57487</v>
+        <v>77714</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5947,39 +5942,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459570</v>
+        <v>459137</v>
       </c>
       <c r="R48" t="n">
-        <v>7031254</v>
+        <v>7031302</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6009,14 +5999,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6031,22 +6031,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122971140</v>
+        <v>122960501</v>
       </c>
       <c r="B49" t="n">
-        <v>56689</v>
+        <v>77714</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6059,42 +6059,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459300</v>
+        <v>459391</v>
       </c>
       <c r="R49" t="n">
-        <v>7031390</v>
+        <v>7031231</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6121,14 +6116,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färsk spillning på snötäcket.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6139,21 +6144,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122960642</v>
+        <v>122988635</v>
       </c>
       <c r="B99" t="n">
-        <v>80734</v>
+        <v>98396</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11814,38 +11814,47 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>459396</v>
+        <v>459043</v>
       </c>
       <c r="R99" t="n">
-        <v>7031227</v>
+        <v>7031643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11875,24 +11884,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På lucker ved på gammal dimensionsavverkningsstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11907,22 +11901,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122988635</v>
+        <v>122960642</v>
       </c>
       <c r="B100" t="n">
-        <v>98396</v>
+        <v>80734</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11931,47 +11925,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>459043</v>
+        <v>459396</v>
       </c>
       <c r="R100" t="n">
-        <v>7031643</v>
+        <v>7031227</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12001,9 +11986,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På lucker ved på gammal dimensionsavverkningsstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12018,12 +12018,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -17799,10 +17799,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122972474</v>
+        <v>122970966</v>
       </c>
       <c r="B151" t="n">
-        <v>91676</v>
+        <v>79862</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17811,41 +17811,46 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>459051</v>
+        <v>459064</v>
       </c>
       <c r="R151" t="n">
-        <v>7031523</v>
+        <v>7031505</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17872,9 +17877,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På nedfallen, gammal sälg</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17889,22 +17909,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122959139</v>
+        <v>122971013</v>
       </c>
       <c r="B152" t="n">
-        <v>77724</v>
+        <v>79862</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17917,21 +17937,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17941,13 +17961,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>459493</v>
+        <v>459018</v>
       </c>
       <c r="R152" t="n">
-        <v>7031246</v>
+        <v>7031385</v>
       </c>
       <c r="S152" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17976,7 +17996,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17986,12 +18006,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran (14 cm dbh, ca 160 år gammal) i gammal granskog vid bäck</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18002,21 +18022,6 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -18033,10 +18038,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122963217</v>
+        <v>122968293</v>
       </c>
       <c r="B153" t="n">
-        <v>57487</v>
+        <v>79862</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18049,42 +18054,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>459236</v>
+        <v>459120</v>
       </c>
       <c r="R153" t="n">
-        <v>7031209</v>
+        <v>7031399</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18111,14 +18111,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18133,19 +18143,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122963067</v>
+        <v>122963217</v>
       </c>
       <c r="B154" t="n">
         <v>57487</v>
@@ -18190,10 +18200,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>459234</v>
+        <v>459236</v>
       </c>
       <c r="R154" t="n">
-        <v>7031238</v>
+        <v>7031209</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18257,7 +18267,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122988620</v>
+        <v>122963067</v>
       </c>
       <c r="B155" t="n">
         <v>57487</v>
@@ -18298,14 +18308,14 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>459240</v>
+        <v>459234</v>
       </c>
       <c r="R155" t="n">
-        <v>7031331</v>
+        <v>7031238</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18340,6 +18350,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -18352,22 +18367,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122972105</v>
+        <v>122988620</v>
       </c>
       <c r="B156" t="n">
-        <v>56697</v>
+        <v>57487</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18376,56 +18391,46 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>459267</v>
+        <v>459240</v>
       </c>
       <c r="R156" t="n">
-        <v>7031413</v>
+        <v>7031331</v>
       </c>
       <c r="S156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18457,11 +18462,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Gott om spillning (uppåt ca 1x7 cm) på ca 7 m2 yta under en tall med utglesad krona med tydliga tecken på tjäderns födosök.</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -18470,31 +18470,26 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122968756</v>
+        <v>122972105</v>
       </c>
       <c r="B157" t="n">
-        <v>57487</v>
+        <v>56697</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18503,31 +18498,41 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18536,13 +18541,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>458952</v>
+        <v>459267</v>
       </c>
       <c r="R157" t="n">
-        <v>7031223</v>
+        <v>7031413</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18576,7 +18581,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om spillning (uppåt ca 1x7 cm) på ca 7 m2 yta under en tall med utglesad krona med tydliga tecken på tjäderns födosök.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18587,6 +18592,11 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
@@ -18603,10 +18613,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122969909</v>
+        <v>122968756</v>
       </c>
       <c r="B158" t="n">
-        <v>56697</v>
+        <v>57487</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18615,40 +18625,31 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18657,10 +18658,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>458792</v>
+        <v>458952</v>
       </c>
       <c r="R158" t="n">
-        <v>7031270</v>
+        <v>7031223</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18693,6 +18694,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18719,10 +18725,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122960006</v>
+        <v>122969909</v>
       </c>
       <c r="B159" t="n">
-        <v>78781</v>
+        <v>56697</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18731,41 +18737,55 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>459491</v>
+        <v>458792</v>
       </c>
       <c r="R159" t="n">
-        <v>7031303</v>
+        <v>7031270</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18805,31 +18825,6 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
@@ -18846,10 +18841,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122969870</v>
+        <v>122961835</v>
       </c>
       <c r="B160" t="n">
-        <v>74875</v>
+        <v>78518</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18862,21 +18857,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18886,13 +18881,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>459089</v>
+        <v>459291</v>
       </c>
       <c r="R160" t="n">
-        <v>7031327</v>
+        <v>7031124</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18921,7 +18916,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18931,12 +18926,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>På gammal gran ca 15 cm i diameter</t>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18951,22 +18946,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122988647</v>
+        <v>122972474</v>
       </c>
       <c r="B161" t="n">
-        <v>78781</v>
+        <v>91676</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18975,38 +18970,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>459096</v>
+        <v>459051</v>
       </c>
       <c r="R161" t="n">
-        <v>7031557</v>
+        <v>7031523</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19053,22 +19048,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122968403</v>
+        <v>122959139</v>
       </c>
       <c r="B162" t="n">
-        <v>78781</v>
+        <v>77724</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19081,37 +19076,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>459474</v>
+        <v>459493</v>
       </c>
       <c r="R162" t="n">
-        <v>7031344</v>
+        <v>7031246</v>
       </c>
       <c r="S162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19138,11 +19133,26 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>På bark på undersidan av död gren på gammal levande gran (14 cm dbh, ca 160 år gammal) i gammal granskog vid bäck</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -19152,11 +19162,6 @@
       <c r="AG162" t="b">
         <v>0</v>
       </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ162" t="inlineStr">
         <is>
           <t>gran</t>
@@ -19167,32 +19172,27 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122988651</v>
+        <v>122960006</v>
       </c>
       <c r="B163" t="n">
         <v>78781</v>
@@ -19228,17 +19228,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>459404</v>
+        <v>459491</v>
       </c>
       <c r="R163" t="n">
-        <v>7031192</v>
+        <v>7031303</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19278,26 +19278,51 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122972459</v>
+        <v>122969870</v>
       </c>
       <c r="B164" t="n">
-        <v>79862</v>
+        <v>74875</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19310,21 +19335,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19334,13 +19359,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>459056</v>
+        <v>459089</v>
       </c>
       <c r="R164" t="n">
-        <v>7031578</v>
+        <v>7031327</v>
       </c>
       <c r="S164" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19369,7 +19394,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19379,12 +19404,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På nedfallen sälg</t>
+          <t>På gammal gran ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19399,22 +19424,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122967565</v>
+        <v>122988647</v>
       </c>
       <c r="B165" t="n">
-        <v>82568</v>
+        <v>78781</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19427,37 +19452,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>459190</v>
+        <v>459096</v>
       </c>
       <c r="R165" t="n">
-        <v>7031278</v>
+        <v>7031557</v>
       </c>
       <c r="S165" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19484,24 +19509,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På lite lutande gran</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19516,22 +19526,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122973197</v>
+        <v>122968403</v>
       </c>
       <c r="B166" t="n">
-        <v>79862</v>
+        <v>78781</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19544,21 +19554,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19568,13 +19578,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>459229</v>
+        <v>459474</v>
       </c>
       <c r="R166" t="n">
-        <v>7031473</v>
+        <v>7031344</v>
       </c>
       <c r="S166" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19604,11 +19614,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>På en gran intill en gammal sälg med fertil lunglav.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19660,10 +19665,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122958245</v>
+        <v>122988651</v>
       </c>
       <c r="B167" t="n">
-        <v>74875</v>
+        <v>78781</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19676,37 +19681,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>459590</v>
+        <v>459404</v>
       </c>
       <c r="R167" t="n">
-        <v>7031260</v>
+        <v>7031192</v>
       </c>
       <c r="S167" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19733,24 +19738,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19765,19 +19755,19 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122970966</v>
+        <v>122972459</v>
       </c>
       <c r="B168" t="n">
         <v>79862</v>
@@ -19811,24 +19801,19 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>459064</v>
+        <v>459056</v>
       </c>
       <c r="R168" t="n">
-        <v>7031505</v>
+        <v>7031578</v>
       </c>
       <c r="S168" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19857,7 +19842,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19867,12 +19852,12 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>På nedfallen, gammal sälg</t>
+          <t>På nedfallen sälg</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19892,17 +19877,17 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122971013</v>
+        <v>122967565</v>
       </c>
       <c r="B169" t="n">
-        <v>79862</v>
+        <v>82568</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19915,37 +19900,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>459018</v>
+        <v>459190</v>
       </c>
       <c r="R169" t="n">
-        <v>7031385</v>
+        <v>7031278</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19974,7 +19959,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19984,12 +19969,12 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På lite lutande gran</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20004,19 +19989,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122968293</v>
+        <v>122973197</v>
       </c>
       <c r="B170" t="n">
         <v>79862</v>
@@ -20056,13 +20041,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>459120</v>
+        <v>459229</v>
       </c>
       <c r="R170" t="n">
-        <v>7031399</v>
+        <v>7031473</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20089,24 +20074,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På en gran intill en gammal sälg med fertil lunglav.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20117,26 +20092,51 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122961835</v>
+        <v>122958245</v>
       </c>
       <c r="B171" t="n">
-        <v>78518</v>
+        <v>74875</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -20149,21 +20149,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -20173,13 +20173,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>459291</v>
+        <v>459590</v>
       </c>
       <c r="R171" t="n">
-        <v>7031124</v>
+        <v>7031260</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -20218,12 +20218,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>På kolad stubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21950,10 +21950,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122970354</v>
+        <v>122971514</v>
       </c>
       <c r="B187" t="n">
-        <v>79862</v>
+        <v>57487</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21966,34 +21966,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>459170</v>
+        <v>459123</v>
       </c>
       <c r="R187" t="n">
-        <v>7031379</v>
+        <v>7031364</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22023,24 +22028,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22055,19 +22050,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122988631</v>
+        <v>122970354</v>
       </c>
       <c r="B188" t="n">
         <v>79862</v>
@@ -22103,14 +22098,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>458987</v>
+        <v>459170</v>
       </c>
       <c r="R188" t="n">
-        <v>7031383</v>
+        <v>7031379</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22140,9 +22135,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -22157,22 +22167,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122971514</v>
+        <v>122988631</v>
       </c>
       <c r="B189" t="n">
-        <v>57487</v>
+        <v>79862</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -22185,39 +22195,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>459123</v>
+        <v>458987</v>
       </c>
       <c r="R189" t="n">
-        <v>7031364</v>
+        <v>7031383</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22252,11 +22257,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -22269,12 +22269,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -24248,10 +24248,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122968278</v>
+        <v>122970661</v>
       </c>
       <c r="B207" t="n">
-        <v>78518</v>
+        <v>79862</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24264,21 +24264,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -24288,13 +24288,13 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>459059</v>
+        <v>459099</v>
       </c>
       <c r="R207" t="n">
-        <v>7031142</v>
+        <v>7031510</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -24321,9 +24321,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>På gammal sälg och på gran</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24338,22 +24353,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122961361</v>
+        <v>122961711</v>
       </c>
       <c r="B208" t="n">
-        <v>78518</v>
+        <v>56689</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24366,34 +24381,44 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>459379</v>
+        <v>459420</v>
       </c>
       <c r="R208" t="n">
-        <v>7031278</v>
+        <v>7031306</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24423,24 +24448,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov tallhögstubbe i gammal granskog vid bäck</t>
+          <t>Färsk spillning ovanpå snön. I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24451,26 +24466,31 @@
       </c>
       <c r="AG208" t="b">
         <v>0</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122970661</v>
+        <v>122968278</v>
       </c>
       <c r="B209" t="n">
-        <v>79862</v>
+        <v>78518</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -24483,21 +24503,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -24507,13 +24527,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>459099</v>
+        <v>459059</v>
       </c>
       <c r="R209" t="n">
-        <v>7031510</v>
+        <v>7031142</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24540,24 +24560,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>På gammal sälg och på gran</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24572,22 +24577,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122961711</v>
+        <v>122961361</v>
       </c>
       <c r="B210" t="n">
-        <v>56689</v>
+        <v>78518</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -24600,44 +24605,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>459420</v>
+        <v>459379</v>
       </c>
       <c r="R210" t="n">
-        <v>7031306</v>
+        <v>7031278</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24667,14 +24662,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snön. I flerskiktad gammal granskog.</t>
+          <t>På kolad ved på gammal grov tallhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24685,31 +24690,26 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122960043</v>
+        <v>122968241</v>
       </c>
       <c r="B211" t="n">
-        <v>95942</v>
+        <v>79862</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24722,21 +24722,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24746,10 +24746,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>459290</v>
+        <v>459060</v>
       </c>
       <c r="R211" t="n">
-        <v>7031285</v>
+        <v>7031144</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24782,6 +24782,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24808,10 +24813,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122969437</v>
+        <v>122988632</v>
       </c>
       <c r="B212" t="n">
-        <v>74866</v>
+        <v>79898</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24820,55 +24825,41 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>492</v>
+        <v>6464</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>459333</v>
+        <v>459229</v>
       </c>
       <c r="R212" t="n">
-        <v>7031413</v>
+        <v>7031281</v>
       </c>
       <c r="S212" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -24895,24 +24886,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Rikligt på ved på gammal björkhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24927,22 +24903,22 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122988609</v>
+        <v>122968704</v>
       </c>
       <c r="B213" t="n">
-        <v>90983</v>
+        <v>79862</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24955,34 +24931,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>458845</v>
+        <v>459364</v>
       </c>
       <c r="R213" t="n">
-        <v>7031403</v>
+        <v>7031404</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25012,9 +24988,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25029,19 +25020,19 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122968241</v>
+        <v>122973126</v>
       </c>
       <c r="B214" t="n">
         <v>79862</v>
@@ -25077,14 +25068,14 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>459060</v>
+        <v>459081</v>
       </c>
       <c r="R214" t="n">
-        <v>7031144</v>
+        <v>7031628</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25117,11 +25108,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25148,10 +25134,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122988632</v>
+        <v>122964051</v>
       </c>
       <c r="B215" t="n">
-        <v>79898</v>
+        <v>79862</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -25160,38 +25146,43 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>459229</v>
+        <v>459393</v>
       </c>
       <c r="R215" t="n">
-        <v>7031281</v>
+        <v>7031334</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25226,6 +25217,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
@@ -25234,26 +25230,51 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122968704</v>
+        <v>122988617</v>
       </c>
       <c r="B216" t="n">
-        <v>79862</v>
+        <v>57487</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -25266,34 +25287,39 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, N. om, , Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>459364</v>
+        <v>459070</v>
       </c>
       <c r="R216" t="n">
-        <v>7031404</v>
+        <v>7031592</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25323,24 +25349,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25355,22 +25366,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122973126</v>
+        <v>122961680</v>
       </c>
       <c r="B217" t="n">
-        <v>79862</v>
+        <v>57640</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -25383,34 +25394,48 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>459081</v>
+        <v>459214</v>
       </c>
       <c r="R217" t="n">
-        <v>7031628</v>
+        <v>7031327</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25469,10 +25494,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122964051</v>
+        <v>122962124</v>
       </c>
       <c r="B218" t="n">
-        <v>79862</v>
+        <v>78518</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -25485,42 +25510,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>459393</v>
+        <v>459228</v>
       </c>
       <c r="R218" t="n">
-        <v>7031334</v>
+        <v>7031174</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25547,14 +25567,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
+          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25565,51 +25595,26 @@
       </c>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122969425</v>
+        <v>122960043</v>
       </c>
       <c r="B219" t="n">
-        <v>78781</v>
+        <v>95942</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25622,21 +25627,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -25646,10 +25651,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>458819</v>
+        <v>459290</v>
       </c>
       <c r="R219" t="n">
-        <v>7031282</v>
+        <v>7031285</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25708,10 +25713,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122960216</v>
+        <v>122969437</v>
       </c>
       <c r="B220" t="n">
-        <v>78781</v>
+        <v>74866</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25720,41 +25725,55 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>459482</v>
+        <v>459333</v>
       </c>
       <c r="R220" t="n">
-        <v>7031303</v>
+        <v>7031413</v>
       </c>
       <c r="S220" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -25781,14 +25800,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt på ved på gammal björkhögstubbe i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25799,51 +25828,26 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122958541</v>
+        <v>122988609</v>
       </c>
       <c r="B221" t="n">
-        <v>91001</v>
+        <v>90983</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25856,34 +25860,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>459525</v>
+        <v>458845</v>
       </c>
       <c r="R221" t="n">
-        <v>7031282</v>
+        <v>7031403</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25930,22 +25934,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122988617</v>
+        <v>122969425</v>
       </c>
       <c r="B222" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25958,39 +25962,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>459070</v>
+        <v>458819</v>
       </c>
       <c r="R222" t="n">
-        <v>7031592</v>
+        <v>7031282</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26037,22 +26036,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122961680</v>
+        <v>122960216</v>
       </c>
       <c r="B223" t="n">
-        <v>57640</v>
+        <v>78781</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -26065,51 +26064,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>459214</v>
+        <v>459482</v>
       </c>
       <c r="R223" t="n">
-        <v>7031327</v>
+        <v>7031303</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -26141,6 +26126,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -26149,6 +26139,31 @@
       </c>
       <c r="AG223" t="b">
         <v>0</v>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
@@ -26165,10 +26180,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122962124</v>
+        <v>122958541</v>
       </c>
       <c r="B224" t="n">
-        <v>78518</v>
+        <v>91001</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -26181,21 +26196,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -26205,13 +26220,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>459228</v>
+        <v>459525</v>
       </c>
       <c r="R224" t="n">
-        <v>7031174</v>
+        <v>7031282</v>
       </c>
       <c r="S224" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -26238,24 +26253,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>På kolad stubbe</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26270,12 +26270,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
@@ -28990,10 +28990,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122988607</v>
+        <v>122962736</v>
       </c>
       <c r="B249" t="n">
-        <v>90983</v>
+        <v>79897</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -29002,41 +29002,41 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>458882</v>
+        <v>459417</v>
       </c>
       <c r="R249" t="n">
-        <v>7031377</v>
+        <v>7031346</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -29076,26 +29076,51 @@
       </c>
       <c r="AG249" t="b">
         <v>0</v>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122988657</v>
+        <v>122988669</v>
       </c>
       <c r="B250" t="n">
-        <v>78781</v>
+        <v>77709</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -29108,21 +29133,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -29132,10 +29157,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>459055</v>
+        <v>459002</v>
       </c>
       <c r="R250" t="n">
-        <v>7031634</v>
+        <v>7031384</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29194,10 +29219,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122971004</v>
+        <v>122988629</v>
       </c>
       <c r="B251" t="n">
-        <v>78781</v>
+        <v>79862</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -29210,51 +29235,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>459301</v>
+        <v>458990</v>
       </c>
       <c r="R251" t="n">
-        <v>7031350</v>
+        <v>7031684</v>
       </c>
       <c r="S251" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -29286,11 +29297,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Rikligt med långväxta bålar på många granar. Fertila bålar med apothecier förekommer.</t>
-        </is>
-      </c>
       <c r="AD251" t="b">
         <v>0</v>
       </c>
@@ -29299,51 +29305,26 @@
       </c>
       <c r="AG251" t="b">
         <v>0</v>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122961958</v>
+        <v>122974681</v>
       </c>
       <c r="B252" t="n">
-        <v>78781</v>
+        <v>79898</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -29352,46 +29333,41 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>459174</v>
+        <v>459157</v>
       </c>
       <c r="R252" t="n">
-        <v>7031337</v>
+        <v>7031692</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -29418,9 +29394,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29435,22 +29426,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122968592</v>
+        <v>122961690</v>
       </c>
       <c r="B253" t="n">
-        <v>82568</v>
+        <v>77714</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -29463,21 +29454,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -29487,13 +29478,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>459172</v>
+        <v>459386</v>
       </c>
       <c r="R253" t="n">
-        <v>7031415</v>
+        <v>7031293</v>
       </c>
       <c r="S253" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -29522,7 +29513,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -29532,12 +29523,12 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>På svagt lutande gran</t>
+          <t>På gammal gran ca 23 cm i diameter</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29552,22 +29543,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122962434</v>
+        <v>122988607</v>
       </c>
       <c r="B254" t="n">
-        <v>79863</v>
+        <v>90983</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -29580,42 +29571,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>459411</v>
+        <v>458882</v>
       </c>
       <c r="R254" t="n">
-        <v>7031335</v>
+        <v>7031377</v>
       </c>
       <c r="S254" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -29647,11 +29633,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>På en liggande levande smal sälg.</t>
-        </is>
-      </c>
       <c r="AD254" t="b">
         <v>0</v>
       </c>
@@ -29660,48 +29641,23 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122988659</v>
+        <v>122988657</v>
       </c>
       <c r="B255" t="n">
         <v>78781</v>
@@ -29741,10 +29697,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>458995</v>
+        <v>459055</v>
       </c>
       <c r="R255" t="n">
-        <v>7031695</v>
+        <v>7031634</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29803,7 +29759,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122970161</v>
+        <v>122971004</v>
       </c>
       <c r="B256" t="n">
         <v>78781</v>
@@ -29836,20 +29792,34 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>459355</v>
+        <v>459301</v>
       </c>
       <c r="R256" t="n">
-        <v>7031426</v>
+        <v>7031350</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29883,7 +29853,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med långväxta bålar på många granar. Fertila bålar med apothecier förekommer.</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29935,10 +29905,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122961346</v>
+        <v>122961958</v>
       </c>
       <c r="B257" t="n">
-        <v>82568</v>
+        <v>78781</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -29951,34 +29921,39 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>459218</v>
+        <v>459174</v>
       </c>
       <c r="R257" t="n">
-        <v>7031359</v>
+        <v>7031337</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -30037,10 +30012,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122962973</v>
+        <v>122968592</v>
       </c>
       <c r="B258" t="n">
-        <v>78781</v>
+        <v>82568</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -30053,46 +30028,37 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>459220</v>
+        <v>459172</v>
       </c>
       <c r="R258" t="n">
-        <v>7031245</v>
+        <v>7031415</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -30119,14 +30085,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>På svagt lutande gran</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -30141,22 +30117,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122988637</v>
+        <v>122962434</v>
       </c>
       <c r="B259" t="n">
-        <v>91001</v>
+        <v>79863</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -30169,37 +30145,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>459515</v>
+        <v>459411</v>
       </c>
       <c r="R259" t="n">
-        <v>7031220</v>
+        <v>7031335</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -30231,6 +30212,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>På en liggande levande smal sälg.</t>
+        </is>
+      </c>
       <c r="AD259" t="b">
         <v>0</v>
       </c>
@@ -30239,26 +30225,51 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122961832</v>
+        <v>122988659</v>
       </c>
       <c r="B260" t="n">
-        <v>74875</v>
+        <v>78781</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -30271,34 +30282,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>459199</v>
+        <v>458995</v>
       </c>
       <c r="R260" t="n">
-        <v>7031334</v>
+        <v>7031695</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30345,22 +30356,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122962736</v>
+        <v>122970161</v>
       </c>
       <c r="B261" t="n">
-        <v>79897</v>
+        <v>78781</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -30369,20 +30380,20 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -30397,13 +30408,13 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>459417</v>
+        <v>459355</v>
       </c>
       <c r="R261" t="n">
-        <v>7031346</v>
+        <v>7031426</v>
       </c>
       <c r="S261" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -30435,6 +30446,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
@@ -30451,22 +30467,22 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -30484,10 +30500,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122988669</v>
+        <v>122961346</v>
       </c>
       <c r="B262" t="n">
-        <v>77709</v>
+        <v>82568</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -30500,34 +30516,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>459002</v>
+        <v>459218</v>
       </c>
       <c r="R262" t="n">
-        <v>7031384</v>
+        <v>7031359</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30574,22 +30590,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122988629</v>
+        <v>122962973</v>
       </c>
       <c r="B263" t="n">
-        <v>79862</v>
+        <v>78781</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -30602,34 +30618,43 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>458990</v>
+        <v>459220</v>
       </c>
       <c r="R263" t="n">
-        <v>7031684</v>
+        <v>7031245</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30664,6 +30689,11 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
+        </is>
+      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
@@ -30676,22 +30706,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122974681</v>
+        <v>122988637</v>
       </c>
       <c r="B264" t="n">
-        <v>79898</v>
+        <v>91001</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -30700,41 +30730,41 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Jo-Nilsvallen, Jo-Nilsvallen, Jmt</t>
+          <t>Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>459157</v>
+        <v>459515</v>
       </c>
       <c r="R264" t="n">
-        <v>7031692</v>
+        <v>7031220</v>
       </c>
       <c r="S264" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -30761,24 +30791,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30793,22 +30808,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122961690</v>
+        <v>122961832</v>
       </c>
       <c r="B265" t="n">
-        <v>77714</v>
+        <v>74875</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -30821,21 +30836,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -30845,13 +30860,13 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>459386</v>
+        <v>459199</v>
       </c>
       <c r="R265" t="n">
-        <v>7031293</v>
+        <v>7031334</v>
       </c>
       <c r="S265" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30878,24 +30893,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>På gammal gran ca 23 cm i diameter</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30910,12 +30910,12 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
@@ -36199,10 +36199,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>123010781</v>
+        <v>123010788</v>
       </c>
       <c r="B312" t="n">
-        <v>77714</v>
+        <v>79863</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -36215,21 +36215,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459191</v>
+        <v>459229</v>
       </c>
       <c r="R312" t="n">
-        <v>7031091</v>
+        <v>7031215</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -36274,7 +36274,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -36295,6 +36295,21 @@
       </c>
       <c r="AG312" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK312" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
@@ -36304,17 +36319,17 @@
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>123010788</v>
+        <v>123010781</v>
       </c>
       <c r="B313" t="n">
-        <v>79863</v>
+        <v>77714</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -36327,21 +36342,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -36351,10 +36366,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>459229</v>
+        <v>459191</v>
       </c>
       <c r="R313" t="n">
-        <v>7031215</v>
+        <v>7031091</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -36386,7 +36401,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -36396,7 +36411,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -36407,21 +36422,6 @@
       </c>
       <c r="AG313" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK313" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO313" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
@@ -37377,10 +37377,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>123010765</v>
+        <v>123010779</v>
       </c>
       <c r="B322" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -37393,21 +37393,21 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -37417,10 +37417,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>459062</v>
+        <v>459170</v>
       </c>
       <c r="R322" t="n">
-        <v>7031083</v>
+        <v>7031086</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -37452,7 +37452,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -37489,7 +37489,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>123010779</v>
+        <v>123010800</v>
       </c>
       <c r="B323" t="n">
         <v>78781</v>
@@ -37529,10 +37529,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>459170</v>
+        <v>459400</v>
       </c>
       <c r="R323" t="n">
-        <v>7031086</v>
+        <v>7031215</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -37564,7 +37564,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -37574,7 +37574,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -37601,10 +37601,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>123010800</v>
+        <v>123010765</v>
       </c>
       <c r="B324" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -37617,21 +37617,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -37641,10 +37641,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>459400</v>
+        <v>459062</v>
       </c>
       <c r="R324" t="n">
-        <v>7031215</v>
+        <v>7031083</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -37676,7 +37676,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -37686,7 +37686,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD324" t="b">

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -34698,10 +34698,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>123010792</v>
+        <v>123010791</v>
       </c>
       <c r="B299" t="n">
-        <v>56689</v>
+        <v>74859</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -34710,43 +34710,38 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>102612</v>
+        <v>6439</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>459312</v>
+        <v>459278</v>
       </c>
       <c r="R299" t="n">
-        <v>7031201</v>
+        <v>7031203</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34778,7 +34773,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -34788,7 +34783,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -34815,10 +34810,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>123010791</v>
+        <v>123010790</v>
       </c>
       <c r="B300" t="n">
-        <v>74859</v>
+        <v>78781</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -34827,25 +34822,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -34855,10 +34850,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>459278</v>
+        <v>459239</v>
       </c>
       <c r="R300" t="n">
-        <v>7031203</v>
+        <v>7031208</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34890,7 +34885,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -34900,7 +34895,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34927,10 +34922,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>123010790</v>
+        <v>123010792</v>
       </c>
       <c r="B301" t="n">
-        <v>78781</v>
+        <v>56689</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -34943,34 +34938,39 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P301" t="inlineStr">
         <is>
           <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>459239</v>
+        <v>459312</v>
       </c>
       <c r="R301" t="n">
-        <v>7031208</v>
+        <v>7031201</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -35002,7 +35002,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -35012,7 +35012,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -36199,10 +36199,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>123010781</v>
+        <v>123010788</v>
       </c>
       <c r="B312" t="n">
-        <v>77714</v>
+        <v>79863</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -36215,21 +36215,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459191</v>
+        <v>459229</v>
       </c>
       <c r="R312" t="n">
-        <v>7031091</v>
+        <v>7031215</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -36274,7 +36274,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -36295,6 +36295,21 @@
       </c>
       <c r="AG312" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK312" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
@@ -36304,17 +36319,17 @@
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>123010788</v>
+        <v>123010781</v>
       </c>
       <c r="B313" t="n">
-        <v>79863</v>
+        <v>77714</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -36327,21 +36342,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -36351,10 +36366,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>459229</v>
+        <v>459191</v>
       </c>
       <c r="R313" t="n">
-        <v>7031215</v>
+        <v>7031091</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -36386,7 +36401,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -36396,7 +36411,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -36407,21 +36422,6 @@
       </c>
       <c r="AG313" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK313" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO313" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
@@ -37015,10 +37015,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122961559</v>
+        <v>123010811</v>
       </c>
       <c r="B319" t="n">
-        <v>79862</v>
+        <v>74875</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -37031,48 +37031,37 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
+          <t>Stavre Ö, Jmt</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>459334</v>
+        <v>459550</v>
       </c>
       <c r="R319" t="n">
-        <v>7031154</v>
+        <v>7031204</v>
       </c>
       <c r="S319" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -37101,7 +37090,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -37111,12 +37100,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -37125,29 +37109,28 @@
       <c r="AE319" t="b">
         <v>0</v>
       </c>
-      <c r="AF319" t="inlineStr"/>
       <c r="AG319" t="b">
         <v>0</v>
       </c>
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>123010811</v>
+        <v>122961873</v>
       </c>
       <c r="B320" t="n">
-        <v>74875</v>
+        <v>74870</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -37160,34 +37143,37 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6440</v>
+        <v>310</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Stavre Ö, Jmt</t>
+          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>459550</v>
+        <v>459357</v>
       </c>
       <c r="R320" t="n">
-        <v>7031204</v>
+        <v>7031297</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -37219,7 +37205,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -37229,7 +37215,12 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -37238,28 +37229,29 @@
       <c r="AE320" t="b">
         <v>0</v>
       </c>
+      <c r="AF320" t="inlineStr"/>
       <c r="AG320" t="b">
         <v>0</v>
       </c>
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122961873</v>
+        <v>122961559</v>
       </c>
       <c r="B321" t="n">
-        <v>74870</v>
+        <v>79862</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -37272,40 +37264,48 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Sönnestmyren, N. om, , Sönnestmyren, Offerdal, Jmt</t>
+          <t>Sönnestmyren, Sönnestmyren, Jmt</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>459357</v>
+        <v>459334</v>
       </c>
       <c r="R321" t="n">
-        <v>7031297</v>
+        <v>7031154</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -37344,12 +37344,12 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal granskog vid bäck</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -37365,12 +37365,12 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
@@ -38202,10 +38202,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>123010767</v>
+        <v>123010748</v>
       </c>
       <c r="B329" t="n">
-        <v>74866</v>
+        <v>79862</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -38214,25 +38214,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -38242,10 +38242,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>459067</v>
+        <v>459052</v>
       </c>
       <c r="R329" t="n">
-        <v>7031089</v>
+        <v>7031465</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -38277,7 +38277,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -38298,21 +38298,6 @@
       </c>
       <c r="AG329" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ329" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK329" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO329" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT329" t="inlineStr"/>
       <c r="AW329" t="inlineStr">
@@ -38329,10 +38314,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>123010796</v>
+        <v>123010784</v>
       </c>
       <c r="B330" t="n">
-        <v>82568</v>
+        <v>78781</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -38345,21 +38330,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -38369,10 +38354,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>459341</v>
+        <v>459156</v>
       </c>
       <c r="R330" t="n">
-        <v>7031193</v>
+        <v>7031153</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -38404,7 +38389,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -38414,7 +38399,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -38441,10 +38426,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>123010748</v>
+        <v>123010767</v>
       </c>
       <c r="B331" t="n">
-        <v>79862</v>
+        <v>74866</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -38453,25 +38438,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -38481,10 +38466,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>459052</v>
+        <v>459067</v>
       </c>
       <c r="R331" t="n">
-        <v>7031465</v>
+        <v>7031089</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -38516,7 +38501,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -38526,7 +38511,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -38537,6 +38522,21 @@
       </c>
       <c r="AG331" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT331" t="inlineStr"/>
       <c r="AW331" t="inlineStr">
@@ -38553,10 +38553,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>123010784</v>
+        <v>123010796</v>
       </c>
       <c r="B332" t="n">
-        <v>78781</v>
+        <v>82568</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -38569,21 +38569,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -38593,10 +38593,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>459156</v>
+        <v>459341</v>
       </c>
       <c r="R332" t="n">
-        <v>7031153</v>
+        <v>7031193</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -38628,7 +38628,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -38638,7 +38638,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD332" t="b">

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -40387,7 +40387,7 @@
         <v>122959638</v>
       </c>
       <c r="B348" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>122958335</v>
       </c>
       <c r="B349" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>

--- a/artfynd/A 9977-2025 artfynd.xlsx
+++ b/artfynd/A 9977-2025 artfynd.xlsx
@@ -40387,7 +40387,7 @@
         <v>122959638</v>
       </c>
       <c r="B348" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>122958335</v>
       </c>
       <c r="B349" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
